--- a/PGN 5.7_planter.xlsx
+++ b/PGN 5.7_planter.xlsx
@@ -11,7 +11,7 @@
     <sheet name="PGN" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">PGN!$A$1:$Q$109</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">PGN!$A$1:$Q$114</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="312">
   <si>
     <t xml:space="preserve">PGN Name</t>
   </si>
@@ -619,75 +619,141 @@
     <t xml:space="preserve">Row Crop</t>
   </si>
   <si>
+    <t xml:space="preserve">Singulation1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 to 100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Singulation2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spacing by row1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 to 255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spacing by row2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA</t>
+  </si>
+  <si>
     <t xml:space="preserve">ConfigB</t>
   </si>
   <si>
     <t xml:space="preserve">Array Speed</t>
   </si>
   <si>
-    <t xml:space="preserve">Singulation1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Row 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Row 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Row 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Row 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Row 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Row 6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Row 7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Row 8</t>
+    <t xml:space="preserve">Array Skips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 1-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 3-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 5-6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 7-8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 9-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 11-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 13-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 15-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">old, not used</t>
   </si>
   <si>
     <t xml:space="preserve">IP = 192.168.1.192</t>
   </si>
   <si>
-    <t xml:space="preserve">Singulation2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Row 9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Row 10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Row 11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Row 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Row 13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Row 14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Row 15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Row 16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">percent</t>
+    <t xml:space="preserve">Array Doubles</t>
   </si>
   <si>
     <t xml:space="preserve">Hello = 9998?</t>
   </si>
   <si>
+    <t xml:space="preserve">Row Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 1-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 5-8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 9-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 13-16</t>
+  </si>
+  <si>
     <t xml:space="preserve">Port = 9998</t>
   </si>
   <si>
@@ -697,69 +763,13 @@
     <t xml:space="preserve">PopulationD10 HI/Lo</t>
   </si>
   <si>
-    <t xml:space="preserve">SkipsPercX100 Hi/Lo</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Doubles</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">PercX100</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> Hi/Lo</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Singulation</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">PercX100</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> Hi/Lo</t>
-    </r>
+    <t xml:space="preserve">SkipsPercX10 Hi/Lo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DoublesPercX10 Hi/Lo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SingulationPercX10 Hi/Lo</t>
   </si>
   <si>
     <t xml:space="preserve">Skips</t>
@@ -768,28 +778,7 @@
     <t xml:space="preserve">E4</t>
   </si>
   <si>
-    <t xml:space="preserve">Row 1-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Row 3-4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Row 5-6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Row 7-8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Row 9-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Row 11-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Row 13-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Row 15-16</t>
+    <t xml:space="preserve">1 to 7 per time array</t>
   </si>
   <si>
     <t xml:space="preserve">Doubles</t>
@@ -798,18 +787,12 @@
     <t xml:space="preserve">E3</t>
   </si>
   <si>
-    <t xml:space="preserve">1 to 7 per time array</t>
-  </si>
-  <si>
     <t xml:space="preserve">Population by row</t>
   </si>
   <si>
     <t xml:space="preserve">E2</t>
   </si>
   <si>
-    <t xml:space="preserve">Pop / ha div 2500</t>
-  </si>
-  <si>
     <t xml:space="preserve">E1</t>
   </si>
   <si>
@@ -838,9 +821,6 @@
   </si>
   <si>
     <t xml:space="preserve">Switch Control</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EA</t>
   </si>
   <si>
     <t xml:space="preserve">Main</t>
@@ -989,7 +969,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1061,12 +1041,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b val="true"/>
@@ -1698,15 +1672,15 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="3" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="3" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="2" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="2" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="3" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="3" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1969,7 +1943,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:AP108"/>
+  <dimension ref="A1:AP113"/>
   <sheetFormatPr defaultColWidth="9.1484375" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.42"/>
@@ -3983,25 +3957,13 @@
       <c r="B69" s="61" t="s">
         <v>197</v>
       </c>
-      <c r="C69" s="73" t="s">
-        <v>198</v>
-      </c>
-      <c r="D69" s="63" t="s">
-        <v>102</v>
-      </c>
+      <c r="C69" s="73"/>
+      <c r="D69" s="63"/>
       <c r="E69" s="74"/>
-      <c r="F69" s="65" t="s">
-        <v>154</v>
-      </c>
-      <c r="G69" s="66" t="n">
-        <v>233</v>
-      </c>
-      <c r="H69" s="75" t="n">
-        <v>8</v>
-      </c>
-      <c r="I69" s="23" t="s">
-        <v>199</v>
-      </c>
+      <c r="F69" s="65"/>
+      <c r="G69" s="66"/>
+      <c r="H69" s="75"/>
+      <c r="I69" s="23"/>
       <c r="J69" s="23"/>
       <c r="K69" s="23"/>
       <c r="L69" s="23"/>
@@ -4014,710 +3976,729 @@
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="69"/>
       <c r="C70" s="76" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D70" s="4" t="s">
         <v>102</v>
       </c>
       <c r="E70" s="77"/>
       <c r="F70" s="6" t="s">
-        <v>162</v>
+        <v>103</v>
       </c>
       <c r="G70" s="7" t="n">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="H70" s="78" t="n">
         <v>8</v>
       </c>
       <c r="I70" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="J70" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="K70" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="J70" s="8" t="s">
+      <c r="L70" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="K70" s="8" t="s">
+      <c r="M70" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="L70" s="8" t="s">
+      <c r="N70" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="M70" s="8" t="s">
+      <c r="O70" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="N70" s="8" t="s">
+      <c r="P70" s="10" t="s">
         <v>206</v>
-      </c>
-      <c r="O70" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="P70" s="10" t="s">
-        <v>208</v>
       </c>
       <c r="Q70" s="78" t="s">
         <v>25</v>
       </c>
+      <c r="R70" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="S70" s="10" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="69"/>
-      <c r="B71" s="49" t="s">
+      <c r="C71" s="76" t="s">
         <v>209</v>
-      </c>
-      <c r="C71" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="D71" s="4" t="s">
         <v>102</v>
       </c>
       <c r="E71" s="77"/>
       <c r="F71" s="6" t="s">
-        <v>172</v>
+        <v>81</v>
       </c>
       <c r="G71" s="7" t="n">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="H71" s="78" t="n">
         <v>8</v>
       </c>
       <c r="I71" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="J71" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="J71" s="8" t="s">
+      <c r="K71" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="K71" s="8" t="s">
+      <c r="L71" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="L71" s="8" t="s">
+      <c r="M71" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="M71" s="8" t="s">
+      <c r="N71" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="N71" s="8" t="s">
+      <c r="O71" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="O71" s="8" t="s">
+      <c r="P71" s="10" t="s">
         <v>217</v>
-      </c>
-      <c r="P71" s="10" t="s">
-        <v>218</v>
       </c>
       <c r="Q71" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="R71" s="10" t="s">
-        <v>219</v>
-      </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="69"/>
-      <c r="B72" s="49" t="s">
-        <v>220</v>
-      </c>
-      <c r="C72" s="76"/>
+      <c r="C72" s="76" t="s">
+        <v>218</v>
+      </c>
       <c r="D72" s="4" t="s">
         <v>102</v>
       </c>
       <c r="E72" s="77"/>
       <c r="F72" s="6" t="s">
-        <v>191</v>
+        <v>83</v>
       </c>
       <c r="G72" s="7" t="n">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="H72" s="78" t="n">
         <v>8</v>
       </c>
-      <c r="I72" s="8"/>
-      <c r="J72" s="8"/>
-      <c r="K72" s="8"/>
-      <c r="L72" s="8"/>
-      <c r="M72" s="8"/>
-      <c r="N72" s="8"/>
-      <c r="O72" s="8"/>
-      <c r="Q72" s="78"/>
+      <c r="I72" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="J72" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="K72" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="L72" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="M72" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="N72" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="O72" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="P72" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q72" s="78" t="s">
+        <v>25</v>
+      </c>
+      <c r="R72" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="S72" s="10" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="69"/>
-      <c r="B73" s="49" t="s">
+      <c r="C73" s="76" t="s">
         <v>221</v>
-      </c>
-      <c r="C73" s="76" t="s">
-        <v>222</v>
       </c>
       <c r="D73" s="4" t="s">
         <v>102</v>
       </c>
       <c r="E73" s="77"/>
       <c r="F73" s="6" t="s">
-        <v>105</v>
+        <v>222</v>
       </c>
       <c r="G73" s="7" t="n">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="H73" s="78" t="n">
         <v>8</v>
       </c>
-      <c r="I73" s="79" t="s">
-        <v>223</v>
-      </c>
-      <c r="J73" s="79"/>
+      <c r="I73" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="J73" s="8" t="s">
+        <v>211</v>
+      </c>
       <c r="K73" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="L73" s="8"/>
+        <v>212</v>
+      </c>
+      <c r="L73" s="8" t="s">
+        <v>213</v>
+      </c>
       <c r="M73" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="N73" s="8"/>
+        <v>214</v>
+      </c>
+      <c r="N73" s="8" t="s">
+        <v>215</v>
+      </c>
       <c r="O73" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="P73" s="8"/>
-      <c r="Q73" s="78"/>
+        <v>216</v>
+      </c>
+      <c r="P73" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q73" s="78" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="69"/>
       <c r="C74" s="76" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D74" s="4" t="s">
         <v>102</v>
       </c>
       <c r="E74" s="77"/>
       <c r="F74" s="6" t="s">
-        <v>228</v>
+        <v>154</v>
       </c>
       <c r="G74" s="7" t="n">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="H74" s="78" t="n">
         <v>8</v>
       </c>
       <c r="I74" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="J74" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="K74" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="L74" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="M74" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="N74" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="O74" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="P74" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="Q74" s="78" t="s">
-        <v>25</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="J74" s="8"/>
+      <c r="K74" s="8"/>
+      <c r="L74" s="8"/>
+      <c r="M74" s="8"/>
+      <c r="N74" s="8"/>
+      <c r="O74" s="8"/>
+      <c r="Q74" s="78"/>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="69"/>
       <c r="C75" s="76" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="D75" s="4" t="s">
         <v>102</v>
       </c>
       <c r="E75" s="77"/>
       <c r="F75" s="6" t="s">
-        <v>238</v>
+        <v>162</v>
       </c>
       <c r="G75" s="7" t="n">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="H75" s="78" t="n">
         <v>8</v>
       </c>
       <c r="I75" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="J75" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="K75" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="L75" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="J75" s="8" t="s">
+      <c r="M75" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="K75" s="8" t="s">
+      <c r="N75" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="L75" s="8" t="s">
+      <c r="O75" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="M75" s="8" t="s">
+      <c r="P75" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="N75" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="O75" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="P75" s="10" t="s">
-        <v>236</v>
       </c>
       <c r="Q75" s="78" t="s">
         <v>25</v>
       </c>
       <c r="R75" s="10" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="69"/>
+      <c r="B76" s="49" t="s">
+        <v>235</v>
+      </c>
       <c r="C76" s="76" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D76" s="4" t="s">
         <v>102</v>
       </c>
       <c r="E76" s="77"/>
       <c r="F76" s="6" t="s">
-        <v>241</v>
+        <v>172</v>
       </c>
       <c r="G76" s="7" t="n">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="H76" s="78" t="n">
         <v>8</v>
       </c>
       <c r="I76" s="8" t="s">
-        <v>201</v>
+        <v>226</v>
       </c>
       <c r="J76" s="8" t="s">
-        <v>202</v>
+        <v>227</v>
       </c>
       <c r="K76" s="8" t="s">
-        <v>203</v>
+        <v>228</v>
       </c>
       <c r="L76" s="8" t="s">
-        <v>204</v>
+        <v>229</v>
       </c>
       <c r="M76" s="8" t="s">
-        <v>205</v>
+        <v>230</v>
       </c>
       <c r="N76" s="8" t="s">
-        <v>206</v>
+        <v>231</v>
       </c>
       <c r="O76" s="8" t="s">
-        <v>207</v>
+        <v>232</v>
       </c>
       <c r="P76" s="10" t="s">
-        <v>208</v>
+        <v>233</v>
       </c>
       <c r="Q76" s="78" t="s">
         <v>25</v>
       </c>
       <c r="R76" s="10" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="69"/>
+      <c r="B77" s="49" t="s">
+        <v>237</v>
+      </c>
       <c r="C77" s="76" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D77" s="4" t="s">
         <v>102</v>
       </c>
       <c r="E77" s="77"/>
       <c r="F77" s="6" t="s">
-        <v>243</v>
+        <v>191</v>
       </c>
       <c r="G77" s="7" t="n">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="H77" s="78" t="n">
         <v>8</v>
       </c>
       <c r="I77" s="8" t="s">
-        <v>211</v>
+        <v>239</v>
       </c>
       <c r="J77" s="8" t="s">
-        <v>212</v>
+        <v>240</v>
       </c>
       <c r="K77" s="8" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="L77" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="M77" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="N77" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="O77" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="P77" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="Q77" s="78" t="s">
+        <v>242</v>
+      </c>
+      <c r="M77" s="8"/>
+      <c r="N77" s="8"/>
+      <c r="O77" s="8"/>
+      <c r="Q77" s="78"/>
+      <c r="R77" s="10" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="69"/>
+      <c r="B78" s="49" t="s">
+        <v>243</v>
+      </c>
+      <c r="C78" s="76" t="s">
+        <v>244</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E78" s="77"/>
+      <c r="F78" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="G78" s="7" t="n">
+        <v>229</v>
+      </c>
+      <c r="H78" s="78" t="n">
+        <v>8</v>
+      </c>
+      <c r="I78" s="79" t="s">
+        <v>245</v>
+      </c>
+      <c r="J78" s="79"/>
+      <c r="K78" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="L78" s="8"/>
+      <c r="M78" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="N78" s="8"/>
+      <c r="O78" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="P78" s="8"/>
+      <c r="Q78" s="78"/>
+    </row>
+    <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="69"/>
+      <c r="C79" s="76" t="s">
+        <v>249</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E79" s="77"/>
+      <c r="F79" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="G79" s="7" t="n">
+        <v>228</v>
+      </c>
+      <c r="H79" s="78" t="n">
+        <v>8</v>
+      </c>
+      <c r="I79" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="J79" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="K79" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="L79" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="M79" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="N79" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="O79" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="P79" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q79" s="78" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="78" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="80"/>
-      <c r="B78" s="51"/>
-      <c r="C78" s="81" t="s">
-        <v>244</v>
-      </c>
-      <c r="D78" s="53" t="s">
+      <c r="R79" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="S79" s="8"/>
+      <c r="T79" s="8"/>
+      <c r="U79" s="8"/>
+      <c r="V79" s="8"/>
+    </row>
+    <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="69"/>
+      <c r="C80" s="76" t="s">
+        <v>252</v>
+      </c>
+      <c r="D80" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="E78" s="82"/>
-      <c r="F78" s="55" t="s">
-        <v>245</v>
-      </c>
-      <c r="G78" s="56" t="n">
-        <v>224</v>
-      </c>
-      <c r="H78" s="83" t="n">
-        <v>8</v>
-      </c>
-      <c r="I78" s="84" t="s">
-        <v>246</v>
-      </c>
-      <c r="J78" s="84" t="s">
-        <v>247</v>
-      </c>
-      <c r="K78" s="84" t="s">
-        <v>248</v>
-      </c>
-      <c r="L78" s="84"/>
-      <c r="M78" s="57" t="s">
-        <v>249</v>
-      </c>
-      <c r="N78" s="57"/>
-      <c r="O78" s="84" t="s">
-        <v>250</v>
-      </c>
-      <c r="P78" s="57" t="s">
-        <v>251</v>
-      </c>
-      <c r="Q78" s="83" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="79" s="60" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B79" s="85"/>
-      <c r="C79" s="62"/>
-      <c r="D79" s="63"/>
-      <c r="E79" s="64"/>
-      <c r="F79" s="65"/>
-      <c r="G79" s="66"/>
-      <c r="H79" s="23"/>
-      <c r="I79" s="67"/>
-      <c r="J79" s="23"/>
-      <c r="K79" s="23"/>
-      <c r="L79" s="23"/>
-      <c r="M79" s="23"/>
-      <c r="N79" s="23"/>
-      <c r="O79" s="23"/>
-      <c r="P79" s="23"/>
-      <c r="Q79" s="23"/>
-      <c r="R79" s="23"/>
-      <c r="S79" s="23"/>
-      <c r="T79" s="23"/>
-      <c r="U79" s="23"/>
-      <c r="V79" s="23"/>
-      <c r="W79" s="23"/>
-      <c r="X79" s="23"/>
-      <c r="Y79" s="23"/>
-      <c r="Z79" s="23"/>
-      <c r="AA79" s="23"/>
-      <c r="AB79" s="23"/>
-      <c r="AC79" s="23"/>
-      <c r="AD79" s="23"/>
-      <c r="AE79" s="23"/>
-      <c r="AF79" s="23"/>
-      <c r="AG79" s="23"/>
-      <c r="AH79" s="23"/>
-      <c r="AI79" s="23"/>
-      <c r="AJ79" s="23"/>
-      <c r="AK79" s="23"/>
-      <c r="AL79" s="23"/>
-      <c r="AM79" s="23"/>
-      <c r="AN79" s="23"/>
-    </row>
-    <row r="80" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B80" s="49"/>
-      <c r="C80" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="D80" s="4" t="n">
-        <v>77</v>
-      </c>
-      <c r="E80" s="5" t="n">
-        <v>119</v>
-      </c>
+      <c r="E80" s="77"/>
       <c r="F80" s="6" t="s">
         <v>253</v>
       </c>
       <c r="G80" s="7" t="n">
+        <v>227</v>
+      </c>
+      <c r="H80" s="78" t="n">
+        <v>8</v>
+      </c>
+      <c r="I80" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="J80" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="K80" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="L80" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="M80" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="N80" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="O80" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="P80" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q80" s="78" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="69"/>
+      <c r="C81" s="76" t="s">
+        <v>254</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E81" s="77"/>
+      <c r="F81" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="G81" s="7" t="n">
+        <v>226</v>
+      </c>
+      <c r="H81" s="78" t="n">
+        <v>8</v>
+      </c>
+      <c r="I81" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="J81" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="K81" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="L81" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="M81" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="N81" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="O81" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="P81" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q81" s="78" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="69"/>
+      <c r="C82" s="76" t="s">
+        <v>254</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E82" s="77"/>
+      <c r="F82" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="G82" s="7" t="n">
+        <v>225</v>
+      </c>
+      <c r="H82" s="78" t="n">
+        <v>8</v>
+      </c>
+      <c r="I82" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="J82" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="K82" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="L82" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="M82" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="N82" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="O82" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="P82" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q82" s="78" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="80"/>
+      <c r="B83" s="51"/>
+      <c r="C83" s="81" t="s">
+        <v>257</v>
+      </c>
+      <c r="D83" s="53" t="s">
+        <v>102</v>
+      </c>
+      <c r="E83" s="82"/>
+      <c r="F83" s="55" t="s">
+        <v>258</v>
+      </c>
+      <c r="G83" s="56" t="n">
+        <v>224</v>
+      </c>
+      <c r="H83" s="83" t="n">
+        <v>8</v>
+      </c>
+      <c r="I83" s="84" t="s">
+        <v>259</v>
+      </c>
+      <c r="J83" s="84" t="s">
+        <v>260</v>
+      </c>
+      <c r="K83" s="84" t="s">
+        <v>261</v>
+      </c>
+      <c r="L83" s="84"/>
+      <c r="M83" s="57" t="s">
+        <v>262</v>
+      </c>
+      <c r="N83" s="57"/>
+      <c r="O83" s="84" t="s">
+        <v>263</v>
+      </c>
+      <c r="P83" s="57" t="s">
+        <v>264</v>
+      </c>
+      <c r="Q83" s="83" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="84" s="60" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B84" s="85"/>
+      <c r="C84" s="62"/>
+      <c r="D84" s="63"/>
+      <c r="E84" s="64"/>
+      <c r="F84" s="65"/>
+      <c r="G84" s="66"/>
+      <c r="H84" s="23"/>
+      <c r="I84" s="67"/>
+      <c r="J84" s="23"/>
+      <c r="K84" s="23"/>
+      <c r="L84" s="23"/>
+      <c r="M84" s="23"/>
+      <c r="N84" s="23"/>
+      <c r="O84" s="23"/>
+      <c r="P84" s="23"/>
+      <c r="Q84" s="23"/>
+      <c r="R84" s="23"/>
+      <c r="S84" s="23"/>
+      <c r="T84" s="23"/>
+      <c r="U84" s="23"/>
+      <c r="V84" s="23"/>
+      <c r="W84" s="23"/>
+      <c r="X84" s="23"/>
+      <c r="Y84" s="23"/>
+      <c r="Z84" s="23"/>
+      <c r="AA84" s="23"/>
+      <c r="AB84" s="23"/>
+      <c r="AC84" s="23"/>
+      <c r="AD84" s="23"/>
+      <c r="AE84" s="23"/>
+      <c r="AF84" s="23"/>
+      <c r="AG84" s="23"/>
+      <c r="AH84" s="23"/>
+      <c r="AI84" s="23"/>
+      <c r="AJ84" s="23"/>
+      <c r="AK84" s="23"/>
+      <c r="AL84" s="23"/>
+      <c r="AM84" s="23"/>
+      <c r="AN84" s="23"/>
+    </row>
+    <row r="85" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B85" s="49"/>
+      <c r="C85" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D85" s="4" t="n">
+        <v>77</v>
+      </c>
+      <c r="E85" s="5" t="n">
+        <v>119</v>
+      </c>
+      <c r="F85" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="G85" s="7" t="n">
         <v>234</v>
       </c>
-      <c r="H80" s="8"/>
-      <c r="I80" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="J80" s="8" t="s">
-        <v>255</v>
-      </c>
-      <c r="K80" s="8" t="s">
-        <v>255</v>
-      </c>
-      <c r="L80" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="M80" s="8" t="s">
-        <v>257</v>
-      </c>
-      <c r="N80" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="O80" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="P80" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="Q80" s="8" t="s">
+      <c r="H85" s="8"/>
+      <c r="I85" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="J85" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="K85" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="L85" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="M85" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="N85" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="O85" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="P85" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q85" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="R80" s="8"/>
-      <c r="S80" s="8"/>
-      <c r="T80" s="8"/>
-      <c r="U80" s="8"/>
-      <c r="V80" s="8"/>
-      <c r="W80" s="8"/>
-      <c r="X80" s="8"/>
-      <c r="Y80" s="8"/>
-      <c r="Z80" s="8"/>
-      <c r="AA80" s="8"/>
-      <c r="AB80" s="8"/>
-      <c r="AC80" s="8"/>
-      <c r="AD80" s="8"/>
-      <c r="AE80" s="8"/>
-      <c r="AF80" s="8"/>
-      <c r="AG80" s="8"/>
-      <c r="AH80" s="8"/>
-      <c r="AI80" s="8"/>
-      <c r="AJ80" s="8"/>
-      <c r="AK80" s="8"/>
-      <c r="AL80" s="8"/>
-      <c r="AM80" s="8"/>
-      <c r="AN80" s="8"/>
-    </row>
-    <row r="81" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B81" s="49"/>
-      <c r="C81" s="3"/>
-      <c r="D81" s="4"/>
-      <c r="E81" s="5"/>
-      <c r="F81" s="6"/>
-      <c r="G81" s="7"/>
-      <c r="H81" s="8"/>
-      <c r="I81" s="9"/>
-      <c r="J81" s="8"/>
-      <c r="K81" s="8"/>
-      <c r="L81" s="8"/>
-      <c r="M81" s="8"/>
-      <c r="N81" s="8"/>
-      <c r="O81" s="8"/>
-      <c r="P81" s="8"/>
-      <c r="Q81" s="8"/>
-      <c r="R81" s="8"/>
-      <c r="S81" s="8"/>
-      <c r="T81" s="8"/>
-      <c r="U81" s="8"/>
-      <c r="V81" s="8"/>
-      <c r="W81" s="8"/>
-      <c r="X81" s="8"/>
-      <c r="Y81" s="8"/>
-      <c r="Z81" s="8"/>
-      <c r="AA81" s="8"/>
-      <c r="AB81" s="8"/>
-      <c r="AC81" s="8"/>
-      <c r="AD81" s="8"/>
-      <c r="AE81" s="8"/>
-      <c r="AF81" s="8"/>
-      <c r="AG81" s="8"/>
-      <c r="AH81" s="8"/>
-      <c r="AI81" s="8"/>
-      <c r="AJ81" s="8"/>
-      <c r="AK81" s="8"/>
-      <c r="AL81" s="8"/>
-      <c r="AM81" s="8"/>
-      <c r="AN81" s="8"/>
-    </row>
-    <row r="82" s="50" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B82" s="51"/>
-      <c r="C82" s="52"/>
-      <c r="D82" s="53"/>
-      <c r="E82" s="54"/>
-      <c r="F82" s="55"/>
-      <c r="G82" s="56"/>
-      <c r="H82" s="57"/>
-      <c r="I82" s="58"/>
-      <c r="J82" s="57"/>
-      <c r="K82" s="57"/>
-      <c r="L82" s="57"/>
-      <c r="M82" s="57"/>
-      <c r="N82" s="57"/>
-      <c r="O82" s="57"/>
-      <c r="P82" s="57"/>
-      <c r="Q82" s="57"/>
-      <c r="R82" s="57"/>
-      <c r="S82" s="57"/>
-      <c r="T82" s="57"/>
-      <c r="U82" s="57"/>
-      <c r="V82" s="57"/>
-      <c r="W82" s="57"/>
-      <c r="X82" s="57"/>
-      <c r="Y82" s="57"/>
-      <c r="Z82" s="57"/>
-      <c r="AA82" s="57"/>
-      <c r="AB82" s="57"/>
-      <c r="AC82" s="57"/>
-      <c r="AD82" s="57"/>
-      <c r="AE82" s="57"/>
-      <c r="AF82" s="57"/>
-      <c r="AG82" s="57"/>
-      <c r="AH82" s="57"/>
-      <c r="AI82" s="57"/>
-      <c r="AJ82" s="57"/>
-      <c r="AK82" s="57"/>
-      <c r="AL82" s="57"/>
-      <c r="AM82" s="57"/>
-      <c r="AN82" s="57"/>
-    </row>
-    <row r="83" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B83" s="49"/>
-      <c r="C83" s="3"/>
-      <c r="D83" s="4"/>
-      <c r="E83" s="5"/>
-      <c r="F83" s="6"/>
-      <c r="G83" s="7"/>
-      <c r="H83" s="8"/>
-      <c r="I83" s="9"/>
-      <c r="J83" s="8"/>
-      <c r="K83" s="8"/>
-      <c r="L83" s="8"/>
-      <c r="M83" s="8"/>
-      <c r="N83" s="8"/>
-      <c r="O83" s="8"/>
-      <c r="P83" s="8"/>
-      <c r="Q83" s="8"/>
-      <c r="R83" s="8"/>
-      <c r="S83" s="8"/>
-      <c r="T83" s="8"/>
-      <c r="U83" s="8"/>
-      <c r="V83" s="8"/>
-      <c r="W83" s="8"/>
-      <c r="X83" s="8"/>
-      <c r="Y83" s="8"/>
-      <c r="Z83" s="8"/>
-      <c r="AA83" s="8"/>
-      <c r="AB83" s="8"/>
-      <c r="AC83" s="8"/>
-      <c r="AD83" s="8"/>
-      <c r="AE83" s="8"/>
-      <c r="AF83" s="8"/>
-      <c r="AG83" s="8"/>
-      <c r="AH83" s="8"/>
-      <c r="AI83" s="8"/>
-      <c r="AJ83" s="8"/>
-      <c r="AK83" s="8"/>
-      <c r="AL83" s="8"/>
-      <c r="AM83" s="8"/>
-      <c r="AN83" s="8"/>
-    </row>
-    <row r="84" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B84" s="49" t="s">
-        <v>261</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="D84" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E84" s="5"/>
-      <c r="F84" s="6"/>
-      <c r="G84" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="H84" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="I84" s="9" t="s">
-        <v>263</v>
-      </c>
-      <c r="J84" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="M84" s="8"/>
-      <c r="N84" s="8"/>
-      <c r="O84" s="8"/>
-      <c r="P84" s="8"/>
-      <c r="Q84" s="8"/>
-      <c r="R84" s="8"/>
-      <c r="S84" s="8"/>
-      <c r="T84" s="8"/>
-      <c r="U84" s="8"/>
-      <c r="V84" s="8"/>
-      <c r="W84" s="8"/>
-      <c r="X84" s="8"/>
-      <c r="Y84" s="8"/>
-      <c r="Z84" s="8"/>
-      <c r="AA84" s="8"/>
-      <c r="AB84" s="8"/>
-      <c r="AC84" s="8"/>
-      <c r="AD84" s="8"/>
-      <c r="AE84" s="8"/>
-      <c r="AF84" s="8"/>
-      <c r="AG84" s="8"/>
-      <c r="AH84" s="8"/>
-      <c r="AI84" s="8"/>
-      <c r="AJ84" s="8"/>
-      <c r="AK84" s="8"/>
-      <c r="AL84" s="8"/>
-      <c r="AM84" s="8"/>
-      <c r="AN84" s="8"/>
-    </row>
-    <row r="85" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B85" s="86"/>
-      <c r="C85" s="3"/>
-      <c r="D85" s="4"/>
-      <c r="E85" s="5"/>
-      <c r="F85" s="6"/>
-      <c r="G85" s="7"/>
-      <c r="H85" s="8"/>
-      <c r="I85" s="9"/>
-      <c r="J85" s="8"/>
-      <c r="K85" s="8"/>
-      <c r="L85" s="8"/>
-      <c r="M85" s="8"/>
-      <c r="N85" s="8"/>
-      <c r="O85" s="8"/>
-      <c r="P85" s="8"/>
-      <c r="Q85" s="8"/>
       <c r="R85" s="8"/>
       <c r="S85" s="8"/>
       <c r="T85" s="8"/>
@@ -4743,41 +4724,19 @@
       <c r="AN85" s="8"/>
     </row>
     <row r="86" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B86" s="49" t="s">
-        <v>264</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="D86" s="4" t="n">
-        <v>126</v>
-      </c>
+      <c r="B86" s="49"/>
+      <c r="C86" s="3"/>
+      <c r="D86" s="4"/>
       <c r="E86" s="5"/>
       <c r="F86" s="6"/>
-      <c r="G86" s="7" t="n">
-        <v>126</v>
-      </c>
-      <c r="H86" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="I86" s="9" t="s">
-        <v>266</v>
-      </c>
-      <c r="J86" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="K86" s="8" t="s">
-        <v>268</v>
-      </c>
-      <c r="L86" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="M86" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="N86" s="8" t="s">
-        <v>25</v>
-      </c>
+      <c r="G86" s="7"/>
+      <c r="H86" s="8"/>
+      <c r="I86" s="9"/>
+      <c r="J86" s="8"/>
+      <c r="K86" s="8"/>
+      <c r="L86" s="8"/>
+      <c r="M86" s="8"/>
+      <c r="N86" s="8"/>
       <c r="O86" s="8"/>
       <c r="P86" s="8"/>
       <c r="Q86" s="8"/>
@@ -4805,101 +4764,61 @@
       <c r="AM86" s="8"/>
       <c r="AN86" s="8"/>
     </row>
-    <row r="87" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B87" s="86"/>
-      <c r="C87" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="D87" s="4" t="n">
-        <v>123</v>
-      </c>
-      <c r="E87" s="5"/>
-      <c r="F87" s="6"/>
-      <c r="G87" s="7" t="n">
-        <v>123</v>
-      </c>
-      <c r="H87" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="I87" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="J87" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="K87" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="L87" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="M87" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="N87" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="O87" s="8"/>
-      <c r="P87" s="8"/>
-      <c r="Q87" s="8"/>
-      <c r="R87" s="8"/>
-      <c r="S87" s="8"/>
-      <c r="T87" s="8"/>
-      <c r="U87" s="8"/>
-      <c r="V87" s="8"/>
-      <c r="W87" s="8"/>
-      <c r="X87" s="8"/>
-      <c r="Y87" s="8"/>
-      <c r="Z87" s="8"/>
-      <c r="AA87" s="8"/>
-      <c r="AB87" s="8"/>
-      <c r="AC87" s="8"/>
-      <c r="AD87" s="8"/>
-      <c r="AE87" s="8"/>
-      <c r="AF87" s="8"/>
-      <c r="AG87" s="8"/>
-      <c r="AH87" s="8"/>
-      <c r="AI87" s="8"/>
-      <c r="AJ87" s="8"/>
-      <c r="AK87" s="8"/>
-      <c r="AL87" s="8"/>
-      <c r="AM87" s="8"/>
-      <c r="AN87" s="8"/>
+    <row r="87" s="50" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B87" s="51"/>
+      <c r="C87" s="52"/>
+      <c r="D87" s="53"/>
+      <c r="E87" s="54"/>
+      <c r="F87" s="55"/>
+      <c r="G87" s="56"/>
+      <c r="H87" s="57"/>
+      <c r="I87" s="58"/>
+      <c r="J87" s="57"/>
+      <c r="K87" s="57"/>
+      <c r="L87" s="57"/>
+      <c r="M87" s="57"/>
+      <c r="N87" s="57"/>
+      <c r="O87" s="57"/>
+      <c r="P87" s="57"/>
+      <c r="Q87" s="57"/>
+      <c r="R87" s="57"/>
+      <c r="S87" s="57"/>
+      <c r="T87" s="57"/>
+      <c r="U87" s="57"/>
+      <c r="V87" s="57"/>
+      <c r="W87" s="57"/>
+      <c r="X87" s="57"/>
+      <c r="Y87" s="57"/>
+      <c r="Z87" s="57"/>
+      <c r="AA87" s="57"/>
+      <c r="AB87" s="57"/>
+      <c r="AC87" s="57"/>
+      <c r="AD87" s="57"/>
+      <c r="AE87" s="57"/>
+      <c r="AF87" s="57"/>
+      <c r="AG87" s="57"/>
+      <c r="AH87" s="57"/>
+      <c r="AI87" s="57"/>
+      <c r="AJ87" s="57"/>
+      <c r="AK87" s="57"/>
+      <c r="AL87" s="57"/>
+      <c r="AM87" s="57"/>
+      <c r="AN87" s="57"/>
     </row>
     <row r="88" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B88" s="86"/>
-      <c r="C88" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="D88" s="4" t="n">
-        <v>121</v>
-      </c>
+      <c r="B88" s="49"/>
+      <c r="C88" s="3"/>
+      <c r="D88" s="4"/>
       <c r="E88" s="5"/>
       <c r="F88" s="6"/>
-      <c r="G88" s="7" t="n">
-        <v>121</v>
-      </c>
-      <c r="H88" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="I88" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="J88" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="K88" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="L88" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="M88" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="N88" s="8" t="s">
-        <v>25</v>
-      </c>
+      <c r="G88" s="7"/>
+      <c r="H88" s="8"/>
+      <c r="I88" s="9"/>
+      <c r="J88" s="8"/>
+      <c r="K88" s="8"/>
+      <c r="L88" s="8"/>
+      <c r="M88" s="8"/>
+      <c r="N88" s="8"/>
       <c r="O88" s="8"/>
       <c r="P88" s="8"/>
       <c r="Q88" s="8"/>
@@ -4928,39 +4847,37 @@
       <c r="AN88" s="8"/>
     </row>
     <row r="89" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B89" s="86"/>
+      <c r="B89" s="49" t="s">
+        <v>273</v>
+      </c>
       <c r="C89" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="D89" s="4" t="n">
-        <v>120</v>
+        <v>274</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="E89" s="5"/>
       <c r="F89" s="6"/>
       <c r="G89" s="7" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="H89" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I89" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="J89" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="K89" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="L89" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="M89" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="N89" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="J89" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" s="8" t="s">
         <v>25</v>
       </c>
+      <c r="M89" s="8"/>
+      <c r="N89" s="8"/>
       <c r="O89" s="8"/>
       <c r="P89" s="8"/>
       <c r="Q89" s="8"/>
@@ -4989,7 +4906,7 @@
       <c r="AN89" s="8"/>
     </row>
     <row r="90" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B90" s="49"/>
+      <c r="B90" s="86"/>
       <c r="C90" s="3"/>
       <c r="D90" s="4"/>
       <c r="E90" s="5"/>
@@ -5036,31 +4953,31 @@
       <c r="C91" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="D91" s="4" t="s">
-        <v>17</v>
+      <c r="D91" s="4" t="n">
+        <v>126</v>
       </c>
       <c r="E91" s="5"/>
       <c r="F91" s="6"/>
       <c r="G91" s="7" t="n">
-        <v>201</v>
+        <v>126</v>
       </c>
       <c r="H91" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="I91" s="9" t="n">
-        <v>201</v>
-      </c>
-      <c r="J91" s="8" t="n">
-        <v>201</v>
+      <c r="I91" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="J91" s="8" t="s">
+        <v>279</v>
       </c>
       <c r="K91" s="8" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="L91" s="8" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="M91" s="8" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="N91" s="8" t="s">
         <v>25</v>
@@ -5093,19 +5010,39 @@
       <c r="AN91" s="8"/>
     </row>
     <row r="92" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B92" s="49"/>
-      <c r="C92" s="3"/>
-      <c r="D92" s="4"/>
+      <c r="B92" s="86"/>
+      <c r="C92" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D92" s="4" t="n">
+        <v>123</v>
+      </c>
       <c r="E92" s="5"/>
       <c r="F92" s="6"/>
-      <c r="G92" s="7"/>
-      <c r="H92" s="8"/>
-      <c r="I92" s="9"/>
-      <c r="J92" s="8"/>
-      <c r="K92" s="8"/>
-      <c r="L92" s="8"/>
-      <c r="M92" s="8"/>
-      <c r="N92" s="8"/>
+      <c r="G92" s="7" t="n">
+        <v>123</v>
+      </c>
+      <c r="H92" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I92" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="J92" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="K92" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="L92" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="M92" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="N92" s="8" t="s">
+        <v>25</v>
+      </c>
       <c r="O92" s="8"/>
       <c r="P92" s="8"/>
       <c r="Q92" s="8"/>
@@ -5134,37 +5071,39 @@
       <c r="AN92" s="8"/>
     </row>
     <row r="93" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B93" s="49" t="s">
-        <v>276</v>
-      </c>
-      <c r="C93" s="87" t="s">
-        <v>281</v>
-      </c>
-      <c r="D93" s="4" t="s">
-        <v>17</v>
+      <c r="B93" s="86"/>
+      <c r="C93" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="D93" s="4" t="n">
+        <v>121</v>
       </c>
       <c r="E93" s="5"/>
       <c r="F93" s="6"/>
       <c r="G93" s="7" t="n">
-        <v>202</v>
+        <v>121</v>
       </c>
       <c r="H93" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="I93" s="9" t="n">
-        <v>202</v>
-      </c>
-      <c r="J93" s="8" t="n">
-        <v>202</v>
-      </c>
-      <c r="K93" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="L93" s="8" t="s">
+      <c r="I93" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="J93" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="K93" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="L93" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="M93" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="N93" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="M93" s="8"/>
-      <c r="N93" s="8"/>
       <c r="O93" s="8"/>
       <c r="P93" s="8"/>
       <c r="Q93" s="8"/>
@@ -5193,19 +5132,39 @@
       <c r="AN93" s="8"/>
     </row>
     <row r="94" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B94" s="49"/>
-      <c r="C94" s="87"/>
-      <c r="D94" s="4"/>
+      <c r="B94" s="86"/>
+      <c r="C94" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="D94" s="4" t="n">
+        <v>120</v>
+      </c>
       <c r="E94" s="5"/>
       <c r="F94" s="6"/>
-      <c r="G94" s="7"/>
-      <c r="H94" s="8"/>
-      <c r="I94" s="9"/>
-      <c r="J94" s="8"/>
-      <c r="K94" s="8"/>
-      <c r="L94" s="8"/>
-      <c r="M94" s="8"/>
-      <c r="N94" s="8"/>
+      <c r="G94" s="7" t="n">
+        <v>120</v>
+      </c>
+      <c r="H94" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I94" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="J94" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="K94" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="L94" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="M94" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="N94" s="8" t="s">
+        <v>25</v>
+      </c>
       <c r="O94" s="8"/>
       <c r="P94" s="8"/>
       <c r="Q94" s="8"/>
@@ -5234,47 +5193,21 @@
       <c r="AN94" s="8"/>
     </row>
     <row r="95" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B95" s="49" t="s">
-        <v>282</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="D95" s="88" t="n">
-        <v>126</v>
-      </c>
+      <c r="B95" s="49"/>
+      <c r="C95" s="3"/>
+      <c r="D95" s="4"/>
       <c r="E95" s="5"/>
       <c r="F95" s="6"/>
-      <c r="G95" s="7" t="n">
-        <v>203</v>
-      </c>
-      <c r="H95" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="I95" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="J95" s="8" t="s">
-        <v>285</v>
-      </c>
-      <c r="K95" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="L95" s="8" t="n">
-        <v>126</v>
-      </c>
-      <c r="M95" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="N95" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="O95" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="P95" s="8" t="s">
-        <v>25</v>
-      </c>
+      <c r="G95" s="7"/>
+      <c r="H95" s="8"/>
+      <c r="I95" s="9"/>
+      <c r="J95" s="8"/>
+      <c r="K95" s="8"/>
+      <c r="L95" s="8"/>
+      <c r="M95" s="8"/>
+      <c r="N95" s="8"/>
+      <c r="O95" s="8"/>
+      <c r="P95" s="8"/>
       <c r="Q95" s="8"/>
       <c r="R95" s="8"/>
       <c r="S95" s="8"/>
@@ -5301,45 +5234,43 @@
       <c r="AN95" s="8"/>
     </row>
     <row r="96" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B96" s="49"/>
+      <c r="B96" s="49" t="s">
+        <v>288</v>
+      </c>
       <c r="C96" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="D96" s="88" t="n">
-        <v>123</v>
+        <v>289</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="E96" s="5"/>
       <c r="F96" s="6"/>
       <c r="G96" s="7" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H96" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="I96" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="J96" s="8" t="s">
-        <v>285</v>
+        <v>5</v>
+      </c>
+      <c r="I96" s="9" t="n">
+        <v>201</v>
+      </c>
+      <c r="J96" s="8" t="n">
+        <v>201</v>
       </c>
       <c r="K96" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="L96" s="8" t="n">
-        <v>123</v>
+        <v>290</v>
+      </c>
+      <c r="L96" s="8" t="s">
+        <v>291</v>
       </c>
       <c r="M96" s="8" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="N96" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="O96" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="P96" s="8" t="s">
         <v>25</v>
       </c>
+      <c r="O96" s="8"/>
+      <c r="P96" s="8"/>
       <c r="Q96" s="8"/>
       <c r="R96" s="8"/>
       <c r="S96" s="8"/>
@@ -5367,44 +5298,20 @@
     </row>
     <row r="97" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B97" s="49"/>
-      <c r="C97" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="D97" s="88" t="n">
-        <v>121</v>
-      </c>
+      <c r="C97" s="3"/>
+      <c r="D97" s="4"/>
       <c r="E97" s="5"/>
       <c r="F97" s="6"/>
-      <c r="G97" s="7" t="n">
-        <v>203</v>
-      </c>
-      <c r="H97" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="I97" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="J97" s="8" t="s">
-        <v>285</v>
-      </c>
-      <c r="K97" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="L97" s="8" t="n">
-        <v>121</v>
-      </c>
-      <c r="M97" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="N97" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="O97" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="P97" s="8" t="s">
-        <v>25</v>
-      </c>
+      <c r="G97" s="7"/>
+      <c r="H97" s="8"/>
+      <c r="I97" s="9"/>
+      <c r="J97" s="8"/>
+      <c r="K97" s="8"/>
+      <c r="L97" s="8"/>
+      <c r="M97" s="8"/>
+      <c r="N97" s="8"/>
+      <c r="O97" s="8"/>
+      <c r="P97" s="8"/>
       <c r="Q97" s="8"/>
       <c r="R97" s="8"/>
       <c r="S97" s="8"/>
@@ -5431,45 +5338,39 @@
       <c r="AN97" s="8"/>
     </row>
     <row r="98" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B98" s="49"/>
-      <c r="C98" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="D98" s="88" t="n">
-        <v>120</v>
+      <c r="B98" s="49" t="s">
+        <v>288</v>
+      </c>
+      <c r="C98" s="87" t="s">
+        <v>293</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="E98" s="5"/>
       <c r="F98" s="6"/>
       <c r="G98" s="7" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H98" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="I98" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="J98" s="8" t="s">
-        <v>285</v>
-      </c>
-      <c r="K98" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="L98" s="8" t="n">
-        <v>120</v>
-      </c>
-      <c r="M98" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="N98" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="O98" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="P98" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I98" s="9" t="n">
+        <v>202</v>
+      </c>
+      <c r="J98" s="8" t="n">
+        <v>202</v>
+      </c>
+      <c r="K98" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L98" s="8" t="s">
         <v>25</v>
       </c>
+      <c r="M98" s="8"/>
+      <c r="N98" s="8"/>
+      <c r="O98" s="8"/>
+      <c r="P98" s="8"/>
       <c r="Q98" s="8"/>
       <c r="R98" s="8"/>
       <c r="S98" s="8"/>
@@ -5497,8 +5398,8 @@
     </row>
     <row r="99" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B99" s="49"/>
-      <c r="C99" s="3"/>
-      <c r="D99" s="88"/>
+      <c r="C99" s="87"/>
+      <c r="D99" s="4"/>
       <c r="E99" s="5"/>
       <c r="F99" s="6"/>
       <c r="G99" s="7"/>
@@ -5536,95 +5437,398 @@
       <c r="AM99" s="8"/>
       <c r="AN99" s="8"/>
     </row>
-    <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C101" s="89" t="s">
-        <v>293</v>
-      </c>
-      <c r="D101" s="90" t="s">
+    <row r="100" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B100" s="49" t="s">
         <v>294</v>
       </c>
-      <c r="E101" s="91"/>
-      <c r="F101" s="92" t="s">
+      <c r="C100" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="G101" s="56"/>
-    </row>
-    <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B102" s="93" t="s">
+      <c r="D100" s="88" t="n">
+        <v>126</v>
+      </c>
+      <c r="E100" s="5"/>
+      <c r="F100" s="6"/>
+      <c r="G100" s="7" t="n">
+        <v>203</v>
+      </c>
+      <c r="H100" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="I100" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J100" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="K100" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="L100" s="8" t="n">
+        <v>126</v>
+      </c>
+      <c r="M100" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="N100" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="O100" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="P100" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q100" s="8"/>
+      <c r="R100" s="8"/>
+      <c r="S100" s="8"/>
+      <c r="T100" s="8"/>
+      <c r="U100" s="8"/>
+      <c r="V100" s="8"/>
+      <c r="W100" s="8"/>
+      <c r="X100" s="8"/>
+      <c r="Y100" s="8"/>
+      <c r="Z100" s="8"/>
+      <c r="AA100" s="8"/>
+      <c r="AB100" s="8"/>
+      <c r="AC100" s="8"/>
+      <c r="AD100" s="8"/>
+      <c r="AE100" s="8"/>
+      <c r="AF100" s="8"/>
+      <c r="AG100" s="8"/>
+      <c r="AH100" s="8"/>
+      <c r="AI100" s="8"/>
+      <c r="AJ100" s="8"/>
+      <c r="AK100" s="8"/>
+      <c r="AL100" s="8"/>
+      <c r="AM100" s="8"/>
+      <c r="AN100" s="8"/>
+    </row>
+    <row r="101" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B101" s="49"/>
+      <c r="C101" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="D101" s="88" t="n">
+        <v>123</v>
+      </c>
+      <c r="E101" s="5"/>
+      <c r="F101" s="6"/>
+      <c r="G101" s="7" t="n">
+        <v>203</v>
+      </c>
+      <c r="H101" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="I101" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J101" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="K101" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="L101" s="8" t="n">
+        <v>123</v>
+      </c>
+      <c r="M101" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="N101" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="O101" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="P101" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q101" s="8"/>
+      <c r="R101" s="8"/>
+      <c r="S101" s="8"/>
+      <c r="T101" s="8"/>
+      <c r="U101" s="8"/>
+      <c r="V101" s="8"/>
+      <c r="W101" s="8"/>
+      <c r="X101" s="8"/>
+      <c r="Y101" s="8"/>
+      <c r="Z101" s="8"/>
+      <c r="AA101" s="8"/>
+      <c r="AB101" s="8"/>
+      <c r="AC101" s="8"/>
+      <c r="AD101" s="8"/>
+      <c r="AE101" s="8"/>
+      <c r="AF101" s="8"/>
+      <c r="AG101" s="8"/>
+      <c r="AH101" s="8"/>
+      <c r="AI101" s="8"/>
+      <c r="AJ101" s="8"/>
+      <c r="AK101" s="8"/>
+      <c r="AL101" s="8"/>
+      <c r="AM101" s="8"/>
+      <c r="AN101" s="8"/>
+    </row>
+    <row r="102" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B102" s="49"/>
+      <c r="C102" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="D102" s="88" t="n">
+        <v>121</v>
+      </c>
+      <c r="E102" s="5"/>
+      <c r="F102" s="6"/>
+      <c r="G102" s="7" t="n">
+        <v>203</v>
+      </c>
+      <c r="H102" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="I102" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J102" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="K102" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="L102" s="8" t="n">
+        <v>121</v>
+      </c>
+      <c r="M102" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="N102" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="O102" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="P102" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q102" s="8"/>
+      <c r="R102" s="8"/>
+      <c r="S102" s="8"/>
+      <c r="T102" s="8"/>
+      <c r="U102" s="8"/>
+      <c r="V102" s="8"/>
+      <c r="W102" s="8"/>
+      <c r="X102" s="8"/>
+      <c r="Y102" s="8"/>
+      <c r="Z102" s="8"/>
+      <c r="AA102" s="8"/>
+      <c r="AB102" s="8"/>
+      <c r="AC102" s="8"/>
+      <c r="AD102" s="8"/>
+      <c r="AE102" s="8"/>
+      <c r="AF102" s="8"/>
+      <c r="AG102" s="8"/>
+      <c r="AH102" s="8"/>
+      <c r="AI102" s="8"/>
+      <c r="AJ102" s="8"/>
+      <c r="AK102" s="8"/>
+      <c r="AL102" s="8"/>
+      <c r="AM102" s="8"/>
+      <c r="AN102" s="8"/>
+    </row>
+    <row r="103" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B103" s="49"/>
+      <c r="C103" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="D103" s="88" t="n">
+        <v>120</v>
+      </c>
+      <c r="E103" s="5"/>
+      <c r="F103" s="6"/>
+      <c r="G103" s="7" t="n">
+        <v>203</v>
+      </c>
+      <c r="H103" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="I103" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J103" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="K103" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="L103" s="8" t="n">
+        <v>120</v>
+      </c>
+      <c r="M103" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="N103" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="O103" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="P103" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q103" s="8"/>
+      <c r="R103" s="8"/>
+      <c r="S103" s="8"/>
+      <c r="T103" s="8"/>
+      <c r="U103" s="8"/>
+      <c r="V103" s="8"/>
+      <c r="W103" s="8"/>
+      <c r="X103" s="8"/>
+      <c r="Y103" s="8"/>
+      <c r="Z103" s="8"/>
+      <c r="AA103" s="8"/>
+      <c r="AB103" s="8"/>
+      <c r="AC103" s="8"/>
+      <c r="AD103" s="8"/>
+      <c r="AE103" s="8"/>
+      <c r="AF103" s="8"/>
+      <c r="AG103" s="8"/>
+      <c r="AH103" s="8"/>
+      <c r="AI103" s="8"/>
+      <c r="AJ103" s="8"/>
+      <c r="AK103" s="8"/>
+      <c r="AL103" s="8"/>
+      <c r="AM103" s="8"/>
+      <c r="AN103" s="8"/>
+    </row>
+    <row r="104" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B104" s="49"/>
+      <c r="C104" s="3"/>
+      <c r="D104" s="88"/>
+      <c r="E104" s="5"/>
+      <c r="F104" s="6"/>
+      <c r="G104" s="7"/>
+      <c r="H104" s="8"/>
+      <c r="I104" s="9"/>
+      <c r="J104" s="8"/>
+      <c r="K104" s="8"/>
+      <c r="L104" s="8"/>
+      <c r="M104" s="8"/>
+      <c r="N104" s="8"/>
+      <c r="O104" s="8"/>
+      <c r="P104" s="8"/>
+      <c r="Q104" s="8"/>
+      <c r="R104" s="8"/>
+      <c r="S104" s="8"/>
+      <c r="T104" s="8"/>
+      <c r="U104" s="8"/>
+      <c r="V104" s="8"/>
+      <c r="W104" s="8"/>
+      <c r="X104" s="8"/>
+      <c r="Y104" s="8"/>
+      <c r="Z104" s="8"/>
+      <c r="AA104" s="8"/>
+      <c r="AB104" s="8"/>
+      <c r="AC104" s="8"/>
+      <c r="AD104" s="8"/>
+      <c r="AE104" s="8"/>
+      <c r="AF104" s="8"/>
+      <c r="AG104" s="8"/>
+      <c r="AH104" s="8"/>
+      <c r="AI104" s="8"/>
+      <c r="AJ104" s="8"/>
+      <c r="AK104" s="8"/>
+      <c r="AL104" s="8"/>
+      <c r="AM104" s="8"/>
+      <c r="AN104" s="8"/>
+    </row>
+    <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C106" s="89" t="s">
+        <v>305</v>
+      </c>
+      <c r="D106" s="90" t="s">
+        <v>306</v>
+      </c>
+      <c r="E106" s="91"/>
+      <c r="F106" s="92" t="s">
+        <v>307</v>
+      </c>
+      <c r="G106" s="56"/>
+    </row>
+    <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B107" s="93" t="s">
         <v>15</v>
       </c>
-      <c r="C102" s="94" t="s">
-        <v>296</v>
-      </c>
-      <c r="D102" s="4" t="n">
+      <c r="C107" s="94" t="s">
+        <v>308</v>
+      </c>
+      <c r="D107" s="4" t="n">
         <v>254</v>
       </c>
-      <c r="E102" s="5" t="s">
+      <c r="E107" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F102" s="6" t="n">
+      <c r="F107" s="6" t="n">
         <v>253</v>
       </c>
-      <c r="G102" s="7" t="s">
+      <c r="G107" s="7" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B103" s="93"/>
-      <c r="C103" s="94"/>
-    </row>
-    <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B104" s="93" t="s">
+    <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B108" s="93"/>
+      <c r="C108" s="94"/>
+    </row>
+    <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B109" s="93" t="s">
         <v>59</v>
       </c>
-      <c r="C104" s="94" t="s">
-        <v>297</v>
-      </c>
-      <c r="D104" s="4" t="n">
+      <c r="C109" s="94" t="s">
+        <v>309</v>
+      </c>
+      <c r="D109" s="4" t="n">
         <v>239</v>
       </c>
-      <c r="E104" s="5" t="s">
+      <c r="E109" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="F104" s="6" t="n">
+      <c r="F109" s="6" t="n">
         <v>237</v>
       </c>
-      <c r="G104" s="7" t="s">
+      <c r="G109" s="7" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B105" s="93"/>
-      <c r="C105" s="94"/>
-    </row>
-    <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B106" s="93" t="s">
+    <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B110" s="93"/>
+      <c r="C110" s="94"/>
+    </row>
+    <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B111" s="93" t="s">
         <v>117</v>
       </c>
-      <c r="C106" s="94" t="s">
-        <v>298</v>
-      </c>
-      <c r="F106" s="6" t="n">
+      <c r="C111" s="94" t="s">
+        <v>310</v>
+      </c>
+      <c r="F111" s="6" t="n">
         <v>211</v>
       </c>
-      <c r="G106" s="7" t="s">
+      <c r="G111" s="7" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B107" s="93"/>
-      <c r="C107" s="94"/>
-    </row>
-    <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B108" s="93" t="s">
+    <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B112" s="93"/>
+      <c r="C112" s="94"/>
+    </row>
+    <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B113" s="93" t="s">
         <v>127</v>
       </c>
-      <c r="C108" s="94" t="s">
-        <v>299</v>
+      <c r="C113" s="94" t="s">
+        <v>311</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="19">
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="N5:O5"/>
@@ -5634,14 +5838,16 @@
     <mergeCell ref="I30:J30"/>
     <mergeCell ref="K30:L30"/>
     <mergeCell ref="M30:N30"/>
-    <mergeCell ref="I73:J73"/>
-    <mergeCell ref="K73:L73"/>
-    <mergeCell ref="M73:N73"/>
-    <mergeCell ref="O73:P73"/>
-    <mergeCell ref="R75:V75"/>
-    <mergeCell ref="R76:V76"/>
+    <mergeCell ref="R75:W75"/>
+    <mergeCell ref="R76:W76"/>
+    <mergeCell ref="R77:W77"/>
+    <mergeCell ref="I78:J78"/>
     <mergeCell ref="K78:L78"/>
     <mergeCell ref="M78:N78"/>
+    <mergeCell ref="O78:P78"/>
+    <mergeCell ref="R79:V79"/>
+    <mergeCell ref="K83:L83"/>
+    <mergeCell ref="M83:N83"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.708333333333333" right="0.708333333333333" top="0.747916666666667" bottom="0.747916666666667" header="0.511811023622047" footer="0.511811023622047"/>

--- a/PGN 5.7_planter.xlsx
+++ b/PGN 5.7_planter.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="316">
   <si>
     <t xml:space="preserve">PGN Name</t>
   </si>
@@ -622,6 +622,9 @@
     <t xml:space="preserve">Singulation1</t>
   </si>
   <si>
+    <t xml:space="preserve">CD</t>
+  </si>
+  <si>
     <t xml:space="preserve">Row 1</t>
   </si>
   <si>
@@ -655,6 +658,9 @@
     <t xml:space="preserve">Singulation2</t>
   </si>
   <si>
+    <t xml:space="preserve">CC</t>
+  </si>
+  <si>
     <t xml:space="preserve">Row 9</t>
   </si>
   <si>
@@ -682,6 +688,9 @@
     <t xml:space="preserve">Spacing by row1</t>
   </si>
   <si>
+    <t xml:space="preserve">CB</t>
+  </si>
+  <si>
     <t xml:space="preserve">0 to 255</t>
   </si>
   <si>
@@ -691,136 +700,139 @@
     <t xml:space="preserve">Spacing by row2</t>
   </si>
   <si>
+    <t xml:space="preserve">CA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ConfigB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Array Speed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Array Skips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 1-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 3-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 5-6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 7-8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 9-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 11-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 13-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 15-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">old, not used</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IP = 192.168.1.192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Array Doubles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hello = 9998?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 1-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 5-8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 9-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 13-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Port = 9998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PopulationD10 HI/Lo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SkipsPercX10 Hi/Lo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DoublesPercX10 Hi/Lo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SingulationPercX10 Hi/Lo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 to 7 per time array</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doubles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Population by row</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Config</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Num Sections (rows)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target SpeedX 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row Width X 10 Hi/Lo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target Population Hi/Lo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doubles Factor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Switch Control</t>
+  </si>
+  <si>
     <t xml:space="preserve">EA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ConfigB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Array Speed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Array Skips</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Row 1-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Row 3-4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Row 5-6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Row 7-8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Row 9-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Row 11-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Row 13-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Row 15-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">old, not used</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IP = 192.168.1.192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Array Doubles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hello = 9998?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Row Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Row 1-4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Row 5-8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Row 9-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Row 13-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Port = 9998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Summary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PopulationD10 HI/Lo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SkipsPercX10 Hi/Lo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DoublesPercX10 Hi/Lo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SingulationPercX10 Hi/Lo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skips</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 to 7 per time array</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Doubles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Population by row</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Config</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Num Sections (rows)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Target SpeedX 10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Row Width X 10 Hi/Lo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Target Population Hi/Lo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Doubles Factor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metric</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Switch Control</t>
   </si>
   <si>
     <t xml:space="preserve">Main</t>
@@ -3983,89 +3995,89 @@
       </c>
       <c r="E70" s="77"/>
       <c r="F70" s="6" t="s">
-        <v>103</v>
+        <v>199</v>
       </c>
       <c r="G70" s="7" t="n">
-        <v>237</v>
+        <v>205</v>
       </c>
       <c r="H70" s="78" t="n">
         <v>8</v>
       </c>
       <c r="I70" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J70" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K70" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L70" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M70" s="8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N70" s="8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O70" s="8" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P70" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q70" s="78" t="s">
         <v>25</v>
       </c>
       <c r="R70" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="S70" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="69"/>
       <c r="C71" s="76" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D71" s="4" t="s">
         <v>102</v>
       </c>
       <c r="E71" s="77"/>
       <c r="F71" s="6" t="s">
-        <v>81</v>
+        <v>211</v>
       </c>
       <c r="G71" s="7" t="n">
-        <v>236</v>
+        <v>204</v>
       </c>
       <c r="H71" s="78" t="n">
         <v>8</v>
       </c>
       <c r="I71" s="8" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="J71" s="8" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K71" s="8" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L71" s="8" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M71" s="8" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N71" s="8" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="O71" s="8" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q71" s="78" t="s">
         <v>25</v>
@@ -4074,96 +4086,96 @@
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="69"/>
       <c r="C72" s="76" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D72" s="4" t="s">
         <v>102</v>
       </c>
       <c r="E72" s="77"/>
       <c r="F72" s="6" t="s">
-        <v>83</v>
+        <v>221</v>
       </c>
       <c r="G72" s="7" t="n">
-        <v>235</v>
+        <v>203</v>
       </c>
       <c r="H72" s="78" t="n">
         <v>8</v>
       </c>
       <c r="I72" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J72" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K72" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L72" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M72" s="8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N72" s="8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O72" s="8" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P72" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q72" s="78" t="s">
         <v>25</v>
       </c>
       <c r="R72" s="10" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="S72" s="10" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="69"/>
       <c r="C73" s="76" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D73" s="4" t="s">
         <v>102</v>
       </c>
       <c r="E73" s="77"/>
       <c r="F73" s="6" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="G73" s="7" t="n">
-        <v>234</v>
+        <v>202</v>
       </c>
       <c r="H73" s="78" t="n">
         <v>8</v>
       </c>
       <c r="I73" s="8" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="J73" s="8" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K73" s="8" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L73" s="8" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M73" s="8" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N73" s="8" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="O73" s="8" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q73" s="78" t="s">
         <v>25</v>
@@ -4172,7 +4184,7 @@
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="69"/>
       <c r="C74" s="76" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D74" s="4" t="s">
         <v>102</v>
@@ -4188,7 +4200,7 @@
         <v>8</v>
       </c>
       <c r="I74" s="8" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="J74" s="8"/>
       <c r="K74" s="8"/>
@@ -4201,7 +4213,7 @@
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="69"/>
       <c r="C75" s="76" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D75" s="4" t="s">
         <v>102</v>
@@ -4217,43 +4229,48 @@
         <v>8</v>
       </c>
       <c r="I75" s="8" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="J75" s="8" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="K75" s="8" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="L75" s="8" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="M75" s="8" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="N75" s="8" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="O75" s="8" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q75" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="R75" s="10" t="s">
-        <v>234</v>
-      </c>
+      <c r="R75" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="S75" s="8"/>
+      <c r="T75" s="8"/>
+      <c r="U75" s="8"/>
+      <c r="V75" s="8"/>
+      <c r="W75" s="8"/>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="69"/>
       <c r="B76" s="49" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C76" s="76" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D76" s="4" t="s">
         <v>102</v>
@@ -4269,43 +4286,48 @@
         <v>8</v>
       </c>
       <c r="I76" s="8" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="J76" s="8" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="K76" s="8" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="L76" s="8" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="M76" s="8" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="N76" s="8" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="O76" s="8" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="P76" s="10" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q76" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="R76" s="10" t="s">
-        <v>234</v>
-      </c>
+      <c r="R76" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="S76" s="8"/>
+      <c r="T76" s="8"/>
+      <c r="U76" s="8"/>
+      <c r="V76" s="8"/>
+      <c r="W76" s="8"/>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="69"/>
       <c r="B77" s="49" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C77" s="76" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D77" s="4" t="s">
         <v>102</v>
@@ -4321,32 +4343,37 @@
         <v>8</v>
       </c>
       <c r="I77" s="8" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="J77" s="8" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="K77" s="8" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="L77" s="8" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="M77" s="8"/>
       <c r="N77" s="8"/>
       <c r="O77" s="8"/>
       <c r="Q77" s="78"/>
-      <c r="R77" s="10" t="s">
-        <v>234</v>
-      </c>
+      <c r="R77" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="S77" s="8"/>
+      <c r="T77" s="8"/>
+      <c r="U77" s="8"/>
+      <c r="V77" s="8"/>
+      <c r="W77" s="8"/>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="69"/>
       <c r="B78" s="49" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C78" s="76" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D78" s="4" t="s">
         <v>102</v>
@@ -4362,19 +4389,19 @@
         <v>8</v>
       </c>
       <c r="I78" s="79" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="J78" s="79"/>
       <c r="K78" s="8" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="L78" s="8"/>
       <c r="M78" s="8" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="N78" s="8"/>
       <c r="O78" s="8" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="P78" s="8"/>
       <c r="Q78" s="78"/>
@@ -4382,14 +4409,14 @@
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="69"/>
       <c r="C79" s="76" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>102</v>
       </c>
       <c r="E79" s="77"/>
       <c r="F79" s="6" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="G79" s="7" t="n">
         <v>228</v>
@@ -4398,34 +4425,34 @@
         <v>8</v>
       </c>
       <c r="I79" s="8" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="J79" s="8" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="K79" s="8" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="L79" s="8" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="M79" s="8" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="N79" s="8" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="O79" s="8" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q79" s="78" t="s">
         <v>25</v>
       </c>
       <c r="R79" s="8" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="S79" s="8"/>
       <c r="T79" s="8"/>
@@ -4435,14 +4462,14 @@
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="69"/>
       <c r="C80" s="76" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>102</v>
       </c>
       <c r="E80" s="77"/>
       <c r="F80" s="6" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G80" s="7" t="n">
         <v>227</v>
@@ -4451,28 +4478,28 @@
         <v>8</v>
       </c>
       <c r="I80" s="8" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="J80" s="8" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="K80" s="8" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="L80" s="8" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="M80" s="8" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="N80" s="8" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="O80" s="8" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="P80" s="10" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q80" s="78" t="s">
         <v>25</v>
@@ -4481,14 +4508,14 @@
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="69"/>
       <c r="C81" s="76" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>102</v>
       </c>
       <c r="E81" s="77"/>
       <c r="F81" s="6" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="G81" s="7" t="n">
         <v>226</v>
@@ -4497,28 +4524,28 @@
         <v>8</v>
       </c>
       <c r="I81" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J81" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K81" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L81" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M81" s="8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N81" s="8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O81" s="8" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q81" s="78" t="s">
         <v>25</v>
@@ -4527,14 +4554,14 @@
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="69"/>
       <c r="C82" s="76" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D82" s="4" t="s">
         <v>102</v>
       </c>
       <c r="E82" s="77"/>
       <c r="F82" s="6" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="G82" s="7" t="n">
         <v>225</v>
@@ -4543,28 +4570,28 @@
         <v>8</v>
       </c>
       <c r="I82" s="8" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="J82" s="8" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K82" s="8" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L82" s="8" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M82" s="8" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N82" s="8" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="O82" s="8" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="P82" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q82" s="78" t="s">
         <v>25</v>
@@ -4574,14 +4601,14 @@
       <c r="A83" s="80"/>
       <c r="B83" s="51"/>
       <c r="C83" s="81" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D83" s="53" t="s">
         <v>102</v>
       </c>
       <c r="E83" s="82"/>
       <c r="F83" s="55" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="G83" s="56" t="n">
         <v>224</v>
@@ -4590,24 +4617,24 @@
         <v>8</v>
       </c>
       <c r="I83" s="84" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="J83" s="84" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="K83" s="84" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="L83" s="84"/>
       <c r="M83" s="57" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="N83" s="57"/>
       <c r="O83" s="84" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="P83" s="57" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q83" s="83" t="s">
         <v>25</v>
@@ -4657,7 +4684,7 @@
     <row r="85" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B85" s="49"/>
       <c r="C85" s="3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D85" s="4" t="n">
         <v>77</v>
@@ -4666,35 +4693,35 @@
         <v>119</v>
       </c>
       <c r="F85" s="6" t="s">
-        <v>222</v>
+        <v>269</v>
       </c>
       <c r="G85" s="7" t="n">
         <v>234</v>
       </c>
       <c r="H85" s="8"/>
       <c r="I85" s="9" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="J85" s="8" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="K85" s="8" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="L85" s="8" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="M85" s="8" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="N85" s="8" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="O85" s="8" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="P85" s="8" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Q85" s="8" t="s">
         <v>25</v>
@@ -4848,10 +4875,10 @@
     </row>
     <row r="89" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B89" s="49" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D89" s="4" t="s">
         <v>17</v>
@@ -4865,7 +4892,7 @@
         <v>3</v>
       </c>
       <c r="I89" s="9" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="J89" s="8" t="n">
         <v>0</v>
@@ -4948,10 +4975,10 @@
     </row>
     <row r="91" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B91" s="49" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="D91" s="4" t="n">
         <v>126</v>
@@ -4965,19 +4992,19 @@
         <v>5</v>
       </c>
       <c r="I91" s="9" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="J91" s="8" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="K91" s="8" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="L91" s="8" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="M91" s="8" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="N91" s="8" t="s">
         <v>25</v>
@@ -5012,7 +5039,7 @@
     <row r="92" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B92" s="86"/>
       <c r="C92" s="3" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D92" s="4" t="n">
         <v>123</v>
@@ -5026,10 +5053,10 @@
         <v>5</v>
       </c>
       <c r="I92" s="9" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="J92" s="8" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="K92" s="8" t="s">
         <v>57</v>
@@ -5073,7 +5100,7 @@
     <row r="93" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B93" s="86"/>
       <c r="C93" s="3" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D93" s="4" t="n">
         <v>121</v>
@@ -5134,7 +5161,7 @@
     <row r="94" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B94" s="86"/>
       <c r="C94" s="3" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="D94" s="4" t="n">
         <v>120</v>
@@ -5235,10 +5262,10 @@
     </row>
     <row r="96" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B96" s="49" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="D96" s="4" t="s">
         <v>17</v>
@@ -5258,13 +5285,13 @@
         <v>201</v>
       </c>
       <c r="K96" s="8" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="L96" s="8" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="M96" s="8" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="N96" s="8" t="s">
         <v>25</v>
@@ -5339,10 +5366,10 @@
     </row>
     <row r="98" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B98" s="49" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C98" s="87" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D98" s="4" t="s">
         <v>17</v>
@@ -5439,10 +5466,10 @@
     </row>
     <row r="100" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B100" s="49" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="D100" s="88" t="n">
         <v>126</v>
@@ -5456,25 +5483,25 @@
         <v>7</v>
       </c>
       <c r="I100" s="9" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="J100" s="8" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="K100" s="8" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="L100" s="8" t="n">
         <v>126</v>
       </c>
       <c r="M100" s="8" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="N100" s="8" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="O100" s="8" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="P100" s="8" t="s">
         <v>25</v>
@@ -5507,7 +5534,7 @@
     <row r="101" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B101" s="49"/>
       <c r="C101" s="3" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="D101" s="88" t="n">
         <v>123</v>
@@ -5521,25 +5548,25 @@
         <v>7</v>
       </c>
       <c r="I101" s="9" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="J101" s="8" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="K101" s="8" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="L101" s="8" t="n">
         <v>123</v>
       </c>
       <c r="M101" s="8" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="N101" s="8" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="O101" s="8" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="P101" s="8" t="s">
         <v>25</v>
@@ -5572,7 +5599,7 @@
     <row r="102" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B102" s="49"/>
       <c r="C102" s="3" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="D102" s="88" t="n">
         <v>121</v>
@@ -5586,25 +5613,25 @@
         <v>7</v>
       </c>
       <c r="I102" s="9" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="J102" s="8" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="K102" s="8" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="L102" s="8" t="n">
         <v>121</v>
       </c>
       <c r="M102" s="8" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="N102" s="8" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="O102" s="8" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="P102" s="8" t="s">
         <v>25</v>
@@ -5637,7 +5664,7 @@
     <row r="103" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B103" s="49"/>
       <c r="C103" s="3" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="D103" s="88" t="n">
         <v>120</v>
@@ -5651,25 +5678,25 @@
         <v>7</v>
       </c>
       <c r="I103" s="9" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="J103" s="8" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="K103" s="8" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="L103" s="8" t="n">
         <v>120</v>
       </c>
       <c r="M103" s="8" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="N103" s="8" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="O103" s="8" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="P103" s="8" t="s">
         <v>25</v>
@@ -5742,14 +5769,14 @@
     </row>
     <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C106" s="89" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="D106" s="90" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="E106" s="91"/>
       <c r="F106" s="92" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="G106" s="56"/>
     </row>
@@ -5758,7 +5785,7 @@
         <v>15</v>
       </c>
       <c r="C107" s="94" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="D107" s="4" t="n">
         <v>254</v>
@@ -5782,7 +5809,7 @@
         <v>59</v>
       </c>
       <c r="C109" s="94" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="D109" s="4" t="n">
         <v>239</v>
@@ -5806,7 +5833,7 @@
         <v>117</v>
       </c>
       <c r="C111" s="94" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>211</v>
@@ -5824,7 +5851,7 @@
         <v>127</v>
       </c>
       <c r="C113" s="94" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>

--- a/PGN 5.7_planter.xlsx
+++ b/PGN 5.7_planter.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -981,7 +981,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1050,6 +1050,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF444444"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF999999"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
@@ -1323,7 +1330,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="99">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1640,6 +1647,22 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1684,15 +1707,15 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="3" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="3" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="2" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="2" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="3" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="3" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1764,7 +1787,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF999999"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
@@ -4212,7 +4235,7 @@
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="69"/>
-      <c r="C75" s="76" t="s">
+      <c r="C75" s="79" t="s">
         <v>228</v>
       </c>
       <c r="D75" s="4" t="s">
@@ -4225,51 +4248,51 @@
       <c r="G75" s="7" t="n">
         <v>232</v>
       </c>
-      <c r="H75" s="78" t="n">
+      <c r="H75" s="80" t="n">
         <v>8</v>
       </c>
-      <c r="I75" s="8" t="s">
+      <c r="I75" s="81" t="s">
         <v>229</v>
       </c>
-      <c r="J75" s="8" t="s">
+      <c r="J75" s="81" t="s">
         <v>230</v>
       </c>
-      <c r="K75" s="8" t="s">
+      <c r="K75" s="81" t="s">
         <v>231</v>
       </c>
-      <c r="L75" s="8" t="s">
+      <c r="L75" s="81" t="s">
         <v>232</v>
       </c>
-      <c r="M75" s="8" t="s">
+      <c r="M75" s="81" t="s">
         <v>233</v>
       </c>
-      <c r="N75" s="8" t="s">
+      <c r="N75" s="81" t="s">
         <v>234</v>
       </c>
-      <c r="O75" s="8" t="s">
+      <c r="O75" s="81" t="s">
         <v>235</v>
       </c>
-      <c r="P75" s="10" t="s">
+      <c r="P75" s="82" t="s">
         <v>236</v>
       </c>
-      <c r="Q75" s="78" t="s">
+      <c r="Q75" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="R75" s="8" t="s">
+      <c r="R75" s="81" t="s">
         <v>237</v>
       </c>
-      <c r="S75" s="8"/>
-      <c r="T75" s="8"/>
-      <c r="U75" s="8"/>
-      <c r="V75" s="8"/>
-      <c r="W75" s="8"/>
+      <c r="S75" s="81"/>
+      <c r="T75" s="81"/>
+      <c r="U75" s="81"/>
+      <c r="V75" s="81"/>
+      <c r="W75" s="81"/>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="69"/>
       <c r="B76" s="49" t="s">
         <v>238</v>
       </c>
-      <c r="C76" s="76" t="s">
+      <c r="C76" s="79" t="s">
         <v>239</v>
       </c>
       <c r="D76" s="4" t="s">
@@ -4282,51 +4305,51 @@
       <c r="G76" s="7" t="n">
         <v>231</v>
       </c>
-      <c r="H76" s="78" t="n">
+      <c r="H76" s="80" t="n">
         <v>8</v>
       </c>
-      <c r="I76" s="8" t="s">
+      <c r="I76" s="81" t="s">
         <v>229</v>
       </c>
-      <c r="J76" s="8" t="s">
+      <c r="J76" s="81" t="s">
         <v>230</v>
       </c>
-      <c r="K76" s="8" t="s">
+      <c r="K76" s="81" t="s">
         <v>231</v>
       </c>
-      <c r="L76" s="8" t="s">
+      <c r="L76" s="81" t="s">
         <v>232</v>
       </c>
-      <c r="M76" s="8" t="s">
+      <c r="M76" s="81" t="s">
         <v>233</v>
       </c>
-      <c r="N76" s="8" t="s">
+      <c r="N76" s="81" t="s">
         <v>234</v>
       </c>
-      <c r="O76" s="8" t="s">
+      <c r="O76" s="81" t="s">
         <v>235</v>
       </c>
-      <c r="P76" s="10" t="s">
+      <c r="P76" s="82" t="s">
         <v>236</v>
       </c>
-      <c r="Q76" s="78" t="s">
+      <c r="Q76" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="R76" s="8" t="s">
+      <c r="R76" s="81" t="s">
         <v>237</v>
       </c>
-      <c r="S76" s="8"/>
-      <c r="T76" s="8"/>
-      <c r="U76" s="8"/>
-      <c r="V76" s="8"/>
-      <c r="W76" s="8"/>
+      <c r="S76" s="81"/>
+      <c r="T76" s="81"/>
+      <c r="U76" s="81"/>
+      <c r="V76" s="81"/>
+      <c r="W76" s="81"/>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="69"/>
       <c r="B77" s="49" t="s">
         <v>240</v>
       </c>
-      <c r="C77" s="76" t="s">
+      <c r="C77" s="79" t="s">
         <v>241</v>
       </c>
       <c r="D77" s="4" t="s">
@@ -4339,33 +4362,34 @@
       <c r="G77" s="7" t="n">
         <v>230</v>
       </c>
-      <c r="H77" s="78" t="n">
+      <c r="H77" s="80" t="n">
         <v>8</v>
       </c>
-      <c r="I77" s="8" t="s">
+      <c r="I77" s="81" t="s">
         <v>242</v>
       </c>
-      <c r="J77" s="8" t="s">
+      <c r="J77" s="81" t="s">
         <v>243</v>
       </c>
-      <c r="K77" s="8" t="s">
+      <c r="K77" s="81" t="s">
         <v>244</v>
       </c>
-      <c r="L77" s="8" t="s">
+      <c r="L77" s="81" t="s">
         <v>245</v>
       </c>
-      <c r="M77" s="8"/>
-      <c r="N77" s="8"/>
-      <c r="O77" s="8"/>
-      <c r="Q77" s="78"/>
-      <c r="R77" s="8" t="s">
+      <c r="M77" s="81"/>
+      <c r="N77" s="81"/>
+      <c r="O77" s="81"/>
+      <c r="P77" s="82"/>
+      <c r="Q77" s="80"/>
+      <c r="R77" s="81" t="s">
         <v>237</v>
       </c>
-      <c r="S77" s="8"/>
-      <c r="T77" s="8"/>
-      <c r="U77" s="8"/>
-      <c r="V77" s="8"/>
-      <c r="W77" s="8"/>
+      <c r="S77" s="81"/>
+      <c r="T77" s="81"/>
+      <c r="U77" s="81"/>
+      <c r="V77" s="81"/>
+      <c r="W77" s="81"/>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="69"/>
@@ -4388,10 +4412,10 @@
       <c r="H78" s="78" t="n">
         <v>8</v>
       </c>
-      <c r="I78" s="79" t="s">
+      <c r="I78" s="83" t="s">
         <v>248</v>
       </c>
-      <c r="J78" s="79"/>
+      <c r="J78" s="83"/>
       <c r="K78" s="8" t="s">
         <v>249</v>
       </c>
@@ -4598,50 +4622,50 @@
       </c>
     </row>
     <row r="83" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="80"/>
+      <c r="A83" s="84"/>
       <c r="B83" s="51"/>
-      <c r="C83" s="81" t="s">
+      <c r="C83" s="85" t="s">
         <v>260</v>
       </c>
       <c r="D83" s="53" t="s">
         <v>102</v>
       </c>
-      <c r="E83" s="82"/>
+      <c r="E83" s="86"/>
       <c r="F83" s="55" t="s">
         <v>261</v>
       </c>
       <c r="G83" s="56" t="n">
         <v>224</v>
       </c>
-      <c r="H83" s="83" t="n">
+      <c r="H83" s="87" t="n">
         <v>8</v>
       </c>
-      <c r="I83" s="84" t="s">
+      <c r="I83" s="88" t="s">
         <v>262</v>
       </c>
-      <c r="J83" s="84" t="s">
+      <c r="J83" s="88" t="s">
         <v>263</v>
       </c>
-      <c r="K83" s="84" t="s">
+      <c r="K83" s="88" t="s">
         <v>264</v>
       </c>
-      <c r="L83" s="84"/>
+      <c r="L83" s="88"/>
       <c r="M83" s="57" t="s">
         <v>265</v>
       </c>
       <c r="N83" s="57"/>
-      <c r="O83" s="84" t="s">
+      <c r="O83" s="88" t="s">
         <v>266</v>
       </c>
       <c r="P83" s="57" t="s">
         <v>267</v>
       </c>
-      <c r="Q83" s="83" t="s">
+      <c r="Q83" s="87" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="84" s="60" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B84" s="85"/>
+      <c r="B84" s="89"/>
       <c r="C84" s="62"/>
       <c r="D84" s="63"/>
       <c r="E84" s="64"/>
@@ -4933,7 +4957,7 @@
       <c r="AN89" s="8"/>
     </row>
     <row r="90" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B90" s="86"/>
+      <c r="B90" s="90"/>
       <c r="C90" s="3"/>
       <c r="D90" s="4"/>
       <c r="E90" s="5"/>
@@ -5037,7 +5061,7 @@
       <c r="AN91" s="8"/>
     </row>
     <row r="92" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B92" s="86"/>
+      <c r="B92" s="90"/>
       <c r="C92" s="3" t="s">
         <v>287</v>
       </c>
@@ -5098,7 +5122,7 @@
       <c r="AN92" s="8"/>
     </row>
     <row r="93" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B93" s="86"/>
+      <c r="B93" s="90"/>
       <c r="C93" s="3" t="s">
         <v>290</v>
       </c>
@@ -5159,7 +5183,7 @@
       <c r="AN93" s="8"/>
     </row>
     <row r="94" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B94" s="86"/>
+      <c r="B94" s="90"/>
       <c r="C94" s="3" t="s">
         <v>291</v>
       </c>
@@ -5368,7 +5392,7 @@
       <c r="B98" s="49" t="s">
         <v>292</v>
       </c>
-      <c r="C98" s="87" t="s">
+      <c r="C98" s="91" t="s">
         <v>297</v>
       </c>
       <c r="D98" s="4" t="s">
@@ -5425,7 +5449,7 @@
     </row>
     <row r="99" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B99" s="49"/>
-      <c r="C99" s="87"/>
+      <c r="C99" s="91"/>
       <c r="D99" s="4"/>
       <c r="E99" s="5"/>
       <c r="F99" s="6"/>
@@ -5471,7 +5495,7 @@
       <c r="C100" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="D100" s="88" t="n">
+      <c r="D100" s="92" t="n">
         <v>126</v>
       </c>
       <c r="E100" s="5"/>
@@ -5536,7 +5560,7 @@
       <c r="C101" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="D101" s="88" t="n">
+      <c r="D101" s="92" t="n">
         <v>123</v>
       </c>
       <c r="E101" s="5"/>
@@ -5601,7 +5625,7 @@
       <c r="C102" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="D102" s="88" t="n">
+      <c r="D102" s="92" t="n">
         <v>121</v>
       </c>
       <c r="E102" s="5"/>
@@ -5666,7 +5690,7 @@
       <c r="C103" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="D103" s="88" t="n">
+      <c r="D103" s="92" t="n">
         <v>120</v>
       </c>
       <c r="E103" s="5"/>
@@ -5729,7 +5753,7 @@
     <row r="104" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B104" s="49"/>
       <c r="C104" s="3"/>
-      <c r="D104" s="88"/>
+      <c r="D104" s="92"/>
       <c r="E104" s="5"/>
       <c r="F104" s="6"/>
       <c r="G104" s="7"/>
@@ -5768,23 +5792,23 @@
       <c r="AN104" s="8"/>
     </row>
     <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C106" s="89" t="s">
+      <c r="C106" s="93" t="s">
         <v>309</v>
       </c>
-      <c r="D106" s="90" t="s">
+      <c r="D106" s="94" t="s">
         <v>310</v>
       </c>
-      <c r="E106" s="91"/>
-      <c r="F106" s="92" t="s">
+      <c r="E106" s="95"/>
+      <c r="F106" s="96" t="s">
         <v>311</v>
       </c>
       <c r="G106" s="56"/>
     </row>
     <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B107" s="93" t="s">
+      <c r="B107" s="97" t="s">
         <v>15</v>
       </c>
-      <c r="C107" s="94" t="s">
+      <c r="C107" s="98" t="s">
         <v>312</v>
       </c>
       <c r="D107" s="4" t="n">
@@ -5801,14 +5825,14 @@
       </c>
     </row>
     <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B108" s="93"/>
-      <c r="C108" s="94"/>
+      <c r="B108" s="97"/>
+      <c r="C108" s="98"/>
     </row>
     <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B109" s="93" t="s">
+      <c r="B109" s="97" t="s">
         <v>59</v>
       </c>
-      <c r="C109" s="94" t="s">
+      <c r="C109" s="98" t="s">
         <v>313</v>
       </c>
       <c r="D109" s="4" t="n">
@@ -5825,14 +5849,14 @@
       </c>
     </row>
     <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B110" s="93"/>
-      <c r="C110" s="94"/>
+      <c r="B110" s="97"/>
+      <c r="C110" s="98"/>
     </row>
     <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B111" s="93" t="s">
+      <c r="B111" s="97" t="s">
         <v>117</v>
       </c>
-      <c r="C111" s="94" t="s">
+      <c r="C111" s="98" t="s">
         <v>314</v>
       </c>
       <c r="F111" s="6" t="n">
@@ -5843,14 +5867,14 @@
       </c>
     </row>
     <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B112" s="93"/>
-      <c r="C112" s="94"/>
+      <c r="B112" s="97"/>
+      <c r="C112" s="98"/>
     </row>
     <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B113" s="93" t="s">
+      <c r="B113" s="97" t="s">
         <v>127</v>
       </c>
-      <c r="C113" s="94" t="s">
+      <c r="C113" s="98" t="s">
         <v>315</v>
       </c>
     </row>

--- a/PGN 5.7_planter.xlsx
+++ b/PGN 5.7_planter.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="319">
   <si>
     <t xml:space="preserve">PGN Name</t>
   </si>
@@ -761,6 +761,15 @@
   </si>
   <si>
     <t xml:space="preserve">Row 13-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sequence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On/Off 1-8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">on/Off 9-16</t>
   </si>
   <si>
     <t xml:space="preserve">Port = 9998</t>
@@ -981,7 +990,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1057,6 +1066,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF999999"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
@@ -1330,7 +1345,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="103">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1663,6 +1678,22 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1707,15 +1738,15 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="3" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="3" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="2" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="2" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="3" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="3" borderId="3" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4349,7 +4380,7 @@
       <c r="B77" s="49" t="s">
         <v>240</v>
       </c>
-      <c r="C77" s="79" t="s">
+      <c r="C77" s="83" t="s">
         <v>241</v>
       </c>
       <c r="D77" s="4" t="s">
@@ -4362,42 +4393,48 @@
       <c r="G77" s="7" t="n">
         <v>230</v>
       </c>
-      <c r="H77" s="80" t="n">
+      <c r="H77" s="84" t="n">
         <v>8</v>
       </c>
-      <c r="I77" s="81" t="s">
+      <c r="I77" s="85" t="s">
         <v>242</v>
       </c>
-      <c r="J77" s="81" t="s">
+      <c r="J77" s="85" t="s">
         <v>243</v>
       </c>
-      <c r="K77" s="81" t="s">
+      <c r="K77" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="L77" s="81" t="s">
+      <c r="L77" s="85" t="s">
         <v>245</v>
       </c>
-      <c r="M77" s="81"/>
-      <c r="N77" s="81"/>
-      <c r="O77" s="81"/>
-      <c r="P77" s="82"/>
-      <c r="Q77" s="80"/>
-      <c r="R77" s="81" t="s">
-        <v>237</v>
-      </c>
-      <c r="S77" s="81"/>
-      <c r="T77" s="81"/>
-      <c r="U77" s="81"/>
-      <c r="V77" s="81"/>
-      <c r="W77" s="81"/>
+      <c r="M77" s="85" t="s">
+        <v>246</v>
+      </c>
+      <c r="N77" s="85" t="s">
+        <v>247</v>
+      </c>
+      <c r="O77" s="85" t="s">
+        <v>248</v>
+      </c>
+      <c r="P77" s="86"/>
+      <c r="Q77" s="84" t="s">
+        <v>25</v>
+      </c>
+      <c r="R77" s="85"/>
+      <c r="S77" s="85"/>
+      <c r="T77" s="85"/>
+      <c r="U77" s="85"/>
+      <c r="V77" s="85"/>
+      <c r="W77" s="85"/>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="69"/>
       <c r="B78" s="49" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C78" s="76" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="D78" s="4" t="s">
         <v>102</v>
@@ -4412,35 +4449,37 @@
       <c r="H78" s="78" t="n">
         <v>8</v>
       </c>
-      <c r="I78" s="83" t="s">
-        <v>248</v>
-      </c>
-      <c r="J78" s="83"/>
+      <c r="I78" s="87" t="s">
+        <v>251</v>
+      </c>
+      <c r="J78" s="87"/>
       <c r="K78" s="8" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="L78" s="8"/>
       <c r="M78" s="8" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="N78" s="8"/>
       <c r="O78" s="8" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="P78" s="8"/>
-      <c r="Q78" s="78"/>
+      <c r="Q78" s="78" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="69"/>
       <c r="C79" s="76" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>102</v>
       </c>
       <c r="E79" s="77"/>
       <c r="F79" s="6" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G79" s="7" t="n">
         <v>228</v>
@@ -4476,7 +4515,7 @@
         <v>25</v>
       </c>
       <c r="R79" s="8" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="S79" s="8"/>
       <c r="T79" s="8"/>
@@ -4486,14 +4525,14 @@
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="69"/>
       <c r="C80" s="76" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>102</v>
       </c>
       <c r="E80" s="77"/>
       <c r="F80" s="6" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="G80" s="7" t="n">
         <v>227</v>
@@ -4532,14 +4571,14 @@
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="69"/>
       <c r="C81" s="76" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>102</v>
       </c>
       <c r="E81" s="77"/>
       <c r="F81" s="6" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="G81" s="7" t="n">
         <v>226</v>
@@ -4578,14 +4617,14 @@
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="69"/>
       <c r="C82" s="76" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D82" s="4" t="s">
         <v>102</v>
       </c>
       <c r="E82" s="77"/>
       <c r="F82" s="6" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="G82" s="7" t="n">
         <v>225</v>
@@ -4622,50 +4661,50 @@
       </c>
     </row>
     <row r="83" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="84"/>
+      <c r="A83" s="88"/>
       <c r="B83" s="51"/>
-      <c r="C83" s="85" t="s">
-        <v>260</v>
+      <c r="C83" s="89" t="s">
+        <v>263</v>
       </c>
       <c r="D83" s="53" t="s">
         <v>102</v>
       </c>
-      <c r="E83" s="86"/>
+      <c r="E83" s="90"/>
       <c r="F83" s="55" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="G83" s="56" t="n">
         <v>224</v>
       </c>
-      <c r="H83" s="87" t="n">
+      <c r="H83" s="91" t="n">
         <v>8</v>
       </c>
-      <c r="I83" s="88" t="s">
-        <v>262</v>
-      </c>
-      <c r="J83" s="88" t="s">
-        <v>263</v>
-      </c>
-      <c r="K83" s="88" t="s">
-        <v>264</v>
-      </c>
-      <c r="L83" s="88"/>
+      <c r="I83" s="92" t="s">
+        <v>265</v>
+      </c>
+      <c r="J83" s="92" t="s">
+        <v>266</v>
+      </c>
+      <c r="K83" s="92" t="s">
+        <v>267</v>
+      </c>
+      <c r="L83" s="92"/>
       <c r="M83" s="57" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="N83" s="57"/>
-      <c r="O83" s="88" t="s">
-        <v>266</v>
+      <c r="O83" s="92" t="s">
+        <v>269</v>
       </c>
       <c r="P83" s="57" t="s">
-        <v>267</v>
-      </c>
-      <c r="Q83" s="87" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q83" s="91" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="84" s="60" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B84" s="89"/>
+      <c r="B84" s="93"/>
       <c r="C84" s="62"/>
       <c r="D84" s="63"/>
       <c r="E84" s="64"/>
@@ -4708,7 +4747,7 @@
     <row r="85" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B85" s="49"/>
       <c r="C85" s="3" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="D85" s="4" t="n">
         <v>77</v>
@@ -4717,35 +4756,35 @@
         <v>119</v>
       </c>
       <c r="F85" s="6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="G85" s="7" t="n">
         <v>234</v>
       </c>
       <c r="H85" s="8"/>
       <c r="I85" s="9" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="J85" s="8" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="K85" s="8" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="L85" s="8" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="M85" s="8" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="N85" s="8" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="O85" s="8" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="P85" s="8" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q85" s="8" t="s">
         <v>25</v>
@@ -4899,10 +4938,10 @@
     </row>
     <row r="89" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B89" s="49" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D89" s="4" t="s">
         <v>17</v>
@@ -4916,7 +4955,7 @@
         <v>3</v>
       </c>
       <c r="I89" s="9" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="J89" s="8" t="n">
         <v>0</v>
@@ -4957,7 +4996,7 @@
       <c r="AN89" s="8"/>
     </row>
     <row r="90" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B90" s="90"/>
+      <c r="B90" s="94"/>
       <c r="C90" s="3"/>
       <c r="D90" s="4"/>
       <c r="E90" s="5"/>
@@ -4999,10 +5038,10 @@
     </row>
     <row r="91" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B91" s="49" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D91" s="4" t="n">
         <v>126</v>
@@ -5016,19 +5055,19 @@
         <v>5</v>
       </c>
       <c r="I91" s="9" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="J91" s="8" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="K91" s="8" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="L91" s="8" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="M91" s="8" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="N91" s="8" t="s">
         <v>25</v>
@@ -5061,9 +5100,9 @@
       <c r="AN91" s="8"/>
     </row>
     <row r="92" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B92" s="90"/>
+      <c r="B92" s="94"/>
       <c r="C92" s="3" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D92" s="4" t="n">
         <v>123</v>
@@ -5077,10 +5116,10 @@
         <v>5</v>
       </c>
       <c r="I92" s="9" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="J92" s="8" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="K92" s="8" t="s">
         <v>57</v>
@@ -5122,9 +5161,9 @@
       <c r="AN92" s="8"/>
     </row>
     <row r="93" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B93" s="90"/>
+      <c r="B93" s="94"/>
       <c r="C93" s="3" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="D93" s="4" t="n">
         <v>121</v>
@@ -5183,9 +5222,9 @@
       <c r="AN93" s="8"/>
     </row>
     <row r="94" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B94" s="90"/>
+      <c r="B94" s="94"/>
       <c r="C94" s="3" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="D94" s="4" t="n">
         <v>120</v>
@@ -5286,10 +5325,10 @@
     </row>
     <row r="96" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B96" s="49" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D96" s="4" t="s">
         <v>17</v>
@@ -5309,13 +5348,13 @@
         <v>201</v>
       </c>
       <c r="K96" s="8" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="L96" s="8" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="M96" s="8" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="N96" s="8" t="s">
         <v>25</v>
@@ -5390,10 +5429,10 @@
     </row>
     <row r="98" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B98" s="49" t="s">
-        <v>292</v>
-      </c>
-      <c r="C98" s="91" t="s">
-        <v>297</v>
+        <v>295</v>
+      </c>
+      <c r="C98" s="95" t="s">
+        <v>300</v>
       </c>
       <c r="D98" s="4" t="s">
         <v>17</v>
@@ -5449,7 +5488,7 @@
     </row>
     <row r="99" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B99" s="49"/>
-      <c r="C99" s="91"/>
+      <c r="C99" s="95"/>
       <c r="D99" s="4"/>
       <c r="E99" s="5"/>
       <c r="F99" s="6"/>
@@ -5490,12 +5529,12 @@
     </row>
     <row r="100" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B100" s="49" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="D100" s="92" t="n">
+        <v>302</v>
+      </c>
+      <c r="D100" s="96" t="n">
         <v>126</v>
       </c>
       <c r="E100" s="5"/>
@@ -5507,25 +5546,25 @@
         <v>7</v>
       </c>
       <c r="I100" s="9" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="J100" s="8" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K100" s="8" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="L100" s="8" t="n">
         <v>126</v>
       </c>
       <c r="M100" s="8" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="N100" s="8" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="O100" s="8" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="P100" s="8" t="s">
         <v>25</v>
@@ -5558,9 +5597,9 @@
     <row r="101" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B101" s="49"/>
       <c r="C101" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="D101" s="92" t="n">
+        <v>309</v>
+      </c>
+      <c r="D101" s="96" t="n">
         <v>123</v>
       </c>
       <c r="E101" s="5"/>
@@ -5572,25 +5611,25 @@
         <v>7</v>
       </c>
       <c r="I101" s="9" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="J101" s="8" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K101" s="8" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="L101" s="8" t="n">
         <v>123</v>
       </c>
       <c r="M101" s="8" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="N101" s="8" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="O101" s="8" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="P101" s="8" t="s">
         <v>25</v>
@@ -5623,9 +5662,9 @@
     <row r="102" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B102" s="49"/>
       <c r="C102" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="D102" s="92" t="n">
+        <v>310</v>
+      </c>
+      <c r="D102" s="96" t="n">
         <v>121</v>
       </c>
       <c r="E102" s="5"/>
@@ -5637,25 +5676,25 @@
         <v>7</v>
       </c>
       <c r="I102" s="9" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="J102" s="8" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K102" s="8" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="L102" s="8" t="n">
         <v>121</v>
       </c>
       <c r="M102" s="8" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="N102" s="8" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="O102" s="8" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="P102" s="8" t="s">
         <v>25</v>
@@ -5688,9 +5727,9 @@
     <row r="103" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B103" s="49"/>
       <c r="C103" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="D103" s="92" t="n">
+        <v>311</v>
+      </c>
+      <c r="D103" s="96" t="n">
         <v>120</v>
       </c>
       <c r="E103" s="5"/>
@@ -5702,25 +5741,25 @@
         <v>7</v>
       </c>
       <c r="I103" s="9" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="J103" s="8" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K103" s="8" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="L103" s="8" t="n">
         <v>120</v>
       </c>
       <c r="M103" s="8" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="N103" s="8" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="O103" s="8" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="P103" s="8" t="s">
         <v>25</v>
@@ -5753,7 +5792,7 @@
     <row r="104" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B104" s="49"/>
       <c r="C104" s="3"/>
-      <c r="D104" s="92"/>
+      <c r="D104" s="96"/>
       <c r="E104" s="5"/>
       <c r="F104" s="6"/>
       <c r="G104" s="7"/>
@@ -5792,24 +5831,24 @@
       <c r="AN104" s="8"/>
     </row>
     <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C106" s="93" t="s">
-        <v>309</v>
-      </c>
-      <c r="D106" s="94" t="s">
-        <v>310</v>
-      </c>
-      <c r="E106" s="95"/>
-      <c r="F106" s="96" t="s">
-        <v>311</v>
+      <c r="C106" s="97" t="s">
+        <v>312</v>
+      </c>
+      <c r="D106" s="98" t="s">
+        <v>313</v>
+      </c>
+      <c r="E106" s="99"/>
+      <c r="F106" s="100" t="s">
+        <v>314</v>
       </c>
       <c r="G106" s="56"/>
     </row>
     <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B107" s="97" t="s">
+      <c r="B107" s="101" t="s">
         <v>15</v>
       </c>
-      <c r="C107" s="98" t="s">
-        <v>312</v>
+      <c r="C107" s="102" t="s">
+        <v>315</v>
       </c>
       <c r="D107" s="4" t="n">
         <v>254</v>
@@ -5825,15 +5864,15 @@
       </c>
     </row>
     <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B108" s="97"/>
-      <c r="C108" s="98"/>
+      <c r="B108" s="101"/>
+      <c r="C108" s="102"/>
     </row>
     <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B109" s="97" t="s">
+      <c r="B109" s="101" t="s">
         <v>59</v>
       </c>
-      <c r="C109" s="98" t="s">
-        <v>313</v>
+      <c r="C109" s="102" t="s">
+        <v>316</v>
       </c>
       <c r="D109" s="4" t="n">
         <v>239</v>
@@ -5849,15 +5888,15 @@
       </c>
     </row>
     <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B110" s="97"/>
-      <c r="C110" s="98"/>
+      <c r="B110" s="101"/>
+      <c r="C110" s="102"/>
     </row>
     <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B111" s="97" t="s">
+      <c r="B111" s="101" t="s">
         <v>117</v>
       </c>
-      <c r="C111" s="98" t="s">
-        <v>314</v>
+      <c r="C111" s="102" t="s">
+        <v>317</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>211</v>
@@ -5867,15 +5906,15 @@
       </c>
     </row>
     <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B112" s="97"/>
-      <c r="C112" s="98"/>
+      <c r="B112" s="101"/>
+      <c r="C112" s="102"/>
     </row>
     <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B113" s="97" t="s">
+      <c r="B113" s="101" t="s">
         <v>127</v>
       </c>
-      <c r="C113" s="98" t="s">
-        <v>315</v>
+      <c r="C113" s="102" t="s">
+        <v>318</v>
       </c>
     </row>
   </sheetData>

--- a/PGN 5.7_planter.xlsx
+++ b/PGN 5.7_planter.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="320">
   <si>
     <t xml:space="preserve">PGN Name</t>
   </si>
@@ -770,6 +770,9 @@
   </si>
   <si>
     <t xml:space="preserve">on/Off 9-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On is 0, off is 1, for compatibility</t>
   </si>
   <si>
     <t xml:space="preserve">Port = 9998</t>
@@ -4421,7 +4424,9 @@
       <c r="Q77" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="R77" s="85"/>
+      <c r="R77" s="85" t="s">
+        <v>249</v>
+      </c>
       <c r="S77" s="85"/>
       <c r="T77" s="85"/>
       <c r="U77" s="85"/>
@@ -4431,10 +4436,10 @@
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="69"/>
       <c r="B78" s="49" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C78" s="76" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D78" s="4" t="s">
         <v>102</v>
@@ -4450,19 +4455,19 @@
         <v>8</v>
       </c>
       <c r="I78" s="87" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="J78" s="87"/>
       <c r="K78" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L78" s="8"/>
       <c r="M78" s="8" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N78" s="8"/>
       <c r="O78" s="8" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P78" s="8"/>
       <c r="Q78" s="78" t="s">
@@ -4472,14 +4477,14 @@
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="69"/>
       <c r="C79" s="76" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>102</v>
       </c>
       <c r="E79" s="77"/>
       <c r="F79" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G79" s="7" t="n">
         <v>228</v>
@@ -4515,7 +4520,7 @@
         <v>25</v>
       </c>
       <c r="R79" s="8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="S79" s="8"/>
       <c r="T79" s="8"/>
@@ -4525,14 +4530,14 @@
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="69"/>
       <c r="C80" s="76" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>102</v>
       </c>
       <c r="E80" s="77"/>
       <c r="F80" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G80" s="7" t="n">
         <v>227</v>
@@ -4571,14 +4576,14 @@
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="69"/>
       <c r="C81" s="76" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>102</v>
       </c>
       <c r="E81" s="77"/>
       <c r="F81" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G81" s="7" t="n">
         <v>226</v>
@@ -4617,14 +4622,14 @@
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="69"/>
       <c r="C82" s="76" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D82" s="4" t="s">
         <v>102</v>
       </c>
       <c r="E82" s="77"/>
       <c r="F82" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G82" s="7" t="n">
         <v>225</v>
@@ -4664,14 +4669,14 @@
       <c r="A83" s="88"/>
       <c r="B83" s="51"/>
       <c r="C83" s="89" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D83" s="53" t="s">
         <v>102</v>
       </c>
       <c r="E83" s="90"/>
       <c r="F83" s="55" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G83" s="56" t="n">
         <v>224</v>
@@ -4680,24 +4685,24 @@
         <v>8</v>
       </c>
       <c r="I83" s="92" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="J83" s="92" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K83" s="92" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L83" s="92"/>
       <c r="M83" s="57" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N83" s="57"/>
       <c r="O83" s="92" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P83" s="57" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q83" s="91" t="s">
         <v>25</v>
@@ -4747,7 +4752,7 @@
     <row r="85" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B85" s="49"/>
       <c r="C85" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D85" s="4" t="n">
         <v>77</v>
@@ -4756,35 +4761,35 @@
         <v>119</v>
       </c>
       <c r="F85" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G85" s="7" t="n">
         <v>234</v>
       </c>
       <c r="H85" s="8"/>
       <c r="I85" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J85" s="8" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K85" s="8" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L85" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M85" s="8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N85" s="8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O85" s="8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P85" s="8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q85" s="8" t="s">
         <v>25</v>
@@ -4938,10 +4943,10 @@
     </row>
     <row r="89" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B89" s="49" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D89" s="4" t="s">
         <v>17</v>
@@ -4955,7 +4960,7 @@
         <v>3</v>
       </c>
       <c r="I89" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J89" s="8" t="n">
         <v>0</v>
@@ -5038,10 +5043,10 @@
     </row>
     <row r="91" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B91" s="49" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D91" s="4" t="n">
         <v>126</v>
@@ -5055,19 +5060,19 @@
         <v>5</v>
       </c>
       <c r="I91" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="J91" s="8" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K91" s="8" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L91" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M91" s="8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N91" s="8" t="s">
         <v>25</v>
@@ -5102,7 +5107,7 @@
     <row r="92" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B92" s="94"/>
       <c r="C92" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D92" s="4" t="n">
         <v>123</v>
@@ -5116,10 +5121,10 @@
         <v>5</v>
       </c>
       <c r="I92" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="J92" s="8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K92" s="8" t="s">
         <v>57</v>
@@ -5163,7 +5168,7 @@
     <row r="93" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B93" s="94"/>
       <c r="C93" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D93" s="4" t="n">
         <v>121</v>
@@ -5224,7 +5229,7 @@
     <row r="94" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B94" s="94"/>
       <c r="C94" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D94" s="4" t="n">
         <v>120</v>
@@ -5325,10 +5330,10 @@
     </row>
     <row r="96" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B96" s="49" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D96" s="4" t="s">
         <v>17</v>
@@ -5348,13 +5353,13 @@
         <v>201</v>
       </c>
       <c r="K96" s="8" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L96" s="8" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M96" s="8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N96" s="8" t="s">
         <v>25</v>
@@ -5429,10 +5434,10 @@
     </row>
     <row r="98" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B98" s="49" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C98" s="95" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D98" s="4" t="s">
         <v>17</v>
@@ -5529,10 +5534,10 @@
     </row>
     <row r="100" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B100" s="49" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D100" s="96" t="n">
         <v>126</v>
@@ -5546,25 +5551,25 @@
         <v>7</v>
       </c>
       <c r="I100" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J100" s="8" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K100" s="8" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L100" s="8" t="n">
         <v>126</v>
       </c>
       <c r="M100" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N100" s="8" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O100" s="8" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P100" s="8" t="s">
         <v>25</v>
@@ -5597,7 +5602,7 @@
     <row r="101" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B101" s="49"/>
       <c r="C101" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D101" s="96" t="n">
         <v>123</v>
@@ -5611,25 +5616,25 @@
         <v>7</v>
       </c>
       <c r="I101" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J101" s="8" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K101" s="8" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L101" s="8" t="n">
         <v>123</v>
       </c>
       <c r="M101" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N101" s="8" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O101" s="8" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P101" s="8" t="s">
         <v>25</v>
@@ -5662,7 +5667,7 @@
     <row r="102" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B102" s="49"/>
       <c r="C102" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D102" s="96" t="n">
         <v>121</v>
@@ -5676,25 +5681,25 @@
         <v>7</v>
       </c>
       <c r="I102" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J102" s="8" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K102" s="8" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L102" s="8" t="n">
         <v>121</v>
       </c>
       <c r="M102" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N102" s="8" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O102" s="8" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P102" s="8" t="s">
         <v>25</v>
@@ -5727,7 +5732,7 @@
     <row r="103" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B103" s="49"/>
       <c r="C103" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D103" s="96" t="n">
         <v>120</v>
@@ -5741,25 +5746,25 @@
         <v>7</v>
       </c>
       <c r="I103" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J103" s="8" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K103" s="8" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L103" s="8" t="n">
         <v>120</v>
       </c>
       <c r="M103" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N103" s="8" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O103" s="8" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P103" s="8" t="s">
         <v>25</v>
@@ -5832,14 +5837,14 @@
     </row>
     <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C106" s="97" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D106" s="98" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E106" s="99"/>
       <c r="F106" s="100" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G106" s="56"/>
     </row>
@@ -5848,7 +5853,7 @@
         <v>15</v>
       </c>
       <c r="C107" s="102" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D107" s="4" t="n">
         <v>254</v>
@@ -5872,7 +5877,7 @@
         <v>59</v>
       </c>
       <c r="C109" s="102" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D109" s="4" t="n">
         <v>239</v>
@@ -5896,7 +5901,7 @@
         <v>117</v>
       </c>
       <c r="C111" s="102" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>211</v>
@@ -5914,7 +5919,7 @@
         <v>127</v>
       </c>
       <c r="C113" s="102" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
   </sheetData>

--- a/PGN 5.7_planter.xlsx
+++ b/PGN 5.7_planter.xlsx
@@ -11,7 +11,7 @@
     <sheet name="PGN" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">PGN!$A$1:$Q$114</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">PGN!$A$1:$Q$124</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="369">
   <si>
     <t xml:space="preserve">PGN Name</t>
   </si>
@@ -739,15 +739,9 @@
     <t xml:space="preserve">old, not used</t>
   </si>
   <si>
-    <t xml:space="preserve">IP = 192.168.1.192</t>
-  </si>
-  <si>
     <t xml:space="preserve">Array Doubles</t>
   </si>
   <si>
-    <t xml:space="preserve">Hello = 9998?</t>
-  </si>
-  <si>
     <t xml:space="preserve">Row Status</t>
   </si>
   <si>
@@ -775,9 +769,6 @@
     <t xml:space="preserve">On is 0, off is 1, for compatibility</t>
   </si>
   <si>
-    <t xml:space="preserve">Port = 9998</t>
-  </si>
-  <si>
     <t xml:space="preserve">Summary</t>
   </si>
   <si>
@@ -866,6 +857,162 @@
   </si>
   <si>
     <t xml:space="preserve">Off Group 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planter Comms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Height</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raw Hi/Lo 0-4095(0-12v)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Height 0-255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On threshold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Off threshold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Height config</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zero Hi/Lo 1-4095 0= no data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOP Hi/Lo 1-4095 0= no data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On threshold 0= no data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Off threshold 0= no data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vacuum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inWC1X10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inWC2X10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vacuum config</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zero1 Hi/Lo 1-4095 0= no data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zero2 Hi/Lo 1-4095 0= no data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Act inWCX10 0= no data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Downpressure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sen1 (kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sen2 (kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sen3 (kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">airDwPres PSI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">status bits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">status bit :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 israising</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 islowering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 pressSwt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 isAuto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Downpressure config</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Act weight(kg), 0 = no data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">set0,1=true,bit = sensNbr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Act PressPSI 0= no data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 raisePres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 lowerPres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fertilizer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(signed)weight (kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Act pos 1-8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Act pos 9-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set pos 1-8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set pos 9-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fertilizer config</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ForceOn 1-8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ForceOn 9-16</t>
   </si>
   <si>
     <t xml:space="preserve">Hello Sent To Module</t>
@@ -1348,7 +1495,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="117">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1723,6 +1870,62 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -2012,7 +2215,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:AP113"/>
+  <dimension ref="A1:AP123"/>
   <sheetFormatPr defaultColWidth="9.1484375" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.42"/>
@@ -2026,7 +2229,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="9" width="14.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="10" style="10" width="14.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="10" width="12.71"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="18" min="18" style="10" width="9.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="10" width="10.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="10" width="6.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="20" style="10" width="5.71"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="41" style="1" width="9.14"/>
@@ -4323,11 +4526,9 @@
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="69"/>
-      <c r="B76" s="49" t="s">
+      <c r="B76" s="49"/>
+      <c r="C76" s="79" t="s">
         <v>238</v>
-      </c>
-      <c r="C76" s="79" t="s">
-        <v>239</v>
       </c>
       <c r="D76" s="4" t="s">
         <v>102</v>
@@ -4380,11 +4581,9 @@
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="69"/>
-      <c r="B77" s="49" t="s">
-        <v>240</v>
-      </c>
+      <c r="B77" s="49"/>
       <c r="C77" s="83" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D77" s="4" t="s">
         <v>102</v>
@@ -4400,32 +4599,32 @@
         <v>8</v>
       </c>
       <c r="I77" s="85" t="s">
+        <v>240</v>
+      </c>
+      <c r="J77" s="85" t="s">
+        <v>241</v>
+      </c>
+      <c r="K77" s="85" t="s">
         <v>242</v>
       </c>
-      <c r="J77" s="85" t="s">
+      <c r="L77" s="85" t="s">
         <v>243</v>
       </c>
-      <c r="K77" s="85" t="s">
+      <c r="M77" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="L77" s="85" t="s">
+      <c r="N77" s="85" t="s">
         <v>245</v>
       </c>
-      <c r="M77" s="85" t="s">
+      <c r="O77" s="85" t="s">
         <v>246</v>
-      </c>
-      <c r="N77" s="85" t="s">
-        <v>247</v>
-      </c>
-      <c r="O77" s="85" t="s">
-        <v>248</v>
       </c>
       <c r="P77" s="86"/>
       <c r="Q77" s="84" t="s">
         <v>25</v>
       </c>
       <c r="R77" s="85" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="S77" s="85"/>
       <c r="T77" s="85"/>
@@ -4435,11 +4634,9 @@
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="69"/>
-      <c r="B78" s="49" t="s">
-        <v>250</v>
-      </c>
+      <c r="B78" s="49"/>
       <c r="C78" s="76" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D78" s="4" t="s">
         <v>102</v>
@@ -4455,19 +4652,19 @@
         <v>8</v>
       </c>
       <c r="I78" s="87" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="J78" s="87"/>
       <c r="K78" s="8" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="L78" s="8"/>
       <c r="M78" s="8" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="N78" s="8"/>
       <c r="O78" s="8" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="P78" s="8"/>
       <c r="Q78" s="78" t="s">
@@ -4477,14 +4674,14 @@
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="69"/>
       <c r="C79" s="76" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>102</v>
       </c>
       <c r="E79" s="77"/>
       <c r="F79" s="6" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="G79" s="7" t="n">
         <v>228</v>
@@ -4520,7 +4717,7 @@
         <v>25</v>
       </c>
       <c r="R79" s="8" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="S79" s="8"/>
       <c r="T79" s="8"/>
@@ -4530,14 +4727,14 @@
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="69"/>
       <c r="C80" s="76" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>102</v>
       </c>
       <c r="E80" s="77"/>
       <c r="F80" s="6" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="G80" s="7" t="n">
         <v>227</v>
@@ -4576,14 +4773,14 @@
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="69"/>
       <c r="C81" s="76" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>102</v>
       </c>
       <c r="E81" s="77"/>
       <c r="F81" s="6" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G81" s="7" t="n">
         <v>226</v>
@@ -4622,14 +4819,14 @@
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="69"/>
       <c r="C82" s="76" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D82" s="4" t="s">
         <v>102</v>
       </c>
       <c r="E82" s="77"/>
       <c r="F82" s="6" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="G82" s="7" t="n">
         <v>225</v>
@@ -4669,14 +4866,14 @@
       <c r="A83" s="88"/>
       <c r="B83" s="51"/>
       <c r="C83" s="89" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D83" s="53" t="s">
         <v>102</v>
       </c>
       <c r="E83" s="90"/>
       <c r="F83" s="55" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="G83" s="56" t="n">
         <v>224</v>
@@ -4685,24 +4882,24 @@
         <v>8</v>
       </c>
       <c r="I83" s="92" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="J83" s="92" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="K83" s="92" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="L83" s="92"/>
       <c r="M83" s="57" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="N83" s="57"/>
       <c r="O83" s="92" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="P83" s="57" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="Q83" s="91" t="s">
         <v>25</v>
@@ -4752,7 +4949,7 @@
     <row r="85" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B85" s="49"/>
       <c r="C85" s="3" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D85" s="4" t="n">
         <v>77</v>
@@ -4761,35 +4958,35 @@
         <v>119</v>
       </c>
       <c r="F85" s="6" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="G85" s="7" t="n">
         <v>234</v>
       </c>
       <c r="H85" s="8"/>
       <c r="I85" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="J85" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="K85" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="L85" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="M85" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="J85" s="8" t="s">
+      <c r="N85" s="8" t="s">
         <v>275</v>
       </c>
-      <c r="K85" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="L85" s="8" t="s">
+      <c r="O85" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="M85" s="8" t="s">
+      <c r="P85" s="8" t="s">
         <v>277</v>
-      </c>
-      <c r="N85" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="O85" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="P85" s="8" t="s">
-        <v>280</v>
       </c>
       <c r="Q85" s="8" t="s">
         <v>25</v>
@@ -4900,82 +5097,86 @@
       <c r="AM87" s="57"/>
       <c r="AN87" s="57"/>
     </row>
-    <row r="88" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B88" s="49"/>
-      <c r="C88" s="3"/>
-      <c r="D88" s="4"/>
-      <c r="E88" s="5"/>
-      <c r="F88" s="6"/>
-      <c r="G88" s="7"/>
-      <c r="H88" s="8"/>
-      <c r="I88" s="9"/>
-      <c r="J88" s="8"/>
-      <c r="K88" s="8"/>
-      <c r="L88" s="8"/>
-      <c r="M88" s="8"/>
-      <c r="N88" s="8"/>
-      <c r="O88" s="8"/>
-      <c r="P88" s="8"/>
-      <c r="Q88" s="8"/>
-      <c r="R88" s="8"/>
-      <c r="S88" s="8"/>
-      <c r="T88" s="8"/>
-      <c r="U88" s="8"/>
-      <c r="V88" s="8"/>
-      <c r="W88" s="8"/>
-      <c r="X88" s="8"/>
-      <c r="Y88" s="8"/>
-      <c r="Z88" s="8"/>
-      <c r="AA88" s="8"/>
-      <c r="AB88" s="8"/>
-      <c r="AC88" s="8"/>
-      <c r="AD88" s="8"/>
-      <c r="AE88" s="8"/>
-      <c r="AF88" s="8"/>
-      <c r="AG88" s="8"/>
-      <c r="AH88" s="8"/>
-      <c r="AI88" s="8"/>
-      <c r="AJ88" s="8"/>
-      <c r="AK88" s="8"/>
-      <c r="AL88" s="8"/>
-      <c r="AM88" s="8"/>
-      <c r="AN88" s="8"/>
+    <row r="88" s="50" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B88" s="94" t="s">
+        <v>278</v>
+      </c>
+      <c r="C88" s="52"/>
+      <c r="D88" s="53"/>
+      <c r="E88" s="54"/>
+      <c r="F88" s="55"/>
+      <c r="G88" s="56"/>
+      <c r="H88" s="57"/>
+      <c r="I88" s="58"/>
+      <c r="J88" s="57"/>
+      <c r="K88" s="57"/>
+      <c r="L88" s="57"/>
+      <c r="M88" s="57"/>
+      <c r="N88" s="57"/>
+      <c r="O88" s="57"/>
+      <c r="P88" s="57"/>
+      <c r="Q88" s="57"/>
+      <c r="R88" s="57"/>
+      <c r="S88" s="57"/>
+      <c r="T88" s="57"/>
+      <c r="U88" s="57"/>
+      <c r="V88" s="57"/>
+      <c r="W88" s="57"/>
+      <c r="X88" s="57"/>
+      <c r="Y88" s="57"/>
+      <c r="Z88" s="57"/>
+      <c r="AA88" s="57"/>
+      <c r="AB88" s="57"/>
+      <c r="AC88" s="57"/>
+      <c r="AD88" s="57"/>
+      <c r="AE88" s="57"/>
+      <c r="AF88" s="57"/>
+      <c r="AG88" s="57"/>
+      <c r="AH88" s="57"/>
+      <c r="AI88" s="57"/>
+      <c r="AJ88" s="57"/>
+      <c r="AK88" s="57"/>
+      <c r="AL88" s="57"/>
+      <c r="AM88" s="57"/>
+      <c r="AN88" s="57"/>
     </row>
     <row r="89" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B89" s="49" t="s">
+      <c r="B89" s="49"/>
+      <c r="C89" s="95" t="s">
+        <v>279</v>
+      </c>
+      <c r="D89" s="96" t="s">
+        <v>102</v>
+      </c>
+      <c r="E89" s="97"/>
+      <c r="F89" s="98" t="s">
+        <v>280</v>
+      </c>
+      <c r="G89" s="99" t="n">
+        <v>160</v>
+      </c>
+      <c r="H89" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="I89" s="100" t="s">
         <v>281</v>
       </c>
-      <c r="C89" s="3" t="s">
+      <c r="J89" s="100"/>
+      <c r="K89" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="D89" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E89" s="5"/>
-      <c r="F89" s="6"/>
-      <c r="G89" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="H89" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="I89" s="9" t="s">
+      <c r="L89" s="101"/>
+      <c r="M89" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="J89" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K89" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="M89" s="8"/>
-      <c r="N89" s="8"/>
+      <c r="N89" s="8" t="s">
+        <v>284</v>
+      </c>
       <c r="O89" s="8"/>
       <c r="P89" s="8"/>
-      <c r="Q89" s="8"/>
+      <c r="Q89" s="87" t="s">
+        <v>25</v>
+      </c>
       <c r="R89" s="8"/>
       <c r="S89" s="8"/>
       <c r="T89" s="8"/>
@@ -5000,23 +5201,43 @@
       <c r="AM89" s="8"/>
       <c r="AN89" s="8"/>
     </row>
-    <row r="90" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B90" s="94"/>
-      <c r="C90" s="3"/>
-      <c r="D90" s="4"/>
-      <c r="E90" s="5"/>
-      <c r="F90" s="6"/>
-      <c r="G90" s="7"/>
-      <c r="H90" s="8"/>
-      <c r="I90" s="9"/>
-      <c r="J90" s="8"/>
-      <c r="K90" s="8"/>
-      <c r="L90" s="8"/>
-      <c r="M90" s="8"/>
-      <c r="N90" s="8"/>
+    <row r="90" s="59" customFormat="true" ht="29.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B90" s="49"/>
+      <c r="C90" s="95" t="s">
+        <v>285</v>
+      </c>
+      <c r="D90" s="96" t="s">
+        <v>102</v>
+      </c>
+      <c r="E90" s="97"/>
+      <c r="F90" s="98" t="s">
+        <v>286</v>
+      </c>
+      <c r="G90" s="99" t="n">
+        <v>161</v>
+      </c>
+      <c r="H90" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="I90" s="100" t="s">
+        <v>287</v>
+      </c>
+      <c r="J90" s="100"/>
+      <c r="K90" s="100" t="s">
+        <v>288</v>
+      </c>
+      <c r="L90" s="100"/>
+      <c r="M90" s="102" t="s">
+        <v>289</v>
+      </c>
+      <c r="N90" s="102" t="s">
+        <v>290</v>
+      </c>
       <c r="O90" s="8"/>
       <c r="P90" s="8"/>
-      <c r="Q90" s="8"/>
+      <c r="Q90" s="87" t="s">
+        <v>25</v>
+      </c>
       <c r="R90" s="8"/>
       <c r="S90" s="8"/>
       <c r="T90" s="8"/>
@@ -5042,44 +5263,42 @@
       <c r="AN90" s="8"/>
     </row>
     <row r="91" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B91" s="49" t="s">
-        <v>284</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="D91" s="4" t="n">
-        <v>126</v>
-      </c>
-      <c r="E91" s="5"/>
-      <c r="F91" s="6"/>
-      <c r="G91" s="7" t="n">
-        <v>126</v>
+      <c r="B91" s="49"/>
+      <c r="C91" s="95" t="s">
+        <v>291</v>
+      </c>
+      <c r="D91" s="96" t="s">
+        <v>102</v>
+      </c>
+      <c r="E91" s="97"/>
+      <c r="F91" s="98" t="s">
+        <v>292</v>
+      </c>
+      <c r="G91" s="99" t="n">
+        <v>162</v>
       </c>
       <c r="H91" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="I91" s="9" t="s">
-        <v>286</v>
-      </c>
-      <c r="J91" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="K91" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="L91" s="8" t="s">
-        <v>289</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="I91" s="100" t="s">
+        <v>281</v>
+      </c>
+      <c r="J91" s="100"/>
+      <c r="K91" s="100" t="s">
+        <v>281</v>
+      </c>
+      <c r="L91" s="100"/>
       <c r="M91" s="8" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="N91" s="8" t="s">
-        <v>25</v>
+        <v>294</v>
       </c>
       <c r="O91" s="8"/>
       <c r="P91" s="8"/>
-      <c r="Q91" s="8"/>
+      <c r="Q91" s="87" t="s">
+        <v>25</v>
+      </c>
       <c r="R91" s="8"/>
       <c r="S91" s="8"/>
       <c r="T91" s="8"/>
@@ -5104,43 +5323,43 @@
       <c r="AM91" s="8"/>
       <c r="AN91" s="8"/>
     </row>
-    <row r="92" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B92" s="94"/>
-      <c r="C92" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="D92" s="4" t="n">
-        <v>123</v>
-      </c>
-      <c r="E92" s="5"/>
-      <c r="F92" s="6"/>
-      <c r="G92" s="7" t="n">
-        <v>123</v>
+    <row r="92" s="59" customFormat="true" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B92" s="49"/>
+      <c r="C92" s="95" t="s">
+        <v>295</v>
+      </c>
+      <c r="D92" s="96" t="s">
+        <v>102</v>
+      </c>
+      <c r="E92" s="97"/>
+      <c r="F92" s="98" t="s">
+        <v>296</v>
+      </c>
+      <c r="G92" s="99" t="n">
+        <v>163</v>
       </c>
       <c r="H92" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="I92" s="9" t="s">
-        <v>292</v>
-      </c>
-      <c r="J92" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="K92" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="L92" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="M92" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="N92" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="I92" s="100" t="s">
+        <v>297</v>
+      </c>
+      <c r="J92" s="100"/>
+      <c r="K92" s="100" t="s">
+        <v>298</v>
+      </c>
+      <c r="L92" s="100"/>
+      <c r="M92" s="103" t="s">
+        <v>299</v>
+      </c>
+      <c r="N92" s="103" t="s">
+        <v>299</v>
+      </c>
+      <c r="O92" s="100"/>
+      <c r="P92" s="8"/>
+      <c r="Q92" s="87" t="s">
         <v>25</v>
       </c>
-      <c r="O92" s="8"/>
-      <c r="P92" s="8"/>
-      <c r="Q92" s="8"/>
       <c r="R92" s="8"/>
       <c r="S92" s="8"/>
       <c r="T92" s="8"/>
@@ -5166,50 +5385,64 @@
       <c r="AN92" s="8"/>
     </row>
     <row r="93" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B93" s="94"/>
-      <c r="C93" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="D93" s="4" t="n">
-        <v>121</v>
-      </c>
-      <c r="E93" s="5"/>
-      <c r="F93" s="6"/>
-      <c r="G93" s="7" t="n">
-        <v>121</v>
+      <c r="B93" s="49"/>
+      <c r="C93" s="95" t="s">
+        <v>300</v>
+      </c>
+      <c r="D93" s="96" t="s">
+        <v>102</v>
+      </c>
+      <c r="E93" s="97"/>
+      <c r="F93" s="98" t="s">
+        <v>301</v>
+      </c>
+      <c r="G93" s="99" t="n">
+        <v>164</v>
       </c>
       <c r="H93" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I93" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="J93" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="K93" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="L93" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="M93" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="N93" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="J93" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="K93" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="L93" s="101"/>
+      <c r="M93" s="100" t="s">
+        <v>281</v>
+      </c>
+      <c r="N93" s="100"/>
+      <c r="O93" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="P93" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="Q93" s="87" t="s">
         <v>25</v>
       </c>
-      <c r="O93" s="8"/>
-      <c r="P93" s="8"/>
-      <c r="Q93" s="8"/>
-      <c r="R93" s="8"/>
-      <c r="S93" s="8"/>
-      <c r="T93" s="8"/>
-      <c r="U93" s="8"/>
+      <c r="R93" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="S93" s="87" t="s">
+        <v>308</v>
+      </c>
+      <c r="T93" s="87"/>
+      <c r="U93" s="8" t="s">
+        <v>309</v>
+      </c>
       <c r="V93" s="8"/>
-      <c r="W93" s="8"/>
+      <c r="W93" s="8" t="s">
+        <v>310</v>
+      </c>
       <c r="X93" s="8"/>
-      <c r="Y93" s="8"/>
+      <c r="Y93" s="8" t="s">
+        <v>311</v>
+      </c>
       <c r="Z93" s="8"/>
       <c r="AA93" s="8"/>
       <c r="AB93" s="8"/>
@@ -5226,52 +5459,66 @@
       <c r="AM93" s="8"/>
       <c r="AN93" s="8"/>
     </row>
-    <row r="94" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B94" s="94"/>
-      <c r="C94" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="D94" s="4" t="n">
-        <v>120</v>
-      </c>
-      <c r="E94" s="5"/>
-      <c r="F94" s="6"/>
-      <c r="G94" s="7" t="n">
-        <v>120</v>
+    <row r="94" s="59" customFormat="true" ht="30.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B94" s="49"/>
+      <c r="C94" s="104" t="s">
+        <v>312</v>
+      </c>
+      <c r="D94" s="96" t="s">
+        <v>102</v>
+      </c>
+      <c r="E94" s="97"/>
+      <c r="F94" s="98" t="s">
+        <v>313</v>
+      </c>
+      <c r="G94" s="99" t="n">
+        <v>165</v>
       </c>
       <c r="H94" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="I94" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="J94" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="K94" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="L94" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="M94" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="N94" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="I94" s="105" t="s">
+        <v>314</v>
+      </c>
+      <c r="J94" s="105" t="s">
+        <v>314</v>
+      </c>
+      <c r="K94" s="105" t="s">
+        <v>314</v>
+      </c>
+      <c r="L94" s="106" t="s">
+        <v>315</v>
+      </c>
+      <c r="M94" s="107" t="s">
+        <v>287</v>
+      </c>
+      <c r="N94" s="107"/>
+      <c r="O94" s="103" t="s">
+        <v>316</v>
+      </c>
+      <c r="P94" s="87" t="s">
+        <v>306</v>
+      </c>
+      <c r="Q94" s="87" t="s">
         <v>25</v>
       </c>
-      <c r="O94" s="8"/>
-      <c r="P94" s="8"/>
-      <c r="Q94" s="8"/>
-      <c r="R94" s="8"/>
-      <c r="S94" s="8"/>
-      <c r="T94" s="8"/>
-      <c r="U94" s="8"/>
-      <c r="V94" s="8"/>
-      <c r="W94" s="8"/>
-      <c r="X94" s="8"/>
-      <c r="Y94" s="8"/>
-      <c r="Z94" s="8"/>
+      <c r="R94" s="87" t="s">
+        <v>307</v>
+      </c>
+      <c r="S94" s="87" t="s">
+        <v>317</v>
+      </c>
+      <c r="T94" s="87"/>
+      <c r="U94" s="87" t="s">
+        <v>318</v>
+      </c>
+      <c r="V94" s="87"/>
+      <c r="W94" s="87"/>
+      <c r="X94" s="87"/>
+      <c r="Y94" s="87" t="s">
+        <v>311</v>
+      </c>
+      <c r="Z94" s="87"/>
       <c r="AA94" s="8"/>
       <c r="AB94" s="8"/>
       <c r="AC94" s="8"/>
@@ -5289,21 +5536,43 @@
     </row>
     <row r="95" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B95" s="49"/>
-      <c r="C95" s="3"/>
-      <c r="D95" s="4"/>
-      <c r="E95" s="5"/>
-      <c r="F95" s="6"/>
-      <c r="G95" s="7"/>
-      <c r="H95" s="8"/>
-      <c r="I95" s="9"/>
-      <c r="J95" s="8"/>
-      <c r="K95" s="8"/>
-      <c r="L95" s="8"/>
-      <c r="M95" s="8"/>
-      <c r="N95" s="8"/>
+      <c r="C95" s="95" t="s">
+        <v>319</v>
+      </c>
+      <c r="D95" s="96" t="s">
+        <v>102</v>
+      </c>
+      <c r="E95" s="97"/>
+      <c r="F95" s="98" t="s">
+        <v>320</v>
+      </c>
+      <c r="G95" s="99" t="n">
+        <v>166</v>
+      </c>
+      <c r="H95" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="I95" s="100" t="s">
+        <v>321</v>
+      </c>
+      <c r="J95" s="100"/>
+      <c r="K95" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="L95" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="M95" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="N95" s="8" t="s">
+        <v>325</v>
+      </c>
       <c r="O95" s="8"/>
       <c r="P95" s="8"/>
-      <c r="Q95" s="8"/>
+      <c r="Q95" s="87" t="s">
+        <v>25</v>
+      </c>
       <c r="R95" s="8"/>
       <c r="S95" s="8"/>
       <c r="T95" s="8"/>
@@ -5329,44 +5598,38 @@
       <c r="AN95" s="8"/>
     </row>
     <row r="96" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B96" s="49" t="s">
-        <v>296</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="D96" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E96" s="5"/>
-      <c r="F96" s="6"/>
-      <c r="G96" s="7" t="n">
-        <v>201</v>
+      <c r="B96" s="49"/>
+      <c r="C96" s="95" t="s">
+        <v>326</v>
+      </c>
+      <c r="D96" s="96" t="s">
+        <v>102</v>
+      </c>
+      <c r="E96" s="97"/>
+      <c r="F96" s="98" t="s">
+        <v>327</v>
+      </c>
+      <c r="G96" s="99" t="n">
+        <v>167</v>
       </c>
       <c r="H96" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="I96" s="9" t="n">
-        <v>201</v>
-      </c>
-      <c r="J96" s="8" t="n">
-        <v>201</v>
-      </c>
-      <c r="K96" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="L96" s="8" t="s">
-        <v>299</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="I96" s="9"/>
+      <c r="J96" s="8"/>
+      <c r="K96" s="101"/>
+      <c r="L96" s="101"/>
       <c r="M96" s="8" t="s">
-        <v>300</v>
+        <v>328</v>
       </c>
       <c r="N96" s="8" t="s">
-        <v>25</v>
+        <v>329</v>
       </c>
       <c r="O96" s="8"/>
       <c r="P96" s="8"/>
-      <c r="Q96" s="8"/>
+      <c r="Q96" s="87" t="s">
+        <v>25</v>
+      </c>
       <c r="R96" s="8"/>
       <c r="S96" s="8"/>
       <c r="T96" s="8"/>
@@ -5433,35 +5696,17 @@
       <c r="AN97" s="8"/>
     </row>
     <row r="98" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B98" s="49" t="s">
-        <v>296</v>
-      </c>
-      <c r="C98" s="95" t="s">
-        <v>301</v>
-      </c>
-      <c r="D98" s="4" t="s">
-        <v>17</v>
-      </c>
+      <c r="B98" s="49"/>
+      <c r="C98" s="3"/>
+      <c r="D98" s="4"/>
       <c r="E98" s="5"/>
       <c r="F98" s="6"/>
-      <c r="G98" s="7" t="n">
-        <v>202</v>
-      </c>
-      <c r="H98" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="I98" s="9" t="n">
-        <v>202</v>
-      </c>
-      <c r="J98" s="8" t="n">
-        <v>202</v>
-      </c>
-      <c r="K98" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="L98" s="8" t="s">
-        <v>25</v>
-      </c>
+      <c r="G98" s="7"/>
+      <c r="H98" s="8"/>
+      <c r="I98" s="9"/>
+      <c r="J98" s="8"/>
+      <c r="K98" s="8"/>
+      <c r="L98" s="8"/>
       <c r="M98" s="8"/>
       <c r="N98" s="8"/>
       <c r="O98" s="8"/>
@@ -5492,17 +5737,35 @@
       <c r="AN98" s="8"/>
     </row>
     <row r="99" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B99" s="49"/>
-      <c r="C99" s="95"/>
-      <c r="D99" s="4"/>
+      <c r="B99" s="49" t="s">
+        <v>330</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="E99" s="5"/>
       <c r="F99" s="6"/>
-      <c r="G99" s="7"/>
-      <c r="H99" s="8"/>
-      <c r="I99" s="9"/>
-      <c r="J99" s="8"/>
-      <c r="K99" s="8"/>
-      <c r="L99" s="8"/>
+      <c r="G99" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="H99" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I99" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="J99" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" s="8" t="s">
+        <v>25</v>
+      </c>
       <c r="M99" s="8"/>
       <c r="N99" s="8"/>
       <c r="O99" s="8"/>
@@ -5533,47 +5796,21 @@
       <c r="AN99" s="8"/>
     </row>
     <row r="100" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B100" s="49" t="s">
-        <v>302</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="D100" s="96" t="n">
-        <v>126</v>
-      </c>
+      <c r="B100" s="108"/>
+      <c r="C100" s="3"/>
+      <c r="D100" s="4"/>
       <c r="E100" s="5"/>
       <c r="F100" s="6"/>
-      <c r="G100" s="7" t="n">
-        <v>203</v>
-      </c>
-      <c r="H100" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="I100" s="9" t="s">
-        <v>304</v>
-      </c>
-      <c r="J100" s="8" t="s">
-        <v>305</v>
-      </c>
-      <c r="K100" s="8" t="s">
-        <v>306</v>
-      </c>
-      <c r="L100" s="8" t="n">
-        <v>126</v>
-      </c>
-      <c r="M100" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="N100" s="8" t="s">
-        <v>308</v>
-      </c>
-      <c r="O100" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="P100" s="8" t="s">
-        <v>25</v>
-      </c>
+      <c r="G100" s="7"/>
+      <c r="H100" s="8"/>
+      <c r="I100" s="9"/>
+      <c r="J100" s="8"/>
+      <c r="K100" s="8"/>
+      <c r="L100" s="8"/>
+      <c r="M100" s="8"/>
+      <c r="N100" s="8"/>
+      <c r="O100" s="8"/>
+      <c r="P100" s="8"/>
       <c r="Q100" s="8"/>
       <c r="R100" s="8"/>
       <c r="S100" s="8"/>
@@ -5600,45 +5837,43 @@
       <c r="AN100" s="8"/>
     </row>
     <row r="101" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B101" s="49"/>
+      <c r="B101" s="49" t="s">
+        <v>333</v>
+      </c>
       <c r="C101" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="D101" s="96" t="n">
-        <v>123</v>
+        <v>334</v>
+      </c>
+      <c r="D101" s="4" t="n">
+        <v>126</v>
       </c>
       <c r="E101" s="5"/>
       <c r="F101" s="6"/>
       <c r="G101" s="7" t="n">
-        <v>203</v>
+        <v>126</v>
       </c>
       <c r="H101" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I101" s="9" t="s">
-        <v>304</v>
+        <v>335</v>
       </c>
       <c r="J101" s="8" t="s">
-        <v>305</v>
+        <v>336</v>
       </c>
       <c r="K101" s="8" t="s">
-        <v>306</v>
-      </c>
-      <c r="L101" s="8" t="n">
-        <v>123</v>
+        <v>337</v>
+      </c>
+      <c r="L101" s="8" t="s">
+        <v>338</v>
       </c>
       <c r="M101" s="8" t="s">
-        <v>307</v>
+        <v>339</v>
       </c>
       <c r="N101" s="8" t="s">
-        <v>308</v>
-      </c>
-      <c r="O101" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="P101" s="8" t="s">
         <v>25</v>
       </c>
+      <c r="O101" s="8"/>
+      <c r="P101" s="8"/>
       <c r="Q101" s="8"/>
       <c r="R101" s="8"/>
       <c r="S101" s="8"/>
@@ -5665,45 +5900,41 @@
       <c r="AN101" s="8"/>
     </row>
     <row r="102" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B102" s="49"/>
+      <c r="B102" s="108"/>
       <c r="C102" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="D102" s="96" t="n">
-        <v>121</v>
+        <v>340</v>
+      </c>
+      <c r="D102" s="4" t="n">
+        <v>123</v>
       </c>
       <c r="E102" s="5"/>
       <c r="F102" s="6"/>
       <c r="G102" s="7" t="n">
-        <v>203</v>
+        <v>123</v>
       </c>
       <c r="H102" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I102" s="9" t="s">
-        <v>304</v>
+        <v>341</v>
       </c>
       <c r="J102" s="8" t="s">
-        <v>305</v>
+        <v>342</v>
       </c>
       <c r="K102" s="8" t="s">
-        <v>306</v>
-      </c>
-      <c r="L102" s="8" t="n">
-        <v>121</v>
+        <v>57</v>
+      </c>
+      <c r="L102" s="8" t="s">
+        <v>57</v>
       </c>
       <c r="M102" s="8" t="s">
-        <v>307</v>
+        <v>57</v>
       </c>
       <c r="N102" s="8" t="s">
-        <v>308</v>
-      </c>
-      <c r="O102" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="P102" s="8" t="s">
         <v>25</v>
       </c>
+      <c r="O102" s="8"/>
+      <c r="P102" s="8"/>
       <c r="Q102" s="8"/>
       <c r="R102" s="8"/>
       <c r="S102" s="8"/>
@@ -5730,45 +5961,41 @@
       <c r="AN102" s="8"/>
     </row>
     <row r="103" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B103" s="49"/>
+      <c r="B103" s="108"/>
       <c r="C103" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="D103" s="96" t="n">
-        <v>120</v>
+        <v>343</v>
+      </c>
+      <c r="D103" s="4" t="n">
+        <v>121</v>
       </c>
       <c r="E103" s="5"/>
       <c r="F103" s="6"/>
       <c r="G103" s="7" t="n">
-        <v>203</v>
+        <v>121</v>
       </c>
       <c r="H103" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I103" s="9" t="s">
-        <v>304</v>
-      </c>
-      <c r="J103" s="8" t="s">
-        <v>305</v>
-      </c>
-      <c r="K103" s="8" t="s">
-        <v>306</v>
-      </c>
-      <c r="L103" s="8" t="n">
-        <v>120</v>
-      </c>
-      <c r="M103" s="8" t="s">
-        <v>307</v>
+        <v>57</v>
+      </c>
+      <c r="J103" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="K103" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="L103" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="M103" s="9" t="s">
+        <v>57</v>
       </c>
       <c r="N103" s="8" t="s">
-        <v>308</v>
-      </c>
-      <c r="O103" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="P103" s="8" t="s">
         <v>25</v>
       </c>
+      <c r="O103" s="8"/>
+      <c r="P103" s="8"/>
       <c r="Q103" s="8"/>
       <c r="R103" s="8"/>
       <c r="S103" s="8"/>
@@ -5795,19 +6022,39 @@
       <c r="AN103" s="8"/>
     </row>
     <row r="104" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B104" s="49"/>
-      <c r="C104" s="3"/>
-      <c r="D104" s="96"/>
+      <c r="B104" s="108"/>
+      <c r="C104" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="D104" s="4" t="n">
+        <v>120</v>
+      </c>
       <c r="E104" s="5"/>
       <c r="F104" s="6"/>
-      <c r="G104" s="7"/>
-      <c r="H104" s="8"/>
-      <c r="I104" s="9"/>
-      <c r="J104" s="8"/>
-      <c r="K104" s="8"/>
-      <c r="L104" s="8"/>
-      <c r="M104" s="8"/>
-      <c r="N104" s="8"/>
+      <c r="G104" s="7" t="n">
+        <v>120</v>
+      </c>
+      <c r="H104" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I104" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="J104" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="K104" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="L104" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="M104" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="N104" s="8" t="s">
+        <v>25</v>
+      </c>
       <c r="O104" s="8"/>
       <c r="P104" s="8"/>
       <c r="Q104" s="8"/>
@@ -5835,95 +6082,643 @@
       <c r="AM104" s="8"/>
       <c r="AN104" s="8"/>
     </row>
-    <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C106" s="97" t="s">
-        <v>313</v>
-      </c>
-      <c r="D106" s="98" t="s">
-        <v>314</v>
-      </c>
-      <c r="E106" s="99"/>
-      <c r="F106" s="100" t="s">
-        <v>315</v>
-      </c>
-      <c r="G106" s="56"/>
-    </row>
-    <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B107" s="101" t="s">
+    <row r="105" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B105" s="49"/>
+      <c r="C105" s="3"/>
+      <c r="D105" s="4"/>
+      <c r="E105" s="5"/>
+      <c r="F105" s="6"/>
+      <c r="G105" s="7"/>
+      <c r="H105" s="8"/>
+      <c r="I105" s="9"/>
+      <c r="J105" s="8"/>
+      <c r="K105" s="8"/>
+      <c r="L105" s="8"/>
+      <c r="M105" s="8"/>
+      <c r="N105" s="8"/>
+      <c r="O105" s="8"/>
+      <c r="P105" s="8"/>
+      <c r="Q105" s="8"/>
+      <c r="R105" s="8"/>
+      <c r="S105" s="8"/>
+      <c r="T105" s="8"/>
+      <c r="U105" s="8"/>
+      <c r="V105" s="8"/>
+      <c r="W105" s="8"/>
+      <c r="X105" s="8"/>
+      <c r="Y105" s="8"/>
+      <c r="Z105" s="8"/>
+      <c r="AA105" s="8"/>
+      <c r="AB105" s="8"/>
+      <c r="AC105" s="8"/>
+      <c r="AD105" s="8"/>
+      <c r="AE105" s="8"/>
+      <c r="AF105" s="8"/>
+      <c r="AG105" s="8"/>
+      <c r="AH105" s="8"/>
+      <c r="AI105" s="8"/>
+      <c r="AJ105" s="8"/>
+      <c r="AK105" s="8"/>
+      <c r="AL105" s="8"/>
+      <c r="AM105" s="8"/>
+      <c r="AN105" s="8"/>
+    </row>
+    <row r="106" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B106" s="49" t="s">
+        <v>345</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E106" s="5"/>
+      <c r="F106" s="6"/>
+      <c r="G106" s="7" t="n">
+        <v>201</v>
+      </c>
+      <c r="H106" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I106" s="9" t="n">
+        <v>201</v>
+      </c>
+      <c r="J106" s="8" t="n">
+        <v>201</v>
+      </c>
+      <c r="K106" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="L106" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="M106" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="N106" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="O106" s="8"/>
+      <c r="P106" s="8"/>
+      <c r="Q106" s="8"/>
+      <c r="R106" s="8"/>
+      <c r="S106" s="8"/>
+      <c r="T106" s="8"/>
+      <c r="U106" s="8"/>
+      <c r="V106" s="8"/>
+      <c r="W106" s="8"/>
+      <c r="X106" s="8"/>
+      <c r="Y106" s="8"/>
+      <c r="Z106" s="8"/>
+      <c r="AA106" s="8"/>
+      <c r="AB106" s="8"/>
+      <c r="AC106" s="8"/>
+      <c r="AD106" s="8"/>
+      <c r="AE106" s="8"/>
+      <c r="AF106" s="8"/>
+      <c r="AG106" s="8"/>
+      <c r="AH106" s="8"/>
+      <c r="AI106" s="8"/>
+      <c r="AJ106" s="8"/>
+      <c r="AK106" s="8"/>
+      <c r="AL106" s="8"/>
+      <c r="AM106" s="8"/>
+      <c r="AN106" s="8"/>
+    </row>
+    <row r="107" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B107" s="49"/>
+      <c r="C107" s="3"/>
+      <c r="D107" s="4"/>
+      <c r="E107" s="5"/>
+      <c r="F107" s="6"/>
+      <c r="G107" s="7"/>
+      <c r="H107" s="8"/>
+      <c r="I107" s="9"/>
+      <c r="J107" s="8"/>
+      <c r="K107" s="8"/>
+      <c r="L107" s="8"/>
+      <c r="M107" s="8"/>
+      <c r="N107" s="8"/>
+      <c r="O107" s="8"/>
+      <c r="P107" s="8"/>
+      <c r="Q107" s="8"/>
+      <c r="R107" s="8"/>
+      <c r="S107" s="8"/>
+      <c r="T107" s="8"/>
+      <c r="U107" s="8"/>
+      <c r="V107" s="8"/>
+      <c r="W107" s="8"/>
+      <c r="X107" s="8"/>
+      <c r="Y107" s="8"/>
+      <c r="Z107" s="8"/>
+      <c r="AA107" s="8"/>
+      <c r="AB107" s="8"/>
+      <c r="AC107" s="8"/>
+      <c r="AD107" s="8"/>
+      <c r="AE107" s="8"/>
+      <c r="AF107" s="8"/>
+      <c r="AG107" s="8"/>
+      <c r="AH107" s="8"/>
+      <c r="AI107" s="8"/>
+      <c r="AJ107" s="8"/>
+      <c r="AK107" s="8"/>
+      <c r="AL107" s="8"/>
+      <c r="AM107" s="8"/>
+      <c r="AN107" s="8"/>
+    </row>
+    <row r="108" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B108" s="49" t="s">
+        <v>345</v>
+      </c>
+      <c r="C108" s="109" t="s">
+        <v>350</v>
+      </c>
+      <c r="D108" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E108" s="5"/>
+      <c r="F108" s="6"/>
+      <c r="G108" s="7" t="n">
+        <v>202</v>
+      </c>
+      <c r="H108" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I108" s="9" t="n">
+        <v>202</v>
+      </c>
+      <c r="J108" s="8" t="n">
+        <v>202</v>
+      </c>
+      <c r="K108" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L108" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M108" s="8"/>
+      <c r="N108" s="8"/>
+      <c r="O108" s="8"/>
+      <c r="P108" s="8"/>
+      <c r="Q108" s="8"/>
+      <c r="R108" s="8"/>
+      <c r="S108" s="8"/>
+      <c r="T108" s="8"/>
+      <c r="U108" s="8"/>
+      <c r="V108" s="8"/>
+      <c r="W108" s="8"/>
+      <c r="X108" s="8"/>
+      <c r="Y108" s="8"/>
+      <c r="Z108" s="8"/>
+      <c r="AA108" s="8"/>
+      <c r="AB108" s="8"/>
+      <c r="AC108" s="8"/>
+      <c r="AD108" s="8"/>
+      <c r="AE108" s="8"/>
+      <c r="AF108" s="8"/>
+      <c r="AG108" s="8"/>
+      <c r="AH108" s="8"/>
+      <c r="AI108" s="8"/>
+      <c r="AJ108" s="8"/>
+      <c r="AK108" s="8"/>
+      <c r="AL108" s="8"/>
+      <c r="AM108" s="8"/>
+      <c r="AN108" s="8"/>
+    </row>
+    <row r="109" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B109" s="49"/>
+      <c r="C109" s="109"/>
+      <c r="D109" s="4"/>
+      <c r="E109" s="5"/>
+      <c r="F109" s="6"/>
+      <c r="G109" s="7"/>
+      <c r="H109" s="8"/>
+      <c r="I109" s="9"/>
+      <c r="J109" s="8"/>
+      <c r="K109" s="8"/>
+      <c r="L109" s="8"/>
+      <c r="M109" s="8"/>
+      <c r="N109" s="8"/>
+      <c r="O109" s="8"/>
+      <c r="P109" s="8"/>
+      <c r="Q109" s="8"/>
+      <c r="R109" s="8"/>
+      <c r="S109" s="8"/>
+      <c r="T109" s="8"/>
+      <c r="U109" s="8"/>
+      <c r="V109" s="8"/>
+      <c r="W109" s="8"/>
+      <c r="X109" s="8"/>
+      <c r="Y109" s="8"/>
+      <c r="Z109" s="8"/>
+      <c r="AA109" s="8"/>
+      <c r="AB109" s="8"/>
+      <c r="AC109" s="8"/>
+      <c r="AD109" s="8"/>
+      <c r="AE109" s="8"/>
+      <c r="AF109" s="8"/>
+      <c r="AG109" s="8"/>
+      <c r="AH109" s="8"/>
+      <c r="AI109" s="8"/>
+      <c r="AJ109" s="8"/>
+      <c r="AK109" s="8"/>
+      <c r="AL109" s="8"/>
+      <c r="AM109" s="8"/>
+      <c r="AN109" s="8"/>
+    </row>
+    <row r="110" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B110" s="49" t="s">
+        <v>351</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="D110" s="110" t="n">
+        <v>126</v>
+      </c>
+      <c r="E110" s="5"/>
+      <c r="F110" s="6"/>
+      <c r="G110" s="7" t="n">
+        <v>203</v>
+      </c>
+      <c r="H110" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="I110" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="J110" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="K110" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="L110" s="8" t="n">
+        <v>126</v>
+      </c>
+      <c r="M110" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="N110" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="O110" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="P110" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q110" s="8"/>
+      <c r="R110" s="8"/>
+      <c r="S110" s="8"/>
+      <c r="T110" s="8"/>
+      <c r="U110" s="8"/>
+      <c r="V110" s="8"/>
+      <c r="W110" s="8"/>
+      <c r="X110" s="8"/>
+      <c r="Y110" s="8"/>
+      <c r="Z110" s="8"/>
+      <c r="AA110" s="8"/>
+      <c r="AB110" s="8"/>
+      <c r="AC110" s="8"/>
+      <c r="AD110" s="8"/>
+      <c r="AE110" s="8"/>
+      <c r="AF110" s="8"/>
+      <c r="AG110" s="8"/>
+      <c r="AH110" s="8"/>
+      <c r="AI110" s="8"/>
+      <c r="AJ110" s="8"/>
+      <c r="AK110" s="8"/>
+      <c r="AL110" s="8"/>
+      <c r="AM110" s="8"/>
+      <c r="AN110" s="8"/>
+    </row>
+    <row r="111" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B111" s="49"/>
+      <c r="C111" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="D111" s="110" t="n">
+        <v>123</v>
+      </c>
+      <c r="E111" s="5"/>
+      <c r="F111" s="6"/>
+      <c r="G111" s="7" t="n">
+        <v>203</v>
+      </c>
+      <c r="H111" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="I111" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="J111" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="K111" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="L111" s="8" t="n">
+        <v>123</v>
+      </c>
+      <c r="M111" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="N111" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="O111" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="P111" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q111" s="8"/>
+      <c r="R111" s="8"/>
+      <c r="S111" s="8"/>
+      <c r="T111" s="8"/>
+      <c r="U111" s="8"/>
+      <c r="V111" s="8"/>
+      <c r="W111" s="8"/>
+      <c r="X111" s="8"/>
+      <c r="Y111" s="8"/>
+      <c r="Z111" s="8"/>
+      <c r="AA111" s="8"/>
+      <c r="AB111" s="8"/>
+      <c r="AC111" s="8"/>
+      <c r="AD111" s="8"/>
+      <c r="AE111" s="8"/>
+      <c r="AF111" s="8"/>
+      <c r="AG111" s="8"/>
+      <c r="AH111" s="8"/>
+      <c r="AI111" s="8"/>
+      <c r="AJ111" s="8"/>
+      <c r="AK111" s="8"/>
+      <c r="AL111" s="8"/>
+      <c r="AM111" s="8"/>
+      <c r="AN111" s="8"/>
+    </row>
+    <row r="112" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B112" s="49"/>
+      <c r="C112" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="D112" s="110" t="n">
+        <v>121</v>
+      </c>
+      <c r="E112" s="5"/>
+      <c r="F112" s="6"/>
+      <c r="G112" s="7" t="n">
+        <v>203</v>
+      </c>
+      <c r="H112" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="I112" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="J112" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="K112" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="L112" s="8" t="n">
+        <v>121</v>
+      </c>
+      <c r="M112" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="N112" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="O112" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="P112" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q112" s="8"/>
+      <c r="R112" s="8"/>
+      <c r="S112" s="8"/>
+      <c r="T112" s="8"/>
+      <c r="U112" s="8"/>
+      <c r="V112" s="8"/>
+      <c r="W112" s="8"/>
+      <c r="X112" s="8"/>
+      <c r="Y112" s="8"/>
+      <c r="Z112" s="8"/>
+      <c r="AA112" s="8"/>
+      <c r="AB112" s="8"/>
+      <c r="AC112" s="8"/>
+      <c r="AD112" s="8"/>
+      <c r="AE112" s="8"/>
+      <c r="AF112" s="8"/>
+      <c r="AG112" s="8"/>
+      <c r="AH112" s="8"/>
+      <c r="AI112" s="8"/>
+      <c r="AJ112" s="8"/>
+      <c r="AK112" s="8"/>
+      <c r="AL112" s="8"/>
+      <c r="AM112" s="8"/>
+      <c r="AN112" s="8"/>
+    </row>
+    <row r="113" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B113" s="49"/>
+      <c r="C113" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="D113" s="110" t="n">
+        <v>120</v>
+      </c>
+      <c r="E113" s="5"/>
+      <c r="F113" s="6"/>
+      <c r="G113" s="7" t="n">
+        <v>203</v>
+      </c>
+      <c r="H113" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="I113" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="J113" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="K113" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="L113" s="8" t="n">
+        <v>120</v>
+      </c>
+      <c r="M113" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="N113" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="O113" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="P113" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q113" s="8"/>
+      <c r="R113" s="8"/>
+      <c r="S113" s="8"/>
+      <c r="T113" s="8"/>
+      <c r="U113" s="8"/>
+      <c r="V113" s="8"/>
+      <c r="W113" s="8"/>
+      <c r="X113" s="8"/>
+      <c r="Y113" s="8"/>
+      <c r="Z113" s="8"/>
+      <c r="AA113" s="8"/>
+      <c r="AB113" s="8"/>
+      <c r="AC113" s="8"/>
+      <c r="AD113" s="8"/>
+      <c r="AE113" s="8"/>
+      <c r="AF113" s="8"/>
+      <c r="AG113" s="8"/>
+      <c r="AH113" s="8"/>
+      <c r="AI113" s="8"/>
+      <c r="AJ113" s="8"/>
+      <c r="AK113" s="8"/>
+      <c r="AL113" s="8"/>
+      <c r="AM113" s="8"/>
+      <c r="AN113" s="8"/>
+    </row>
+    <row r="114" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B114" s="49"/>
+      <c r="C114" s="3"/>
+      <c r="D114" s="110"/>
+      <c r="E114" s="5"/>
+      <c r="F114" s="6"/>
+      <c r="G114" s="7"/>
+      <c r="H114" s="8"/>
+      <c r="I114" s="9"/>
+      <c r="J114" s="8"/>
+      <c r="K114" s="8"/>
+      <c r="L114" s="8"/>
+      <c r="M114" s="8"/>
+      <c r="N114" s="8"/>
+      <c r="O114" s="8"/>
+      <c r="P114" s="8"/>
+      <c r="Q114" s="8"/>
+      <c r="R114" s="8"/>
+      <c r="S114" s="8"/>
+      <c r="T114" s="8"/>
+      <c r="U114" s="8"/>
+      <c r="V114" s="8"/>
+      <c r="W114" s="8"/>
+      <c r="X114" s="8"/>
+      <c r="Y114" s="8"/>
+      <c r="Z114" s="8"/>
+      <c r="AA114" s="8"/>
+      <c r="AB114" s="8"/>
+      <c r="AC114" s="8"/>
+      <c r="AD114" s="8"/>
+      <c r="AE114" s="8"/>
+      <c r="AF114" s="8"/>
+      <c r="AG114" s="8"/>
+      <c r="AH114" s="8"/>
+      <c r="AI114" s="8"/>
+      <c r="AJ114" s="8"/>
+      <c r="AK114" s="8"/>
+      <c r="AL114" s="8"/>
+      <c r="AM114" s="8"/>
+      <c r="AN114" s="8"/>
+    </row>
+    <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C116" s="111" t="s">
+        <v>362</v>
+      </c>
+      <c r="D116" s="112" t="s">
+        <v>363</v>
+      </c>
+      <c r="E116" s="113"/>
+      <c r="F116" s="114" t="s">
+        <v>364</v>
+      </c>
+      <c r="G116" s="56"/>
+    </row>
+    <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B117" s="115" t="s">
         <v>15</v>
       </c>
-      <c r="C107" s="102" t="s">
-        <v>316</v>
-      </c>
-      <c r="D107" s="4" t="n">
+      <c r="C117" s="116" t="s">
+        <v>365</v>
+      </c>
+      <c r="D117" s="4" t="n">
         <v>254</v>
       </c>
-      <c r="E107" s="5" t="s">
+      <c r="E117" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F107" s="6" t="n">
+      <c r="F117" s="6" t="n">
         <v>253</v>
       </c>
-      <c r="G107" s="7" t="s">
+      <c r="G117" s="7" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B108" s="101"/>
-      <c r="C108" s="102"/>
-    </row>
-    <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B109" s="101" t="s">
+    <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B118" s="115"/>
+      <c r="C118" s="116"/>
+    </row>
+    <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B119" s="115" t="s">
         <v>59</v>
       </c>
-      <c r="C109" s="102" t="s">
-        <v>317</v>
-      </c>
-      <c r="D109" s="4" t="n">
+      <c r="C119" s="116" t="s">
+        <v>366</v>
+      </c>
+      <c r="D119" s="4" t="n">
         <v>239</v>
       </c>
-      <c r="E109" s="5" t="s">
+      <c r="E119" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="F109" s="6" t="n">
+      <c r="F119" s="6" t="n">
         <v>237</v>
       </c>
-      <c r="G109" s="7" t="s">
+      <c r="G119" s="7" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B110" s="101"/>
-      <c r="C110" s="102"/>
-    </row>
-    <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B111" s="101" t="s">
+    <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B120" s="115"/>
+      <c r="C120" s="116"/>
+    </row>
+    <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B121" s="115" t="s">
         <v>117</v>
       </c>
-      <c r="C111" s="102" t="s">
-        <v>318</v>
-      </c>
-      <c r="F111" s="6" t="n">
+      <c r="C121" s="116" t="s">
+        <v>367</v>
+      </c>
+      <c r="F121" s="6" t="n">
         <v>211</v>
       </c>
-      <c r="G111" s="7" t="s">
+      <c r="G121" s="7" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B112" s="101"/>
-      <c r="C112" s="102"/>
-    </row>
-    <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B113" s="101" t="s">
+    <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B122" s="115"/>
+      <c r="C122" s="116"/>
+    </row>
+    <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B123" s="115" t="s">
         <v>127</v>
       </c>
-      <c r="C113" s="102" t="s">
-        <v>319</v>
+      <c r="C123" s="116" t="s">
+        <v>368</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="37">
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="N5:O5"/>
@@ -5943,6 +6738,24 @@
     <mergeCell ref="R79:V79"/>
     <mergeCell ref="K83:L83"/>
     <mergeCell ref="M83:N83"/>
+    <mergeCell ref="I89:J89"/>
+    <mergeCell ref="I90:J90"/>
+    <mergeCell ref="K90:L90"/>
+    <mergeCell ref="I91:J91"/>
+    <mergeCell ref="K91:L91"/>
+    <mergeCell ref="I92:J92"/>
+    <mergeCell ref="K92:L92"/>
+    <mergeCell ref="M93:N93"/>
+    <mergeCell ref="S93:T93"/>
+    <mergeCell ref="U93:V93"/>
+    <mergeCell ref="W93:X93"/>
+    <mergeCell ref="Y93:Z93"/>
+    <mergeCell ref="M94:N94"/>
+    <mergeCell ref="S94:T94"/>
+    <mergeCell ref="U94:V94"/>
+    <mergeCell ref="W94:X94"/>
+    <mergeCell ref="Y94:Z94"/>
+    <mergeCell ref="I95:J95"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.708333333333333" right="0.708333333333333" top="0.747916666666667" bottom="0.747916666666667" header="0.511811023622047" footer="0.511811023622047"/>

--- a/PGN 5.7_planter.xlsx
+++ b/PGN 5.7_planter.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="371">
   <si>
     <t xml:space="preserve">PGN Name</t>
   </si>
@@ -886,16 +886,16 @@
     <t xml:space="preserve">A1</t>
   </si>
   <si>
-    <t xml:space="preserve">Zero Hi/Lo 1-4095 0= no data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOP Hi/Lo 1-4095 0= no data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">On threshold 0= no data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Off threshold 0= no data</t>
+    <t xml:space="preserve">Zero Hi/Lo 1-4095 0xFFFF= no data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOP Hi/Lo 1-4095 0xFFFF= no data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On threshold 0xFF= no data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Off threshold 0xFF= no data</t>
   </si>
   <si>
     <t xml:space="preserve">Vacuum</t>
@@ -916,13 +916,13 @@
     <t xml:space="preserve">A3</t>
   </si>
   <si>
-    <t xml:space="preserve">Zero1 Hi/Lo 1-4095 0= no data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zero2 Hi/Lo 1-4095 0= no data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Act inWCX10 0= no data</t>
+    <t xml:space="preserve">Zero1 Hi/Lo 1-4095 0xFFFF= no data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zero2 Hi/Lo 1-4095 0xFFFF= no data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Act inWCX10 0xFF= no data</t>
   </si>
   <si>
     <t xml:space="preserve">Downpressure</t>
@@ -967,13 +967,13 @@
     <t xml:space="preserve">A5</t>
   </si>
   <si>
-    <t xml:space="preserve">Act weight(kg), 0 = no data</t>
+    <t xml:space="preserve">Act weight(kg), 0xFF = no data</t>
   </si>
   <si>
     <t xml:space="preserve">set0,1=true,bit = sensNbr</t>
   </si>
   <si>
-    <t xml:space="preserve">Act PressPSI 0= no data</t>
+    <t xml:space="preserve">Act PressPSI 0xFF= no data</t>
   </si>
   <si>
     <t xml:space="preserve">0 raisePres</t>
@@ -1007,6 +1007,12 @@
   </si>
   <si>
     <t xml:space="preserve">A7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zero Hi/Lo  0x7FFF= no data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ActWeight(kg) Hi/Lo &gt;0 0xFFFF= no data</t>
   </si>
   <si>
     <t xml:space="preserve">ForceOn 1-8</t>
@@ -1904,15 +1910,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1922,10 +1932,6 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -5148,7 +5154,9 @@
       <c r="D89" s="96" t="s">
         <v>102</v>
       </c>
-      <c r="E89" s="97"/>
+      <c r="E89" s="97" t="n">
+        <v>123</v>
+      </c>
       <c r="F89" s="98" t="s">
         <v>280</v>
       </c>
@@ -5203,13 +5211,15 @@
     </row>
     <row r="90" s="59" customFormat="true" ht="29.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B90" s="49"/>
-      <c r="C90" s="95" t="s">
+      <c r="C90" s="102" t="s">
         <v>285</v>
       </c>
       <c r="D90" s="96" t="s">
         <v>102</v>
       </c>
-      <c r="E90" s="97"/>
+      <c r="E90" s="97" t="n">
+        <v>123</v>
+      </c>
       <c r="F90" s="98" t="s">
         <v>286</v>
       </c>
@@ -5219,18 +5229,18 @@
       <c r="H90" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="I90" s="100" t="s">
+      <c r="I90" s="103" t="s">
         <v>287</v>
       </c>
-      <c r="J90" s="100"/>
-      <c r="K90" s="100" t="s">
+      <c r="J90" s="103"/>
+      <c r="K90" s="103" t="s">
         <v>288</v>
       </c>
-      <c r="L90" s="100"/>
-      <c r="M90" s="102" t="s">
+      <c r="L90" s="103"/>
+      <c r="M90" s="104" t="s">
         <v>289</v>
       </c>
-      <c r="N90" s="102" t="s">
+      <c r="N90" s="104" t="s">
         <v>290</v>
       </c>
       <c r="O90" s="8"/>
@@ -5264,13 +5274,15 @@
     </row>
     <row r="91" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B91" s="49"/>
-      <c r="C91" s="95" t="s">
+      <c r="C91" s="102" t="s">
         <v>291</v>
       </c>
       <c r="D91" s="96" t="s">
         <v>102</v>
       </c>
-      <c r="E91" s="97"/>
+      <c r="E91" s="97" t="n">
+        <v>123</v>
+      </c>
       <c r="F91" s="98" t="s">
         <v>292</v>
       </c>
@@ -5325,13 +5337,15 @@
     </row>
     <row r="92" s="59" customFormat="true" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B92" s="49"/>
-      <c r="C92" s="95" t="s">
+      <c r="C92" s="102" t="s">
         <v>295</v>
       </c>
       <c r="D92" s="96" t="s">
         <v>102</v>
       </c>
-      <c r="E92" s="97"/>
+      <c r="E92" s="97" t="n">
+        <v>123</v>
+      </c>
       <c r="F92" s="98" t="s">
         <v>296</v>
       </c>
@@ -5341,14 +5355,14 @@
       <c r="H92" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="I92" s="100" t="s">
+      <c r="I92" s="103" t="s">
         <v>297</v>
       </c>
-      <c r="J92" s="100"/>
-      <c r="K92" s="100" t="s">
+      <c r="J92" s="103"/>
+      <c r="K92" s="103" t="s">
         <v>298</v>
       </c>
-      <c r="L92" s="100"/>
+      <c r="L92" s="103"/>
       <c r="M92" s="103" t="s">
         <v>299</v>
       </c>
@@ -5386,13 +5400,15 @@
     </row>
     <row r="93" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B93" s="49"/>
-      <c r="C93" s="95" t="s">
+      <c r="C93" s="102" t="s">
         <v>300</v>
       </c>
       <c r="D93" s="96" t="s">
         <v>102</v>
       </c>
-      <c r="E93" s="97"/>
+      <c r="E93" s="97" t="n">
+        <v>123</v>
+      </c>
       <c r="F93" s="98" t="s">
         <v>301</v>
       </c>
@@ -5461,13 +5477,15 @@
     </row>
     <row r="94" s="59" customFormat="true" ht="30.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B94" s="49"/>
-      <c r="C94" s="104" t="s">
+      <c r="C94" s="105" t="s">
         <v>312</v>
       </c>
       <c r="D94" s="96" t="s">
         <v>102</v>
       </c>
-      <c r="E94" s="97"/>
+      <c r="E94" s="97" t="n">
+        <v>123</v>
+      </c>
       <c r="F94" s="98" t="s">
         <v>313</v>
       </c>
@@ -5477,16 +5495,16 @@
       <c r="H94" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="I94" s="105" t="s">
+      <c r="I94" s="106" t="s">
         <v>314</v>
       </c>
-      <c r="J94" s="105" t="s">
+      <c r="J94" s="106" t="s">
         <v>314</v>
       </c>
-      <c r="K94" s="105" t="s">
+      <c r="K94" s="106" t="s">
         <v>314</v>
       </c>
-      <c r="L94" s="106" t="s">
+      <c r="L94" s="107" t="s">
         <v>315</v>
       </c>
       <c r="M94" s="107" t="s">
@@ -5536,13 +5554,15 @@
     </row>
     <row r="95" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B95" s="49"/>
-      <c r="C95" s="95" t="s">
+      <c r="C95" s="102" t="s">
         <v>319</v>
       </c>
       <c r="D95" s="96" t="s">
         <v>102</v>
       </c>
-      <c r="E95" s="97"/>
+      <c r="E95" s="97" t="n">
+        <v>123</v>
+      </c>
       <c r="F95" s="98" t="s">
         <v>320</v>
       </c>
@@ -5597,15 +5617,17 @@
       <c r="AM95" s="8"/>
       <c r="AN95" s="8"/>
     </row>
-    <row r="96" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="96" s="59" customFormat="true" ht="27.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B96" s="49"/>
-      <c r="C96" s="95" t="s">
+      <c r="C96" s="102" t="s">
         <v>326</v>
       </c>
       <c r="D96" s="96" t="s">
         <v>102</v>
       </c>
-      <c r="E96" s="97"/>
+      <c r="E96" s="97" t="n">
+        <v>123</v>
+      </c>
       <c r="F96" s="98" t="s">
         <v>327</v>
       </c>
@@ -5615,15 +5637,19 @@
       <c r="H96" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="I96" s="9"/>
-      <c r="J96" s="8"/>
-      <c r="K96" s="101"/>
-      <c r="L96" s="101"/>
+      <c r="I96" s="103" t="s">
+        <v>328</v>
+      </c>
+      <c r="J96" s="103"/>
+      <c r="K96" s="103" t="s">
+        <v>329</v>
+      </c>
+      <c r="L96" s="103"/>
       <c r="M96" s="8" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="N96" s="8" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="O96" s="8"/>
       <c r="P96" s="8"/>
@@ -5738,10 +5764,10 @@
     </row>
     <row r="99" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B99" s="49" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D99" s="4" t="s">
         <v>17</v>
@@ -5755,7 +5781,7 @@
         <v>3</v>
       </c>
       <c r="I99" s="9" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="J99" s="8" t="n">
         <v>0</v>
@@ -5838,10 +5864,10 @@
     </row>
     <row r="101" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B101" s="49" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D101" s="4" t="n">
         <v>126</v>
@@ -5855,19 +5881,19 @@
         <v>5</v>
       </c>
       <c r="I101" s="9" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J101" s="8" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="K101" s="8" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L101" s="8" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="M101" s="8" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="N101" s="8" t="s">
         <v>25</v>
@@ -5902,7 +5928,7 @@
     <row r="102" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B102" s="108"/>
       <c r="C102" s="3" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D102" s="4" t="n">
         <v>123</v>
@@ -5916,10 +5942,10 @@
         <v>5</v>
       </c>
       <c r="I102" s="9" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="J102" s="8" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K102" s="8" t="s">
         <v>57</v>
@@ -5963,7 +5989,7 @@
     <row r="103" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B103" s="108"/>
       <c r="C103" s="3" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D103" s="4" t="n">
         <v>121</v>
@@ -6024,7 +6050,7 @@
     <row r="104" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B104" s="108"/>
       <c r="C104" s="3" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D104" s="4" t="n">
         <v>120</v>
@@ -6125,10 +6151,10 @@
     </row>
     <row r="106" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B106" s="49" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D106" s="4" t="s">
         <v>17</v>
@@ -6148,13 +6174,13 @@
         <v>201</v>
       </c>
       <c r="K106" s="8" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="L106" s="8" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="M106" s="8" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="N106" s="8" t="s">
         <v>25</v>
@@ -6229,10 +6255,10 @@
     </row>
     <row r="108" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B108" s="49" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C108" s="109" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D108" s="4" t="s">
         <v>17</v>
@@ -6329,10 +6355,10 @@
     </row>
     <row r="110" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B110" s="49" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D110" s="110" t="n">
         <v>126</v>
@@ -6346,25 +6372,25 @@
         <v>7</v>
       </c>
       <c r="I110" s="9" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="J110" s="8" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K110" s="8" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="L110" s="8" t="n">
         <v>126</v>
       </c>
       <c r="M110" s="8" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="N110" s="8" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="O110" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="P110" s="8" t="s">
         <v>25</v>
@@ -6397,7 +6423,7 @@
     <row r="111" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B111" s="49"/>
       <c r="C111" s="3" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D111" s="110" t="n">
         <v>123</v>
@@ -6411,25 +6437,25 @@
         <v>7</v>
       </c>
       <c r="I111" s="9" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="J111" s="8" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K111" s="8" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="L111" s="8" t="n">
         <v>123</v>
       </c>
       <c r="M111" s="8" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="N111" s="8" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="O111" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="P111" s="8" t="s">
         <v>25</v>
@@ -6462,7 +6488,7 @@
     <row r="112" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B112" s="49"/>
       <c r="C112" s="3" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D112" s="110" t="n">
         <v>121</v>
@@ -6476,25 +6502,25 @@
         <v>7</v>
       </c>
       <c r="I112" s="9" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="J112" s="8" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K112" s="8" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="L112" s="8" t="n">
         <v>121</v>
       </c>
       <c r="M112" s="8" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="N112" s="8" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="O112" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="P112" s="8" t="s">
         <v>25</v>
@@ -6527,7 +6553,7 @@
     <row r="113" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B113" s="49"/>
       <c r="C113" s="3" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D113" s="110" t="n">
         <v>120</v>
@@ -6541,25 +6567,25 @@
         <v>7</v>
       </c>
       <c r="I113" s="9" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="J113" s="8" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K113" s="8" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="L113" s="8" t="n">
         <v>120</v>
       </c>
       <c r="M113" s="8" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="N113" s="8" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="O113" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="P113" s="8" t="s">
         <v>25</v>
@@ -6632,14 +6658,14 @@
     </row>
     <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C116" s="111" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D116" s="112" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E116" s="113"/>
       <c r="F116" s="114" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="G116" s="56"/>
     </row>
@@ -6648,7 +6674,7 @@
         <v>15</v>
       </c>
       <c r="C117" s="116" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D117" s="4" t="n">
         <v>254</v>
@@ -6672,7 +6698,7 @@
         <v>59</v>
       </c>
       <c r="C119" s="116" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D119" s="4" t="n">
         <v>239</v>
@@ -6696,7 +6722,7 @@
         <v>117</v>
       </c>
       <c r="C121" s="116" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>211</v>
@@ -6714,11 +6740,11 @@
         <v>127</v>
       </c>
       <c r="C123" s="116" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="37">
+  <mergeCells count="39">
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="N5:O5"/>
@@ -6756,6 +6782,8 @@
     <mergeCell ref="W94:X94"/>
     <mergeCell ref="Y94:Z94"/>
     <mergeCell ref="I95:J95"/>
+    <mergeCell ref="I96:J96"/>
+    <mergeCell ref="K96:L96"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.708333333333333" right="0.708333333333333" top="0.747916666666667" bottom="0.747916666666667" header="0.511811023622047" footer="0.511811023622047"/>

--- a/PGN 5.7_planter.xlsx
+++ b/PGN 5.7_planter.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="372">
   <si>
     <t xml:space="preserve">PGN Name</t>
   </si>
@@ -1001,6 +1001,9 @@
   </si>
   <si>
     <t xml:space="preserve">Set pos 9-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 is dispensing, 0 not dispensing</t>
   </si>
   <si>
     <t xml:space="preserve">fertilizer config</t>
@@ -1501,7 +1504,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="118">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1932,6 +1935,10 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -5554,7 +5561,7 @@
     </row>
     <row r="95" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B95" s="49"/>
-      <c r="C95" s="102" t="s">
+      <c r="C95" s="108" t="s">
         <v>319</v>
       </c>
       <c r="D95" s="96" t="s">
@@ -5593,11 +5600,13 @@
       <c r="Q95" s="87" t="s">
         <v>25</v>
       </c>
-      <c r="R95" s="8"/>
-      <c r="S95" s="8"/>
-      <c r="T95" s="8"/>
-      <c r="U95" s="8"/>
-      <c r="V95" s="8"/>
+      <c r="R95" s="87" t="s">
+        <v>326</v>
+      </c>
+      <c r="S95" s="87"/>
+      <c r="T95" s="87"/>
+      <c r="U95" s="87"/>
+      <c r="V95" s="87"/>
       <c r="W95" s="8"/>
       <c r="X95" s="8"/>
       <c r="Y95" s="8"/>
@@ -5619,8 +5628,8 @@
     </row>
     <row r="96" s="59" customFormat="true" ht="27.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B96" s="49"/>
-      <c r="C96" s="102" t="s">
-        <v>326</v>
+      <c r="C96" s="108" t="s">
+        <v>327</v>
       </c>
       <c r="D96" s="96" t="s">
         <v>102</v>
@@ -5629,7 +5638,7 @@
         <v>123</v>
       </c>
       <c r="F96" s="98" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G96" s="99" t="n">
         <v>167</v>
@@ -5638,18 +5647,18 @@
         <v>8</v>
       </c>
       <c r="I96" s="103" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J96" s="103"/>
       <c r="K96" s="103" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L96" s="103"/>
       <c r="M96" s="8" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N96" s="8" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O96" s="8"/>
       <c r="P96" s="8"/>
@@ -5764,10 +5773,10 @@
     </row>
     <row r="99" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B99" s="49" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D99" s="4" t="s">
         <v>17</v>
@@ -5781,7 +5790,7 @@
         <v>3</v>
       </c>
       <c r="I99" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="J99" s="8" t="n">
         <v>0</v>
@@ -5822,7 +5831,7 @@
       <c r="AN99" s="8"/>
     </row>
     <row r="100" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B100" s="108"/>
+      <c r="B100" s="109"/>
       <c r="C100" s="3"/>
       <c r="D100" s="4"/>
       <c r="E100" s="5"/>
@@ -5864,10 +5873,10 @@
     </row>
     <row r="101" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B101" s="49" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D101" s="4" t="n">
         <v>126</v>
@@ -5881,19 +5890,19 @@
         <v>5</v>
       </c>
       <c r="I101" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="J101" s="8" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K101" s="8" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L101" s="8" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M101" s="8" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N101" s="8" t="s">
         <v>25</v>
@@ -5926,9 +5935,9 @@
       <c r="AN101" s="8"/>
     </row>
     <row r="102" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B102" s="108"/>
+      <c r="B102" s="109"/>
       <c r="C102" s="3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D102" s="4" t="n">
         <v>123</v>
@@ -5942,10 +5951,10 @@
         <v>5</v>
       </c>
       <c r="I102" s="9" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J102" s="8" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K102" s="8" t="s">
         <v>57</v>
@@ -5987,9 +5996,9 @@
       <c r="AN102" s="8"/>
     </row>
     <row r="103" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B103" s="108"/>
+      <c r="B103" s="109"/>
       <c r="C103" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D103" s="4" t="n">
         <v>121</v>
@@ -6048,9 +6057,9 @@
       <c r="AN103" s="8"/>
     </row>
     <row r="104" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B104" s="108"/>
+      <c r="B104" s="109"/>
       <c r="C104" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D104" s="4" t="n">
         <v>120</v>
@@ -6151,10 +6160,10 @@
     </row>
     <row r="106" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B106" s="49" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D106" s="4" t="s">
         <v>17</v>
@@ -6174,13 +6183,13 @@
         <v>201</v>
       </c>
       <c r="K106" s="8" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L106" s="8" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M106" s="8" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N106" s="8" t="s">
         <v>25</v>
@@ -6255,10 +6264,10 @@
     </row>
     <row r="108" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B108" s="49" t="s">
-        <v>347</v>
-      </c>
-      <c r="C108" s="109" t="s">
-        <v>352</v>
+        <v>348</v>
+      </c>
+      <c r="C108" s="110" t="s">
+        <v>353</v>
       </c>
       <c r="D108" s="4" t="s">
         <v>17</v>
@@ -6314,7 +6323,7 @@
     </row>
     <row r="109" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B109" s="49"/>
-      <c r="C109" s="109"/>
+      <c r="C109" s="110"/>
       <c r="D109" s="4"/>
       <c r="E109" s="5"/>
       <c r="F109" s="6"/>
@@ -6355,12 +6364,12 @@
     </row>
     <row r="110" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B110" s="49" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="D110" s="110" t="n">
+        <v>355</v>
+      </c>
+      <c r="D110" s="111" t="n">
         <v>126</v>
       </c>
       <c r="E110" s="5"/>
@@ -6372,25 +6381,25 @@
         <v>7</v>
       </c>
       <c r="I110" s="9" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J110" s="8" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K110" s="8" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L110" s="8" t="n">
         <v>126</v>
       </c>
       <c r="M110" s="8" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N110" s="8" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O110" s="8" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="P110" s="8" t="s">
         <v>25</v>
@@ -6423,9 +6432,9 @@
     <row r="111" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B111" s="49"/>
       <c r="C111" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="D111" s="110" t="n">
+        <v>362</v>
+      </c>
+      <c r="D111" s="111" t="n">
         <v>123</v>
       </c>
       <c r="E111" s="5"/>
@@ -6437,25 +6446,25 @@
         <v>7</v>
       </c>
       <c r="I111" s="9" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J111" s="8" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K111" s="8" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L111" s="8" t="n">
         <v>123</v>
       </c>
       <c r="M111" s="8" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N111" s="8" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O111" s="8" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="P111" s="8" t="s">
         <v>25</v>
@@ -6488,9 +6497,9 @@
     <row r="112" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B112" s="49"/>
       <c r="C112" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="D112" s="110" t="n">
+        <v>363</v>
+      </c>
+      <c r="D112" s="111" t="n">
         <v>121</v>
       </c>
       <c r="E112" s="5"/>
@@ -6502,25 +6511,25 @@
         <v>7</v>
       </c>
       <c r="I112" s="9" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J112" s="8" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K112" s="8" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L112" s="8" t="n">
         <v>121</v>
       </c>
       <c r="M112" s="8" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N112" s="8" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O112" s="8" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="P112" s="8" t="s">
         <v>25</v>
@@ -6553,9 +6562,9 @@
     <row r="113" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B113" s="49"/>
       <c r="C113" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="D113" s="110" t="n">
+        <v>364</v>
+      </c>
+      <c r="D113" s="111" t="n">
         <v>120</v>
       </c>
       <c r="E113" s="5"/>
@@ -6567,25 +6576,25 @@
         <v>7</v>
       </c>
       <c r="I113" s="9" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J113" s="8" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K113" s="8" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L113" s="8" t="n">
         <v>120</v>
       </c>
       <c r="M113" s="8" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N113" s="8" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O113" s="8" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="P113" s="8" t="s">
         <v>25</v>
@@ -6618,7 +6627,7 @@
     <row r="114" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B114" s="49"/>
       <c r="C114" s="3"/>
-      <c r="D114" s="110"/>
+      <c r="D114" s="111"/>
       <c r="E114" s="5"/>
       <c r="F114" s="6"/>
       <c r="G114" s="7"/>
@@ -6657,24 +6666,24 @@
       <c r="AN114" s="8"/>
     </row>
     <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C116" s="111" t="s">
-        <v>364</v>
-      </c>
-      <c r="D116" s="112" t="s">
+      <c r="C116" s="112" t="s">
         <v>365</v>
       </c>
-      <c r="E116" s="113"/>
-      <c r="F116" s="114" t="s">
+      <c r="D116" s="113" t="s">
         <v>366</v>
       </c>
+      <c r="E116" s="114"/>
+      <c r="F116" s="115" t="s">
+        <v>367</v>
+      </c>
       <c r="G116" s="56"/>
     </row>
     <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B117" s="115" t="s">
+      <c r="B117" s="116" t="s">
         <v>15</v>
       </c>
-      <c r="C117" s="116" t="s">
-        <v>367</v>
+      <c r="C117" s="117" t="s">
+        <v>368</v>
       </c>
       <c r="D117" s="4" t="n">
         <v>254</v>
@@ -6690,15 +6699,15 @@
       </c>
     </row>
     <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B118" s="115"/>
-      <c r="C118" s="116"/>
+      <c r="B118" s="116"/>
+      <c r="C118" s="117"/>
     </row>
     <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B119" s="115" t="s">
+      <c r="B119" s="116" t="s">
         <v>59</v>
       </c>
-      <c r="C119" s="116" t="s">
-        <v>368</v>
+      <c r="C119" s="117" t="s">
+        <v>369</v>
       </c>
       <c r="D119" s="4" t="n">
         <v>239</v>
@@ -6714,15 +6723,15 @@
       </c>
     </row>
     <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B120" s="115"/>
-      <c r="C120" s="116"/>
+      <c r="B120" s="116"/>
+      <c r="C120" s="117"/>
     </row>
     <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B121" s="115" t="s">
+      <c r="B121" s="116" t="s">
         <v>117</v>
       </c>
-      <c r="C121" s="116" t="s">
-        <v>369</v>
+      <c r="C121" s="117" t="s">
+        <v>370</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>211</v>
@@ -6732,19 +6741,19 @@
       </c>
     </row>
     <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B122" s="115"/>
-      <c r="C122" s="116"/>
+      <c r="B122" s="116"/>
+      <c r="C122" s="117"/>
     </row>
     <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B123" s="115" t="s">
+      <c r="B123" s="116" t="s">
         <v>127</v>
       </c>
-      <c r="C123" s="116" t="s">
-        <v>370</v>
+      <c r="C123" s="117" t="s">
+        <v>371</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="40">
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="N5:O5"/>
@@ -6782,6 +6791,7 @@
     <mergeCell ref="W94:X94"/>
     <mergeCell ref="Y94:Z94"/>
     <mergeCell ref="I95:J95"/>
+    <mergeCell ref="R95:V95"/>
     <mergeCell ref="I96:J96"/>
     <mergeCell ref="K96:L96"/>
   </mergeCells>

--- a/PGN 5.7_planter.xlsx
+++ b/PGN 5.7_planter.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="375">
   <si>
     <t xml:space="preserve">PGN Name</t>
   </si>
@@ -904,10 +904,19 @@
     <t xml:space="preserve">A2</t>
   </si>
   <si>
-    <t xml:space="preserve">inWC1X10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inWC2X10</t>
+    <t xml:space="preserve">Raw1Left Hi/Lo 0-4095(0-12v)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raw2Rgh Hi/Lo 0-4095(0-12v)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InWC1X10-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InWC2X10-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For 0 it send 5</t>
   </si>
   <si>
     <t xml:space="preserve">Vacuum config</t>
@@ -1913,18 +1922,22 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1935,10 +1948,6 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -5300,26 +5309,28 @@
         <v>8</v>
       </c>
       <c r="I91" s="100" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="J91" s="100"/>
       <c r="K91" s="100" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="L91" s="100"/>
       <c r="M91" s="8" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="N91" s="8" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="O91" s="8"/>
       <c r="P91" s="8"/>
       <c r="Q91" s="87" t="s">
         <v>25</v>
       </c>
-      <c r="R91" s="8"/>
-      <c r="S91" s="8"/>
+      <c r="R91" s="87" t="s">
+        <v>297</v>
+      </c>
+      <c r="S91" s="87"/>
       <c r="T91" s="8"/>
       <c r="U91" s="8"/>
       <c r="V91" s="8"/>
@@ -5345,7 +5356,7 @@
     <row r="92" s="59" customFormat="true" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B92" s="49"/>
       <c r="C92" s="102" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D92" s="96" t="s">
         <v>102</v>
@@ -5354,7 +5365,7 @@
         <v>123</v>
       </c>
       <c r="F92" s="98" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="G92" s="99" t="n">
         <v>163</v>
@@ -5363,18 +5374,18 @@
         <v>8</v>
       </c>
       <c r="I92" s="103" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="J92" s="103"/>
       <c r="K92" s="103" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="L92" s="103"/>
       <c r="M92" s="103" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="N92" s="103" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="O92" s="100"/>
       <c r="P92" s="8"/>
@@ -5407,8 +5418,8 @@
     </row>
     <row r="93" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B93" s="49"/>
-      <c r="C93" s="102" t="s">
-        <v>300</v>
+      <c r="C93" s="105" t="s">
+        <v>303</v>
       </c>
       <c r="D93" s="96" t="s">
         <v>102</v>
@@ -5417,7 +5428,7 @@
         <v>123</v>
       </c>
       <c r="F93" s="98" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="G93" s="99" t="n">
         <v>164</v>
@@ -5426,13 +5437,13 @@
         <v>8</v>
       </c>
       <c r="I93" s="9" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="J93" s="8" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="K93" s="8" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="L93" s="101"/>
       <c r="M93" s="100" t="s">
@@ -5440,31 +5451,31 @@
       </c>
       <c r="N93" s="100"/>
       <c r="O93" s="8" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="P93" s="8" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q93" s="87" t="s">
         <v>25</v>
       </c>
       <c r="R93" s="8" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="S93" s="87" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="T93" s="87"/>
       <c r="U93" s="8" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="V93" s="8"/>
       <c r="W93" s="8" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="X93" s="8"/>
       <c r="Y93" s="8" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Z93" s="8"/>
       <c r="AA93" s="8"/>
@@ -5484,8 +5495,8 @@
     </row>
     <row r="94" s="59" customFormat="true" ht="30.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B94" s="49"/>
-      <c r="C94" s="105" t="s">
-        <v>312</v>
+      <c r="C94" s="106" t="s">
+        <v>315</v>
       </c>
       <c r="D94" s="96" t="s">
         <v>102</v>
@@ -5494,7 +5505,7 @@
         <v>123</v>
       </c>
       <c r="F94" s="98" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="G94" s="99" t="n">
         <v>165</v>
@@ -5502,46 +5513,46 @@
       <c r="H94" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="I94" s="106" t="s">
-        <v>314</v>
-      </c>
-      <c r="J94" s="106" t="s">
-        <v>314</v>
-      </c>
-      <c r="K94" s="106" t="s">
-        <v>314</v>
-      </c>
-      <c r="L94" s="107" t="s">
-        <v>315</v>
-      </c>
-      <c r="M94" s="107" t="s">
+      <c r="I94" s="107" t="s">
+        <v>317</v>
+      </c>
+      <c r="J94" s="107" t="s">
+        <v>317</v>
+      </c>
+      <c r="K94" s="107" t="s">
+        <v>317</v>
+      </c>
+      <c r="L94" s="108" t="s">
+        <v>318</v>
+      </c>
+      <c r="M94" s="108" t="s">
         <v>287</v>
       </c>
-      <c r="N94" s="107"/>
+      <c r="N94" s="108"/>
       <c r="O94" s="103" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="P94" s="87" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q94" s="87" t="s">
         <v>25</v>
       </c>
       <c r="R94" s="87" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="S94" s="87" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="T94" s="87"/>
       <c r="U94" s="87" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="V94" s="87"/>
       <c r="W94" s="87"/>
       <c r="X94" s="87"/>
       <c r="Y94" s="87" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Z94" s="87"/>
       <c r="AA94" s="8"/>
@@ -5561,8 +5572,8 @@
     </row>
     <row r="95" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B95" s="49"/>
-      <c r="C95" s="108" t="s">
-        <v>319</v>
+      <c r="C95" s="102" t="s">
+        <v>322</v>
       </c>
       <c r="D95" s="96" t="s">
         <v>102</v>
@@ -5571,7 +5582,7 @@
         <v>123</v>
       </c>
       <c r="F95" s="98" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="G95" s="99" t="n">
         <v>166</v>
@@ -5580,20 +5591,20 @@
         <v>8</v>
       </c>
       <c r="I95" s="100" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="J95" s="100"/>
       <c r="K95" s="8" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="L95" s="8" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="M95" s="8" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="N95" s="8" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="O95" s="8"/>
       <c r="P95" s="8"/>
@@ -5601,7 +5612,7 @@
         <v>25</v>
       </c>
       <c r="R95" s="87" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="S95" s="87"/>
       <c r="T95" s="87"/>
@@ -5628,8 +5639,8 @@
     </row>
     <row r="96" s="59" customFormat="true" ht="27.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B96" s="49"/>
-      <c r="C96" s="108" t="s">
-        <v>327</v>
+      <c r="C96" s="102" t="s">
+        <v>330</v>
       </c>
       <c r="D96" s="96" t="s">
         <v>102</v>
@@ -5638,7 +5649,7 @@
         <v>123</v>
       </c>
       <c r="F96" s="98" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="G96" s="99" t="n">
         <v>167</v>
@@ -5647,18 +5658,18 @@
         <v>8</v>
       </c>
       <c r="I96" s="103" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="J96" s="103"/>
       <c r="K96" s="103" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="L96" s="103"/>
       <c r="M96" s="8" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="N96" s="8" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="O96" s="8"/>
       <c r="P96" s="8"/>
@@ -5773,10 +5784,10 @@
     </row>
     <row r="99" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B99" s="49" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D99" s="4" t="s">
         <v>17</v>
@@ -5790,7 +5801,7 @@
         <v>3</v>
       </c>
       <c r="I99" s="9" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="J99" s="8" t="n">
         <v>0</v>
@@ -5873,10 +5884,10 @@
     </row>
     <row r="101" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B101" s="49" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="D101" s="4" t="n">
         <v>126</v>
@@ -5890,19 +5901,19 @@
         <v>5</v>
       </c>
       <c r="I101" s="9" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="J101" s="8" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="K101" s="8" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="L101" s="8" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="M101" s="8" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="N101" s="8" t="s">
         <v>25</v>
@@ -5937,7 +5948,7 @@
     <row r="102" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B102" s="109"/>
       <c r="C102" s="3" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="D102" s="4" t="n">
         <v>123</v>
@@ -5951,10 +5962,10 @@
         <v>5</v>
       </c>
       <c r="I102" s="9" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="J102" s="8" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="K102" s="8" t="s">
         <v>57</v>
@@ -5998,7 +6009,7 @@
     <row r="103" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B103" s="109"/>
       <c r="C103" s="3" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D103" s="4" t="n">
         <v>121</v>
@@ -6059,7 +6070,7 @@
     <row r="104" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B104" s="109"/>
       <c r="C104" s="3" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="D104" s="4" t="n">
         <v>120</v>
@@ -6160,10 +6171,10 @@
     </row>
     <row r="106" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B106" s="49" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="D106" s="4" t="s">
         <v>17</v>
@@ -6183,13 +6194,13 @@
         <v>201</v>
       </c>
       <c r="K106" s="8" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="L106" s="8" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="M106" s="8" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="N106" s="8" t="s">
         <v>25</v>
@@ -6264,10 +6275,10 @@
     </row>
     <row r="108" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B108" s="49" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C108" s="110" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="D108" s="4" t="s">
         <v>17</v>
@@ -6364,10 +6375,10 @@
     </row>
     <row r="110" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B110" s="49" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="D110" s="111" t="n">
         <v>126</v>
@@ -6381,25 +6392,25 @@
         <v>7</v>
       </c>
       <c r="I110" s="9" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="J110" s="8" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="K110" s="8" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="L110" s="8" t="n">
         <v>126</v>
       </c>
       <c r="M110" s="8" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="N110" s="8" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="O110" s="8" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="P110" s="8" t="s">
         <v>25</v>
@@ -6432,7 +6443,7 @@
     <row r="111" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B111" s="49"/>
       <c r="C111" s="3" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="D111" s="111" t="n">
         <v>123</v>
@@ -6446,25 +6457,25 @@
         <v>7</v>
       </c>
       <c r="I111" s="9" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="J111" s="8" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="K111" s="8" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="L111" s="8" t="n">
         <v>123</v>
       </c>
       <c r="M111" s="8" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="N111" s="8" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="O111" s="8" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="P111" s="8" t="s">
         <v>25</v>
@@ -6497,7 +6508,7 @@
     <row r="112" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B112" s="49"/>
       <c r="C112" s="3" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="D112" s="111" t="n">
         <v>121</v>
@@ -6511,25 +6522,25 @@
         <v>7</v>
       </c>
       <c r="I112" s="9" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="J112" s="8" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="K112" s="8" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="L112" s="8" t="n">
         <v>121</v>
       </c>
       <c r="M112" s="8" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="N112" s="8" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="O112" s="8" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="P112" s="8" t="s">
         <v>25</v>
@@ -6562,7 +6573,7 @@
     <row r="113" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B113" s="49"/>
       <c r="C113" s="3" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="D113" s="111" t="n">
         <v>120</v>
@@ -6576,25 +6587,25 @@
         <v>7</v>
       </c>
       <c r="I113" s="9" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="J113" s="8" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="K113" s="8" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="L113" s="8" t="n">
         <v>120</v>
       </c>
       <c r="M113" s="8" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="N113" s="8" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="O113" s="8" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="P113" s="8" t="s">
         <v>25</v>
@@ -6667,14 +6678,14 @@
     </row>
     <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C116" s="112" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="D116" s="113" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="E116" s="114"/>
       <c r="F116" s="115" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="G116" s="56"/>
     </row>
@@ -6683,7 +6694,7 @@
         <v>15</v>
       </c>
       <c r="C117" s="117" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="D117" s="4" t="n">
         <v>254</v>
@@ -6707,7 +6718,7 @@
         <v>59</v>
       </c>
       <c r="C119" s="117" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="D119" s="4" t="n">
         <v>239</v>
@@ -6731,7 +6742,7 @@
         <v>117</v>
       </c>
       <c r="C121" s="117" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>211</v>
@@ -6749,11 +6760,11 @@
         <v>127</v>
       </c>
       <c r="C123" s="117" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="40">
+  <mergeCells count="41">
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="N5:O5"/>
@@ -6778,6 +6789,7 @@
     <mergeCell ref="K90:L90"/>
     <mergeCell ref="I91:J91"/>
     <mergeCell ref="K91:L91"/>
+    <mergeCell ref="R91:S91"/>
     <mergeCell ref="I92:J92"/>
     <mergeCell ref="K92:L92"/>
     <mergeCell ref="M93:N93"/>

--- a/PGN 5.7_planter.xlsx
+++ b/PGN 5.7_planter.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="377">
   <si>
     <t xml:space="preserve">PGN Name</t>
   </si>
@@ -1010,6 +1010,12 @@
   </si>
   <si>
     <t xml:space="preserve">Set pos 9-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forced 1-8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forced 9-16</t>
   </si>
   <si>
     <t xml:space="preserve">1 is dispensing, 0 not dispensing</t>
@@ -5606,13 +5612,17 @@
       <c r="N95" s="8" t="s">
         <v>328</v>
       </c>
-      <c r="O95" s="8"/>
-      <c r="P95" s="8"/>
+      <c r="O95" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="P95" s="8" t="s">
+        <v>330</v>
+      </c>
       <c r="Q95" s="87" t="s">
         <v>25</v>
       </c>
       <c r="R95" s="87" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="S95" s="87"/>
       <c r="T95" s="87"/>
@@ -5640,7 +5650,7 @@
     <row r="96" s="59" customFormat="true" ht="27.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B96" s="49"/>
       <c r="C96" s="102" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D96" s="96" t="s">
         <v>102</v>
@@ -5649,7 +5659,7 @@
         <v>123</v>
       </c>
       <c r="F96" s="98" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G96" s="99" t="n">
         <v>167</v>
@@ -5658,18 +5668,18 @@
         <v>8</v>
       </c>
       <c r="I96" s="103" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="J96" s="103"/>
       <c r="K96" s="103" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="L96" s="103"/>
       <c r="M96" s="8" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="N96" s="8" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="O96" s="8"/>
       <c r="P96" s="8"/>
@@ -5784,10 +5794,10 @@
     </row>
     <row r="99" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B99" s="49" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D99" s="4" t="s">
         <v>17</v>
@@ -5801,7 +5811,7 @@
         <v>3</v>
       </c>
       <c r="I99" s="9" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="J99" s="8" t="n">
         <v>0</v>
@@ -5884,10 +5894,10 @@
     </row>
     <row r="101" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B101" s="49" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D101" s="4" t="n">
         <v>126</v>
@@ -5901,19 +5911,19 @@
         <v>5</v>
       </c>
       <c r="I101" s="9" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="J101" s="8" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K101" s="8" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="L101" s="8" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M101" s="8" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="N101" s="8" t="s">
         <v>25</v>
@@ -5948,7 +5958,7 @@
     <row r="102" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B102" s="109"/>
       <c r="C102" s="3" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D102" s="4" t="n">
         <v>123</v>
@@ -5962,10 +5972,10 @@
         <v>5</v>
       </c>
       <c r="I102" s="9" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="J102" s="8" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="K102" s="8" t="s">
         <v>57</v>
@@ -6009,7 +6019,7 @@
     <row r="103" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B103" s="109"/>
       <c r="C103" s="3" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D103" s="4" t="n">
         <v>121</v>
@@ -6070,7 +6080,7 @@
     <row r="104" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B104" s="109"/>
       <c r="C104" s="3" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D104" s="4" t="n">
         <v>120</v>
@@ -6171,10 +6181,10 @@
     </row>
     <row r="106" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B106" s="49" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D106" s="4" t="s">
         <v>17</v>
@@ -6194,13 +6204,13 @@
         <v>201</v>
       </c>
       <c r="K106" s="8" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L106" s="8" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="M106" s="8" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="N106" s="8" t="s">
         <v>25</v>
@@ -6275,10 +6285,10 @@
     </row>
     <row r="108" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B108" s="49" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C108" s="110" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D108" s="4" t="s">
         <v>17</v>
@@ -6375,10 +6385,10 @@
     </row>
     <row r="110" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B110" s="49" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D110" s="111" t="n">
         <v>126</v>
@@ -6392,25 +6402,25 @@
         <v>7</v>
       </c>
       <c r="I110" s="9" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="J110" s="8" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K110" s="8" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L110" s="8" t="n">
         <v>126</v>
       </c>
       <c r="M110" s="8" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="N110" s="8" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O110" s="8" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="P110" s="8" t="s">
         <v>25</v>
@@ -6443,7 +6453,7 @@
     <row r="111" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B111" s="49"/>
       <c r="C111" s="3" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D111" s="111" t="n">
         <v>123</v>
@@ -6457,25 +6467,25 @@
         <v>7</v>
       </c>
       <c r="I111" s="9" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="J111" s="8" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K111" s="8" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L111" s="8" t="n">
         <v>123</v>
       </c>
       <c r="M111" s="8" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="N111" s="8" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O111" s="8" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="P111" s="8" t="s">
         <v>25</v>
@@ -6508,7 +6518,7 @@
     <row r="112" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B112" s="49"/>
       <c r="C112" s="3" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D112" s="111" t="n">
         <v>121</v>
@@ -6522,25 +6532,25 @@
         <v>7</v>
       </c>
       <c r="I112" s="9" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="J112" s="8" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K112" s="8" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L112" s="8" t="n">
         <v>121</v>
       </c>
       <c r="M112" s="8" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="N112" s="8" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O112" s="8" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="P112" s="8" t="s">
         <v>25</v>
@@ -6573,7 +6583,7 @@
     <row r="113" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B113" s="49"/>
       <c r="C113" s="3" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D113" s="111" t="n">
         <v>120</v>
@@ -6587,25 +6597,25 @@
         <v>7</v>
       </c>
       <c r="I113" s="9" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="J113" s="8" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K113" s="8" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L113" s="8" t="n">
         <v>120</v>
       </c>
       <c r="M113" s="8" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="N113" s="8" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O113" s="8" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="P113" s="8" t="s">
         <v>25</v>
@@ -6678,14 +6688,14 @@
     </row>
     <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C116" s="112" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D116" s="113" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E116" s="114"/>
       <c r="F116" s="115" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="G116" s="56"/>
     </row>
@@ -6694,7 +6704,7 @@
         <v>15</v>
       </c>
       <c r="C117" s="117" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D117" s="4" t="n">
         <v>254</v>
@@ -6718,7 +6728,7 @@
         <v>59</v>
       </c>
       <c r="C119" s="117" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D119" s="4" t="n">
         <v>239</v>
@@ -6742,7 +6752,7 @@
         <v>117</v>
       </c>
       <c r="C121" s="117" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>211</v>
@@ -6760,7 +6770,7 @@
         <v>127</v>
       </c>
       <c r="C123" s="117" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>

--- a/PGN 5.7_planter.xlsx
+++ b/PGN 5.7_planter.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="380">
   <si>
     <t xml:space="preserve">PGN Name</t>
   </si>
@@ -940,51 +940,63 @@
     <t xml:space="preserve">A4</t>
   </si>
   <si>
-    <t xml:space="preserve">sen1 (kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sen2 (kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sen3 (kg)</t>
+    <t xml:space="preserve">sen1 (kg +5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sen2 (kg +5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sen3 (kg +5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">airDwPres PSI +5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">status bits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">status bit :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 israising</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 islowering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 pressSwt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 isAutoWeight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 is AutoPressure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 use main target</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Downpressure config</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Act weight(kg), 0xFF = no data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">main target (kg or psi) 0-255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alt target (kg or psi) 0-255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">set0,1=true,bit = sensNbr, bit 4-7 : set weight from byte1</t>
   </si>
   <si>
     <t xml:space="preserve">airDwPres PSI</t>
   </si>
   <si>
-    <t xml:space="preserve">status bits</t>
-  </si>
-  <si>
-    <t xml:space="preserve">status bit :</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 israising</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 islowering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 pressSwt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 isAuto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Downpressure config</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Act weight(kg), 0xFF = no data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">set0,1=true,bit = sensNbr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Act PressPSI 0xFF= no data</t>
-  </si>
-  <si>
     <t xml:space="preserve">0 raisePres</t>
   </si>
   <si>
@@ -1010,9 +1022,6 @@
   </si>
   <si>
     <t xml:space="preserve">Set pos 9-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forced 1-8</t>
   </si>
   <si>
     <t xml:space="preserve">Forced 9-16</t>
@@ -1164,7 +1173,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1249,6 +1258,19 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b val="true"/>
@@ -1519,7 +1541,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="120">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1944,6 +1966,10 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1952,6 +1978,10 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1972,15 +2002,15 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="3" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="2" borderId="3" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="2" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="2" borderId="2" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="3" borderId="3" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="3" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5456,7 +5486,7 @@
         <v>281</v>
       </c>
       <c r="N93" s="100"/>
-      <c r="O93" s="8" t="s">
+      <c r="O93" s="106" t="s">
         <v>308</v>
       </c>
       <c r="P93" s="8" t="s">
@@ -5480,15 +5510,19 @@
         <v>313</v>
       </c>
       <c r="X93" s="8"/>
-      <c r="Y93" s="8" t="s">
+      <c r="Y93" s="87" t="s">
         <v>314</v>
       </c>
-      <c r="Z93" s="8"/>
-      <c r="AA93" s="8"/>
-      <c r="AB93" s="8"/>
-      <c r="AC93" s="8"/>
-      <c r="AD93" s="8"/>
-      <c r="AE93" s="8"/>
+      <c r="Z93" s="87"/>
+      <c r="AA93" s="87"/>
+      <c r="AB93" s="87" t="s">
+        <v>315</v>
+      </c>
+      <c r="AC93" s="87"/>
+      <c r="AD93" s="87"/>
+      <c r="AE93" s="8" t="s">
+        <v>316</v>
+      </c>
       <c r="AF93" s="8"/>
       <c r="AG93" s="8"/>
       <c r="AH93" s="8"/>
@@ -5499,10 +5533,10 @@
       <c r="AM93" s="8"/>
       <c r="AN93" s="8"/>
     </row>
-    <row r="94" s="59" customFormat="true" ht="30.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="94" s="59" customFormat="true" ht="64.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B94" s="49"/>
-      <c r="C94" s="106" t="s">
-        <v>315</v>
+      <c r="C94" s="107" t="s">
+        <v>317</v>
       </c>
       <c r="D94" s="96" t="s">
         <v>102</v>
@@ -5511,7 +5545,7 @@
         <v>123</v>
       </c>
       <c r="F94" s="98" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="G94" s="99" t="n">
         <v>165</v>
@@ -5519,24 +5553,24 @@
       <c r="H94" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="I94" s="107" t="s">
-        <v>317</v>
-      </c>
-      <c r="J94" s="107" t="s">
-        <v>317</v>
-      </c>
-      <c r="K94" s="107" t="s">
-        <v>317</v>
-      </c>
-      <c r="L94" s="108" t="s">
-        <v>318</v>
-      </c>
-      <c r="M94" s="108" t="s">
+      <c r="I94" s="108" t="s">
+        <v>319</v>
+      </c>
+      <c r="J94" s="108" t="s">
+        <v>320</v>
+      </c>
+      <c r="K94" s="109" t="s">
+        <v>321</v>
+      </c>
+      <c r="L94" s="110" t="s">
+        <v>322</v>
+      </c>
+      <c r="M94" s="110" t="s">
         <v>287</v>
       </c>
-      <c r="N94" s="108"/>
-      <c r="O94" s="103" t="s">
-        <v>319</v>
+      <c r="N94" s="110"/>
+      <c r="O94" s="8" t="s">
+        <v>323</v>
       </c>
       <c r="P94" s="87" t="s">
         <v>309</v>
@@ -5548,11 +5582,11 @@
         <v>310</v>
       </c>
       <c r="S94" s="87" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="T94" s="87"/>
       <c r="U94" s="87" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="V94" s="87"/>
       <c r="W94" s="87"/>
@@ -5561,13 +5595,17 @@
         <v>314</v>
       </c>
       <c r="Z94" s="87"/>
-      <c r="AA94" s="8"/>
-      <c r="AB94" s="8"/>
-      <c r="AC94" s="8"/>
-      <c r="AD94" s="8"/>
-      <c r="AE94" s="8"/>
-      <c r="AF94" s="8"/>
-      <c r="AG94" s="8"/>
+      <c r="AA94" s="87"/>
+      <c r="AB94" s="87" t="s">
+        <v>315</v>
+      </c>
+      <c r="AC94" s="87"/>
+      <c r="AD94" s="87"/>
+      <c r="AE94" s="87" t="s">
+        <v>316</v>
+      </c>
+      <c r="AF94" s="87"/>
+      <c r="AG94" s="87"/>
       <c r="AH94" s="8"/>
       <c r="AI94" s="8"/>
       <c r="AJ94" s="8"/>
@@ -5579,7 +5617,7 @@
     <row r="95" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B95" s="49"/>
       <c r="C95" s="102" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="D95" s="96" t="s">
         <v>102</v>
@@ -5588,7 +5626,7 @@
         <v>123</v>
       </c>
       <c r="F95" s="98" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="G95" s="99" t="n">
         <v>166</v>
@@ -5597,32 +5635,32 @@
         <v>8</v>
       </c>
       <c r="I95" s="100" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="J95" s="100"/>
       <c r="K95" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="L95" s="8" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="M95" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="N95" s="8" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="O95" s="8" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="P95" s="8" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q95" s="87" t="s">
         <v>25</v>
       </c>
       <c r="R95" s="87" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="S95" s="87"/>
       <c r="T95" s="87"/>
@@ -5650,7 +5688,7 @@
     <row r="96" s="59" customFormat="true" ht="27.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B96" s="49"/>
       <c r="C96" s="102" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="D96" s="96" t="s">
         <v>102</v>
@@ -5659,7 +5697,7 @@
         <v>123</v>
       </c>
       <c r="F96" s="98" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="G96" s="99" t="n">
         <v>167</v>
@@ -5668,18 +5706,18 @@
         <v>8</v>
       </c>
       <c r="I96" s="103" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="J96" s="103"/>
       <c r="K96" s="103" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="L96" s="103"/>
       <c r="M96" s="8" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="N96" s="8" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="O96" s="8"/>
       <c r="P96" s="8"/>
@@ -5794,10 +5832,10 @@
     </row>
     <row r="99" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B99" s="49" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D99" s="4" t="s">
         <v>17</v>
@@ -5811,7 +5849,7 @@
         <v>3</v>
       </c>
       <c r="I99" s="9" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="J99" s="8" t="n">
         <v>0</v>
@@ -5852,7 +5890,7 @@
       <c r="AN99" s="8"/>
     </row>
     <row r="100" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B100" s="109"/>
+      <c r="B100" s="111"/>
       <c r="C100" s="3"/>
       <c r="D100" s="4"/>
       <c r="E100" s="5"/>
@@ -5894,10 +5932,10 @@
     </row>
     <row r="101" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B101" s="49" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="D101" s="4" t="n">
         <v>126</v>
@@ -5911,19 +5949,19 @@
         <v>5</v>
       </c>
       <c r="I101" s="9" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="J101" s="8" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="K101" s="8" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="L101" s="8" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="M101" s="8" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="N101" s="8" t="s">
         <v>25</v>
@@ -5956,9 +5994,9 @@
       <c r="AN101" s="8"/>
     </row>
     <row r="102" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B102" s="109"/>
+      <c r="B102" s="111"/>
       <c r="C102" s="3" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D102" s="4" t="n">
         <v>123</v>
@@ -5972,10 +6010,10 @@
         <v>5</v>
       </c>
       <c r="I102" s="9" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="J102" s="8" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="K102" s="8" t="s">
         <v>57</v>
@@ -6017,9 +6055,9 @@
       <c r="AN102" s="8"/>
     </row>
     <row r="103" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B103" s="109"/>
+      <c r="B103" s="111"/>
       <c r="C103" s="3" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D103" s="4" t="n">
         <v>121</v>
@@ -6078,9 +6116,9 @@
       <c r="AN103" s="8"/>
     </row>
     <row r="104" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B104" s="109"/>
+      <c r="B104" s="111"/>
       <c r="C104" s="3" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="D104" s="4" t="n">
         <v>120</v>
@@ -6181,10 +6219,10 @@
     </row>
     <row r="106" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B106" s="49" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="D106" s="4" t="s">
         <v>17</v>
@@ -6204,13 +6242,13 @@
         <v>201</v>
       </c>
       <c r="K106" s="8" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="L106" s="8" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="M106" s="8" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="N106" s="8" t="s">
         <v>25</v>
@@ -6285,10 +6323,10 @@
     </row>
     <row r="108" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B108" s="49" t="s">
-        <v>353</v>
-      </c>
-      <c r="C108" s="110" t="s">
-        <v>358</v>
+        <v>356</v>
+      </c>
+      <c r="C108" s="112" t="s">
+        <v>361</v>
       </c>
       <c r="D108" s="4" t="s">
         <v>17</v>
@@ -6344,7 +6382,7 @@
     </row>
     <row r="109" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B109" s="49"/>
-      <c r="C109" s="110"/>
+      <c r="C109" s="112"/>
       <c r="D109" s="4"/>
       <c r="E109" s="5"/>
       <c r="F109" s="6"/>
@@ -6385,12 +6423,12 @@
     </row>
     <row r="110" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B110" s="49" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="D110" s="111" t="n">
+        <v>363</v>
+      </c>
+      <c r="D110" s="113" t="n">
         <v>126</v>
       </c>
       <c r="E110" s="5"/>
@@ -6402,25 +6440,25 @@
         <v>7</v>
       </c>
       <c r="I110" s="9" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="J110" s="8" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="K110" s="8" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="L110" s="8" t="n">
         <v>126</v>
       </c>
       <c r="M110" s="8" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="N110" s="8" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="O110" s="8" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="P110" s="8" t="s">
         <v>25</v>
@@ -6453,9 +6491,9 @@
     <row r="111" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B111" s="49"/>
       <c r="C111" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="D111" s="111" t="n">
+        <v>370</v>
+      </c>
+      <c r="D111" s="113" t="n">
         <v>123</v>
       </c>
       <c r="E111" s="5"/>
@@ -6467,25 +6505,25 @@
         <v>7</v>
       </c>
       <c r="I111" s="9" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="J111" s="8" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="K111" s="8" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="L111" s="8" t="n">
         <v>123</v>
       </c>
       <c r="M111" s="8" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="N111" s="8" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="O111" s="8" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="P111" s="8" t="s">
         <v>25</v>
@@ -6518,9 +6556,9 @@
     <row r="112" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B112" s="49"/>
       <c r="C112" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="D112" s="111" t="n">
+        <v>371</v>
+      </c>
+      <c r="D112" s="113" t="n">
         <v>121</v>
       </c>
       <c r="E112" s="5"/>
@@ -6532,25 +6570,25 @@
         <v>7</v>
       </c>
       <c r="I112" s="9" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="J112" s="8" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="K112" s="8" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="L112" s="8" t="n">
         <v>121</v>
       </c>
       <c r="M112" s="8" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="N112" s="8" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="O112" s="8" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="P112" s="8" t="s">
         <v>25</v>
@@ -6583,9 +6621,9 @@
     <row r="113" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B113" s="49"/>
       <c r="C113" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="D113" s="111" t="n">
+        <v>372</v>
+      </c>
+      <c r="D113" s="113" t="n">
         <v>120</v>
       </c>
       <c r="E113" s="5"/>
@@ -6597,25 +6635,25 @@
         <v>7</v>
       </c>
       <c r="I113" s="9" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="J113" s="8" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="K113" s="8" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="L113" s="8" t="n">
         <v>120</v>
       </c>
       <c r="M113" s="8" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="N113" s="8" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="O113" s="8" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="P113" s="8" t="s">
         <v>25</v>
@@ -6648,7 +6686,7 @@
     <row r="114" s="59" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B114" s="49"/>
       <c r="C114" s="3"/>
-      <c r="D114" s="111"/>
+      <c r="D114" s="113"/>
       <c r="E114" s="5"/>
       <c r="F114" s="6"/>
       <c r="G114" s="7"/>
@@ -6687,24 +6725,24 @@
       <c r="AN114" s="8"/>
     </row>
     <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C116" s="112" t="s">
-        <v>370</v>
-      </c>
-      <c r="D116" s="113" t="s">
-        <v>371</v>
-      </c>
-      <c r="E116" s="114"/>
-      <c r="F116" s="115" t="s">
-        <v>372</v>
+      <c r="C116" s="114" t="s">
+        <v>373</v>
+      </c>
+      <c r="D116" s="115" t="s">
+        <v>374</v>
+      </c>
+      <c r="E116" s="116"/>
+      <c r="F116" s="117" t="s">
+        <v>375</v>
       </c>
       <c r="G116" s="56"/>
     </row>
     <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B117" s="116" t="s">
+      <c r="B117" s="118" t="s">
         <v>15</v>
       </c>
-      <c r="C117" s="117" t="s">
-        <v>373</v>
+      <c r="C117" s="119" t="s">
+        <v>376</v>
       </c>
       <c r="D117" s="4" t="n">
         <v>254</v>
@@ -6720,15 +6758,15 @@
       </c>
     </row>
     <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B118" s="116"/>
-      <c r="C118" s="117"/>
+      <c r="B118" s="118"/>
+      <c r="C118" s="119"/>
     </row>
     <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B119" s="116" t="s">
+      <c r="B119" s="118" t="s">
         <v>59</v>
       </c>
-      <c r="C119" s="117" t="s">
-        <v>374</v>
+      <c r="C119" s="119" t="s">
+        <v>377</v>
       </c>
       <c r="D119" s="4" t="n">
         <v>239</v>
@@ -6744,15 +6782,15 @@
       </c>
     </row>
     <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B120" s="116"/>
-      <c r="C120" s="117"/>
+      <c r="B120" s="118"/>
+      <c r="C120" s="119"/>
     </row>
     <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B121" s="116" t="s">
+      <c r="B121" s="118" t="s">
         <v>117</v>
       </c>
-      <c r="C121" s="117" t="s">
-        <v>375</v>
+      <c r="C121" s="119" t="s">
+        <v>378</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>211</v>
@@ -6762,19 +6800,19 @@
       </c>
     </row>
     <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B122" s="116"/>
-      <c r="C122" s="117"/>
+      <c r="B122" s="118"/>
+      <c r="C122" s="119"/>
     </row>
     <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B123" s="116" t="s">
+      <c r="B123" s="118" t="s">
         <v>127</v>
       </c>
-      <c r="C123" s="117" t="s">
-        <v>376</v>
+      <c r="C123" s="119" t="s">
+        <v>379</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="41">
+  <mergeCells count="45">
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="N5:O5"/>
@@ -6806,12 +6844,16 @@
     <mergeCell ref="S93:T93"/>
     <mergeCell ref="U93:V93"/>
     <mergeCell ref="W93:X93"/>
-    <mergeCell ref="Y93:Z93"/>
+    <mergeCell ref="Y93:AA93"/>
+    <mergeCell ref="AB93:AD93"/>
+    <mergeCell ref="AE93:AG93"/>
     <mergeCell ref="M94:N94"/>
     <mergeCell ref="S94:T94"/>
     <mergeCell ref="U94:V94"/>
     <mergeCell ref="W94:X94"/>
-    <mergeCell ref="Y94:Z94"/>
+    <mergeCell ref="Y94:AA94"/>
+    <mergeCell ref="AB94:AD94"/>
+    <mergeCell ref="AE94:AG94"/>
     <mergeCell ref="I95:J95"/>
     <mergeCell ref="R95:V95"/>
     <mergeCell ref="I96:J96"/>
